--- a/data/programme.xlsx
+++ b/data/programme.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11220" yWindow="3910" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Настройки" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Секции" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Блоки" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Доклады" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Постеры" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Изменения" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Секции" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Блоки" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Доклады" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Постеры" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Изменения" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -20,10 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
     <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy\ hh:mm"/>
+    <numFmt numFmtId="167" formatCode="HH:MM"/>
+    <numFmt numFmtId="168" formatCode="YYYY-MM-DD HH:MM"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -65,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -76,6 +78,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -999,7 +1004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1009,7 +1014,8 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="11"/>
+    <col width="22" customWidth="1" min="10" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1060,10 +1066,20 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Председатель (RU)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Председатель (EN)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Примечание (RU)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Примечание (EN)</t>
         </is>
@@ -1094,6 +1110,11 @@
           <t>Registration</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>вестибюль</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1125,6 +1146,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Купряшкин И. В.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>I. V. Kupryashkin</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1166,6 +1197,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Купряшкин И. В.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>I. V. Kupryashkin</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1207,6 +1248,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Купряшкин И. В.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>I. V. Kupryashkin</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1274,6 +1325,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Чувильский Ю. М.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Yu. M. Tchuvil'sky</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1315,6 +1376,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Чувильский Ю. М.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yu. M. Tchuvil'sky</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1356,6 +1427,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Чувильский Ю. М.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yu. M. Tchuvil'sky</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1423,6 +1504,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Сидорчук С. И.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>S. I. Sidorchuk</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1464,6 +1555,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Сидорчук С. И.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>S. I. Sidorchuk</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1505,6 +1606,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Сидорчук С. И.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>S. I. Sidorchuk</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1546,6 +1657,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Сидорчук С. И.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>S. I. Sidorchuk</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1587,6 +1708,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Сидорчук С. И.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>S. I. Sidorchuk</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1641,7 +1772,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>235ц</t>
+          <t>библиотека</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1803,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>144ц</t>
+          <t>235ц</t>
         </is>
       </c>
     </row>
@@ -1804,6 +1935,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Титова Л. В.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>L. V. Titova</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1845,6 +1986,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Титова Л. В.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>L. V. Titova</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1886,6 +2037,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Титова Л. В.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>L. V. Titova</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1953,6 +2114,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Чувильский Ю. М.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Yu. M. Tchuvil'sky</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1994,6 +2165,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Чувильский Ю. М.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Yu. M. Tchuvil'sky</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2035,6 +2216,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Чувильский Ю. М.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Yu. M. Tchuvil'sky</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -2089,7 +2280,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>235ц</t>
+          <t>библиотека</t>
         </is>
       </c>
     </row>
@@ -2100,8 +2291,8 @@
       <c r="B31" s="3" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>0.65625</v>
+      <c r="C31" s="6" t="n">
+        <v>0.6458333333333334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2115,12 +2306,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8-14</t>
+          <t>8-13</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>144ц</t>
+          <t>235ц</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2430,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>144ц</t>
+          <t>235ц</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2461,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>235ц</t>
+          <t>библиотека</t>
         </is>
       </c>
     </row>
@@ -2281,8 +2472,8 @@
       <c r="B37" s="3" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="C37" s="3" t="n">
-        <v>0.75</v>
+      <c r="C37" s="6" t="n">
+        <v>0.7291666666666666</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2296,7 +2487,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8-14</t>
+          <t>8-12</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2402,6 +2593,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Жеребчевский В. И.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>V. I. Zherebchevsky</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -2443,6 +2644,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Жеребчевский В. И.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>V. I. Zherebchevsky</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2484,6 +2695,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Жеребчевский В. И.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>V. I. Zherebchevsky</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -2551,6 +2772,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Черняев А. П.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>A. P. Chernyaev</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2592,6 +2823,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Черняев А. П.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>A. P. Chernyaev</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2633,6 +2874,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Черняев А. П.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>A. P. Chernyaev</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2687,7 +2938,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>235ц</t>
+          <t>библиотека</t>
         </is>
       </c>
     </row>
@@ -2698,8 +2949,8 @@
       <c r="B49" s="3" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C49" s="3" t="n">
-        <v>0.6666666666666666</v>
+      <c r="C49" s="6" t="n">
+        <v>0.65625</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2713,12 +2964,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>22-29</t>
+          <t>22-28</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>144ц</t>
+          <t>235ц</t>
         </is>
       </c>
     </row>
@@ -2835,12 +3086,17 @@
           <t>Poster session</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>холл2</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>Время уточняется</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Time to be confirmed</t>
         </is>
@@ -2886,6 +3142,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Нестеренко В.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>V. Nesterenko</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -2927,6 +3193,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Нестеренко В.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>V. Nesterenko</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -2968,6 +3244,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Нестеренко В.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>V. Nesterenko</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -3035,6 +3321,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Яковлев С. Л.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>S. L. Yakovlev</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -3076,6 +3372,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Яковлев С. Л.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>S. L. Yakovlev</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3117,6 +3423,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Яковлев С. Л.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>S. L. Yakovlev</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -3236,6 +3552,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Пшеничнов И. А.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>I. A. Pshenichnov</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -3277,6 +3603,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Пшеничнов И. А.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>I. A. Pshenichnov</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3318,6 +3654,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Пшеничнов И. А.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>I. A. Pshenichnov</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -3385,6 +3731,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Мочалов В. В.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>V. V. Mochalov</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -3426,6 +3782,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Мочалов В. В.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>V. V. Mochalov</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -3467,6 +3833,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Мочалов В. В.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>V. V. Mochalov</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -3501,8 +3877,8 @@
       <c r="B72" s="3" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C72" s="3" t="n">
-        <v>0.65625</v>
+      <c r="C72" s="6" t="n">
+        <v>0.6354166666666666</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3516,7 +3892,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>23-29</t>
+          <t>23-27</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3614,7 +3990,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>144ц</t>
+          <t>библиотека</t>
         </is>
       </c>
     </row>
@@ -3702,7 +4078,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>144ц</t>
+          <t>библиотека</t>
         </is>
       </c>
     </row>
@@ -3777,6 +4153,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Мазур А. И.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>A. I. Mazur</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -3818,6 +4204,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Мазур А. И.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>A. I. Mazur</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -3857,6 +4253,16 @@
       <c r="I82" t="inlineStr">
         <is>
           <t>235ц</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Мазур А. И.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>A. I. Mazur</t>
         </is>
       </c>
     </row>
@@ -3933,7 +4339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O198"/>
+  <dimension ref="A1:O192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5105,7 +5511,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5205,7 +5611,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5255,7 +5661,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5305,7 +5711,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5386,11 +5792,6 @@
       <c r="J29" t="n">
         <v>30</v>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>отменён</t>
-        </is>
-      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>2</t>
@@ -5705,7 +6106,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5750,7 +6151,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7010,107 +7411,101 @@
     <row r="66" ht="174" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S1-28</t>
+          <t>S2-02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>28</v>
-      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Мардыбан</t>
+          <t>Демьянова</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Евгений</t>
+          <t>Алла</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Сергеевна</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИЦ КИ</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>mardyban@theor.jinr.ru</t>
+          <t>a.s.demyanova@bk.ru</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>Isotopic dependence of the fission threshold in nuclei with Z=114 and Z=120</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>отменён</t>
+          <t>Анализ реакции срыва ¹³C(d,t)¹²C в области энергий 13–18 мэв: определение асимптотических нормировочных коэффициентов и структуры состояний ядра ¹²C</t>
         </is>
       </c>
     </row>
     <row r="67" ht="319" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S1-29</t>
+          <t>S2-03</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>29</v>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Безбах</t>
+          <t>Соловьев</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Сергеевич</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ВНИИА</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>bezbakh@theor.jinr.ru</t>
+          <t>alexander.solovyev@mail.ru</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>Анализ альфа-распадных цепочек элементов 119 и 120 в двухцентровой оболочечной модели: конкуренция незапрещённых и запрещённых переходов</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>отменён</t>
+          <t>Полный и парциальные астрофизические S-факторы реакции ³He(d, p)⁴He в микроскопическом кластерном подходе</t>
         </is>
       </c>
     </row>
     <row r="68" ht="290" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S2-01</t>
+          <t>S2-04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7118,49 +7513,46 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C68" t="n">
-        <v>1</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Данилов</t>
+          <t>Куликов</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Василий</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>danilov1987@mail.ru</t>
+          <t>kulikov@nucl-th.sinp.msu.ru</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>Анализ рассеяния дейтронов на ядре ¹³C в области энергий 13–18 МэВ: структура возбуждённых состояний и нейтронное гало</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>отменён</t>
+          <t>Ab initio description of scattering</t>
         </is>
       </c>
     </row>
     <row r="69" ht="362.5" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S2-02</t>
+          <t>S2-05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7168,44 +7560,41 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>2</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Демьянова</t>
+          <t>Shakhov</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Алла</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Сергеевна</t>
+          <t>Aleksei</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>a.s.demyanova@bk.ru</t>
+          <t>shahov@jinr.ru</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Анализ реакции срыва ¹³C(d,t)¹²C в области энергий 13–18 мэв: определение асимптотических нормировочных коэффициентов и структуры состояний ядра ¹²C</t>
+          <t>Multinucleon transfer reactions in ⁷Li, ¹²C,⁴⁰Ar, ⁴⁰⸴ ⁴⁸Ca + ¹⁹⁷Au</t>
         </is>
       </c>
     </row>
     <row r="70" ht="275.5" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S2-03</t>
+          <t>S2-06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7213,44 +7602,46 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C70" t="n">
-        <v>3</v>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Соловьев</t>
+          <t>Егоров</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Михаил</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Сергеевич</t>
+          <t>Викторович</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ВНИИА</t>
+          <t>ТГУ(Томск)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>alexander.solovyev@mail.ru</t>
+          <t>egorovphys@mail.ru</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>Полный и парциальные астрофизические S-факторы реакции ³He(d, p)⁴He в микроскопическом кластерном подходе</t>
+          <t>Мультикластерная реализация задачи трёх тел на примере ядерных реакций с лёгкими ядрами</t>
         </is>
       </c>
     </row>
     <row r="71" ht="72.5" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S2-04</t>
+          <t>S2-07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7258,22 +7649,24 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C71" t="n">
-        <v>4</v>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Куликов</t>
+          <t>Яников</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Василий</t>
+          <t>Устин</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Михайлович</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -7283,19 +7676,19 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>kulikov@nucl-th.sinp.msu.ru</t>
+          <t>yanikov-u@yandex.ru</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Ab initio description of scattering</t>
+          <t>Учет кулоновской асимптотики в формализме осцилляторного представления теории рассеяния</t>
         </is>
       </c>
     </row>
     <row r="72" ht="130.5" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S2-05</t>
+          <t>S2-08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7304,16 +7697,21 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Shakhov</t>
+          <t>Изосимов</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aleksei</t>
+          <t>Игорь</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -7323,19 +7721,19 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>shahov@jinr.ru</t>
+          <t>izosimov@jinr.ru</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>Multinucleon transfer reactions in ⁷Li, ¹²C,⁴⁰Ar, ⁴⁰⸴ ⁴⁸Ca + ¹⁹⁷Au</t>
+          <t>Excitation and decay of the Gamow-Teller resonance and its satellites in compaund nuclei</t>
         </is>
       </c>
     </row>
     <row r="73" ht="232" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S2-06</t>
+          <t>S2-10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7343,44 +7741,41 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>6</v>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Егоров</t>
+          <t>Tran</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Михаил</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Викторович</t>
+          <t>Ngoc TOan</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ТГУ(Томск)</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>egorovphys@mail.ru</t>
+          <t>chan@jinr.ru</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>Мультикластерная реализация задачи трёх тел на примере ядерных реакций с лёгкими ядрами</t>
+          <t>Theoretical and experimental investigation on the optimization of accelerator driven subcritical reactors</t>
         </is>
       </c>
     </row>
     <row r="74" ht="203" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S2-07</t>
+          <t>S2-11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7388,44 +7783,46 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C74" t="n">
-        <v>7</v>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Яников</t>
+          <t>Уланова</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Устин</t>
+          <t>Ирина</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Михайлович</t>
+          <t>Ивановна</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>yanikov-u@yandex.ru</t>
+          <t>ulanova@jinr.ru</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>Учет кулоновской асимптотики в формализме осцилляторного представления теории рассеяния</t>
+          <t>Время-проекционная камера для исследования свойств распада сверхтяжелых ядер</t>
         </is>
       </c>
     </row>
     <row r="75" ht="203" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S2-08</t>
+          <t>S2-12</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7433,22 +7830,24 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>8</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Изосимов</t>
+          <t>Шевчик</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Егор</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -7458,19 +7857,19 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>izosimov@jinr.ru</t>
+          <t>shevchik@jinr.ru</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>Excitation and decay of the Gamow-Teller resonance and its satellites in compaund nuclei</t>
+          <t>Активная аргоновая защита в низкофоновых экспериментах по поиску двойного безнейтринного бета распада GERDA и LEGEND</t>
         </is>
       </c>
     </row>
     <row r="76" ht="203" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S2-09</t>
+          <t>S2-13</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7478,22 +7877,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>9</v>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Каманин</t>
+          <t>Shehada</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Владимирович</t>
+          <t>Abdullah</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -7503,24 +7899,19 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>kamanin@jinr.ru</t>
+          <t>shikhada@jinr.ru</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>Status of research on fissioning isomers in the fragments of binary fission of heavy nuclei</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>отменён</t>
+          <t>Comparative study of simulated and measured isotope production in target and HPGe detector in muon capture experiments</t>
         </is>
       </c>
     </row>
     <row r="77" ht="217.5" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S2-10</t>
+          <t>S2-14</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7528,17 +7919,24 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>10</v>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tran</t>
+          <t>Fedorov</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ngoc TOan</t>
+          <t>Nikita</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Alexandrovich</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7548,19 +7946,19 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>chan@jinr.ru</t>
+          <t>na.fedorov@physics.msu.ru</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>Theoretical and experimental investigation on the optimization of accelerator driven subcritical reactors</t>
+          <t>Development of the evaluated cross sections database for (n,xγ)-type reactions</t>
         </is>
       </c>
     </row>
     <row r="78" ht="174" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S2-11</t>
+          <t>S2-15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7569,21 +7967,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Уланова</t>
+          <t>Грозданов</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ирина</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Ивановна</t>
+          <t>Димитър</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -7593,19 +7986,19 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ulanova@jinr.ru</t>
+          <t>dimitar@nf.jinr.ru</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>Время-проекционная камера для исследования свойств распада сверхтяжелых ядер</t>
+          <t>Measurements of the gamma-ray emission cross sections and angular distributions from (n, xγ) reactions with 14.1 MeV neutrons</t>
         </is>
       </c>
     </row>
     <row r="79" ht="304.5" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S2-12</t>
+          <t>S2-16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7614,16 +8007,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Шевчик</t>
+          <t>Демичев</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Егор</t>
+          <t>Михаил</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7638,19 +8031,19 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>shevchik@jinr.ru</t>
+          <t>mdemichev@jinr.ru</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>Активная аргоновая защита в низкофоновых экспериментах по поиску двойного безнейтринного бета распада GERDA и LEGEND</t>
+          <t>Измерение выхода фотоядерной реакции (γ,p5n) на ядре висмута</t>
         </is>
       </c>
     </row>
     <row r="80" ht="261" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S2-13</t>
+          <t>S2-17</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7659,38 +8052,43 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Shehada</t>
+          <t>Ким</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Abdullah</t>
+          <t>Андрей</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>shikhada@jinr.ru</t>
+          <t>kim@srd.sinp.msu.ru</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>Comparative study of simulated and measured isotope production in target and HPGe detector in muon capture experiments</t>
+          <t>Фотоядерные реакции с вылетом протонов на изотопах эрбия</t>
         </is>
       </c>
     </row>
     <row r="81" ht="174" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S2-14</t>
+          <t>S2-19</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7699,43 +8097,43 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Fedorov</t>
+          <t>Давыдов</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nikita</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Alexandrovich</t>
+          <t>Иванович</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>na.fedorov@physics.msu.ru</t>
+          <t>aleksander.davydov@physmsu.ru</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>Development of the evaluated cross sections database for (n,xγ)-type reactions</t>
+          <t>Особенности фоторасщепления изотопов рения ¹⁸⁵⸴ ¹⁸⁷Re</t>
         </is>
       </c>
     </row>
     <row r="82" ht="290" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S2-15</t>
+          <t>S2-20</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7744,38 +8142,43 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Грозданов</t>
+          <t>Титова</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Димитър</t>
+          <t>Лариса</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Витальевна</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ВГУ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>dimitar@nf.jinr.ru</t>
+          <t>titova_lv@phys.vsu.ru</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>Measurements of the gamma-ray emission cross sections and angular distributions from (n, xγ) reactions with 14.1 MeV neutrons</t>
+          <t>Определение вероятностей формирования предразрывных конфигураций в тройном делении ядер</t>
         </is>
       </c>
     </row>
     <row r="83" ht="145" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S2-16</t>
+          <t>S2-21</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7784,43 +8187,43 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Демичев</t>
+          <t>Любашевский</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Дмитрий</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Евгеньевич</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ВГУ</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>mdemichev@jinr.ru</t>
+          <t>dima_physicist@mail.ru</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>Измерение выхода фотоядерной реакции (γ,p5n) на ядре висмута</t>
+          <t>Моменты инерции bending-моды и их влияние на спины фрагментов деления</t>
         </is>
       </c>
     </row>
     <row r="84" ht="145" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S2-17</t>
+          <t>S2-22</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7829,43 +8232,38 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ким</t>
+          <t>Abdullah</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Андрей</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Александрович</t>
+          <t>Md. Nure Alam</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>Бангладеш</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>kim@srd.sinp.msu.ru</t>
+          <t>abdullah@phy.jnu.ac.bd</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>Фотоядерные реакции с вылетом протонов на изотопах эрбия</t>
+          <t>Potential description of α+¹⁹⁷Au elastic scattering</t>
         </is>
       </c>
     </row>
     <row r="85" ht="130.5" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S2-19</t>
+          <t>S2-23</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7873,44 +8271,41 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>19</v>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Давыдов</t>
+          <t>Галюзов</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Александр</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Иванович</t>
+          <t>Андрей</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ВНИИА</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>aleksander.davydov@physmsu.ru</t>
+          <t>agar10@yandex.ru</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>Особенности фоторасщепления изотопов рения ¹⁸⁵⸴ ¹⁸⁷Re</t>
+          <t>Описание дифференциальных сечений упругого рассеяния изотопов водорода в теории прямых ядерных реакций</t>
         </is>
       </c>
     </row>
     <row r="86" ht="203" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S2-20</t>
+          <t>S2-24</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7918,44 +8313,41 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>20</v>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Титова</t>
+          <t>Музалевский</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Лариса</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Витальевна</t>
+          <t>Иван</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ВГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>titova_lv@phys.vsu.ru</t>
+          <t>muzalevsky@jinr.ru</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>Определение вероятностей формирования предразрывных конфигураций в тройном делении ядер</t>
+          <t>Исследование рассеяния ⁶He - ⁴He на фрагмент-сепараторе АКУЛИНА-2</t>
         </is>
       </c>
     </row>
     <row r="87" ht="188.5" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S2-21</t>
+          <t>S2-25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7963,44 +8355,46 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>21</v>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Любашевский</t>
+          <t>Naumenko</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Mikhail</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Евгеньевич</t>
+          <t>Alekseyevich</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ВГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>dima_physicist@mail.ru</t>
+          <t>anaumenko@jinr.ru</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>Моменты инерции bending-моды и их влияние на спины фрагментов деления</t>
+          <t>Experimental studies of ¹⁰B(⁷Li, ⁸Li)⁹B transfer reaction at 58 MeV</t>
         </is>
       </c>
     </row>
     <row r="88" ht="130.5" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S2-22</t>
+          <t>S2-26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8008,39 +8402,46 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C88" t="n">
-        <v>22</v>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Abdullah</t>
+          <t>Поташев</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Md. Nure Alam</t>
+          <t>Станислав</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ильич</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Бангладеш</t>
+          <t>ИЯИ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>abdullah@phy.jnu.ac.bd</t>
+          <t>s.potashev@mail.ru</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>Potential description of α+¹⁹⁷Au elastic scattering</t>
+          <t>Экспериментальный поиск аномалии при снятии возбуждения ядра ⁸Ве* с испусканием электрон-позитронной пары в реакции взаимодействия нейтронов с энергией свыше 20 МэВ с ядром ¹⁰В</t>
         </is>
       </c>
     </row>
     <row r="89" ht="290" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S2-23</t>
+          <t>S2-27</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8048,39 +8449,41 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C89" t="n">
-        <v>23</v>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Галюзов</t>
+          <t>Макаров</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Данила</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ВНИИА</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>agar10@yandex.ru</t>
+          <t>makarov-danila-2001@mail.ru</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>Описание дифференциальных сечений упругого рассеяния изотопов водорода в теории прямых ядерных реакций</t>
+          <t>Изучение механизмов выбивания нейтрона в реакции ⁹Be(⁷Be, ⁶Be)X при промежуточной энергии</t>
         </is>
       </c>
     </row>
     <row r="90" ht="159.5" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S2-24</t>
+          <t>S2-28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8088,17 +8491,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v>24</v>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Музалевский</t>
+          <t>Безбах</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Андрей</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -8108,19 +8513,19 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>muzalevsky@jinr.ru</t>
+          <t>bezbakh@jinr.ru</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>Исследование рассеяния ⁶He - ⁴He на фрагмент-сепараторе АКУЛИНА-2</t>
+          <t>Измерение угловых распределений распада ⁷He заселяемого в реакции ⁶He(d,p)</t>
         </is>
       </c>
     </row>
     <row r="91" ht="145" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S2-25</t>
+          <t>S2-29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8128,22 +8533,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C91" t="n">
-        <v>25</v>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Naumenko</t>
+          <t>Ryzhkov</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mikhail</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Alekseyevich</t>
+          <t>Nikita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8153,19 +8555,19 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>anaumenko@jinr.ru</t>
+          <t>ryzhkov@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>Experimental studies of ¹⁰B(⁷Li, ⁸Li)⁹B transfer reaction at 58 MeV</t>
+          <t>Analytical approach to the generation of angular momentum in spontaneous fission fragments</t>
         </is>
       </c>
     </row>
     <row r="92" ht="409.5" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S2-26</t>
+          <t>S2-30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8174,43 +8576,38 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Поташев</t>
+          <t>Адоньев</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Станислав</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Ильич</t>
+          <t>Степан</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>s.potashev@mail.ru</t>
+          <t>stepan1018@mail.ru</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>Экспериментальный поиск аномалии при снятии возбуждения ядра ⁸Ве* с испусканием электрон-позитронной пары в реакции взаимодействия нейтронов с энергией свыше 20 МэВ с ядром ¹⁰В</t>
+          <t>Исследование протон-индуцированных реакций на висмуте-209</t>
         </is>
       </c>
     </row>
     <row r="93" ht="232" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S2-27</t>
+          <t>S2-31</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8219,16 +8616,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Макаров</t>
+          <t>Karanfil</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Данила</t>
+          <t>Ege</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8238,19 +8635,19 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>makarov-danila-2001@mail.ru</t>
+          <t>karanfil@jinr.ru</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>Изучение механизмов выбивания нейтрона в реакции ⁹Be(⁷Be, ⁶Be)X при промежуточной энергии</t>
+          <t>²³⁷Np+⁴⁸Ca reaction and decay properties of ²⁸²Nh and descendant nuclei at DGFRS‑2</t>
         </is>
       </c>
     </row>
     <row r="94" ht="174" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S2-28</t>
+          <t>S2-32</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8259,16 +8656,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Безбах</t>
+          <t>Mikhailova</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Tatiana</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8278,19 +8675,19 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>bezbakh@jinr.ru</t>
+          <t>tmikh@jinr.ru</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>Измерение угловых распределений распада ⁷He заселяемого в реакции ⁶He(d,p)</t>
+          <t>Modeling of isotopic scaling and target ratio in transport statistical approach</t>
         </is>
       </c>
     </row>
     <row r="95" ht="203" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S2-29</t>
+          <t>S2-33</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8299,38 +8696,38 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ryzhkov</t>
+          <t>Молоторенко</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nikita</t>
+          <t>Ксения</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ВГУ, ОИЯИ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>ryzhkov@theor.jinr.ru</t>
+          <t>molotorenkoksenia@gmail.com</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>Analytical approach to the generation of angular momentum in spontaneous fission fragments</t>
+          <t>Роль нейтронного избытка в механизмах передачи нуклонов в реакциях тяжелых ионов ⁴⁰⸴ ⁴⁸Ca + ¹⁹⁷Au</t>
         </is>
       </c>
     </row>
     <row r="96" ht="145" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S2-30</t>
+          <t>S2-34</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8339,38 +8736,38 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Адоньев</t>
+          <t>Унжакова</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Степан</t>
+          <t>Анна</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stepan1018@mail.ru</t>
+          <t>a.unzhakova@spbu.ru</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>Исследование протон-индуцированных реакций на висмуте-209</t>
+          <t>Multi-agent modeling of collective dynamics in heavy nuclei fission</t>
         </is>
       </c>
     </row>
     <row r="97" ht="188.5" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S2-31</t>
+          <t>S2-35</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8379,38 +8776,43 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Karanfil</t>
+          <t>Goncharenko</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ege</t>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Alexandrovich</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>karanfil@jinr.ru</t>
+          <t>iv.gonch.0907@gmail.com</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>²³⁷Np+⁴⁸Ca reaction and decay properties of ²⁸²Nh and descendant nuclei at DGFRS‑2</t>
+          <t>Neutron yield uncertainty calculations for (α, n) reactions using the NeuCBOT program</t>
         </is>
       </c>
     </row>
     <row r="98" ht="188.5" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S2-32</t>
+          <t>S2-36</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8419,16 +8821,21 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mikhailova</t>
+          <t>Андреев</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tatiana</t>
+          <t>Александр</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8438,189 +8845,194 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>tmikh@jinr.ru</t>
+          <t>andreev.av20@physics.msu.ru</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>Modeling of isotopic scaling and target ratio in transport statistical approach</t>
+          <t>Theoretical calculation of the angular anisotropy of gamma radiation on carbon, cromium and iron nuclei in inelastic neutron scattering</t>
         </is>
       </c>
     </row>
     <row r="99" ht="246.5" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S2-33</t>
+          <t>S3-01</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Молоторенко</t>
+          <t>Ковалев</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ксения</t>
+          <t>Максим</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Борисович</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>ВГУ, ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>molotorenkoksenia@gmail.com</t>
+          <t>physics1818@yandex.ru</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>Роль нейтронного избытка в механизмах передачи нуклонов в реакциях тяжелых ионов ⁴⁰⸴ ⁴⁸Ca + ¹⁹⁷Au</t>
+          <t>Исследование эффекта наложения сигналов (pile-up) при регистрации ат-мосферных мюонов в нейтринном телескопе Baikal-GVD.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="159.5" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S2-34</t>
+          <t>S3-02</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Унжакова</t>
+          <t>Скобляков</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Викторович</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>НИЦ КИ</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>a.unzhakova@spbu.ru</t>
+          <t>dinAlt220@yandex.ru</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>Multi-agent modeling of collective dynamics in heavy nuclei fission</t>
+          <t>Виртуальный генератор потока АТМОСФЕРНЫХ мюонов В варьируемом диапазоне энергий до 100 ТэВ</t>
         </is>
       </c>
     </row>
     <row r="101" ht="188.5" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S2-35</t>
+          <t>S3-03</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Goncharenko</t>
+          <t>Канцырев</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Alexandrovich</t>
+          <t>Викторович</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>НИЦ КИ</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>iv.gonch.0907@gmail.com</t>
+          <t>kantsyrev@itep.ru</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>Neutron yield uncertainty calculations for (α, n) reactions using the NeuCBOT program</t>
+          <t>Мюонная томография крупномасштабных объектов с применением компактных цилиндрических позиционно-чувствительных детекторов</t>
         </is>
       </c>
     </row>
     <row r="102" ht="290" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S2-36</t>
+          <t>S3-04</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Андреев</t>
+          <t>Лашин</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Александр</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Владимирович</t>
+          <t>Константин</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ВНИИЭФ</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>andreev.av20@physics.msu.ru</t>
+          <t>kosty2112@gmail.com</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>Theoretical calculation of the angular anisotropy of gamma radiation on carbon, cromium and iron nuclei in inelastic neutron scattering</t>
+          <t>Реконструкция плотности многокомпонентных объектов в протонной радиографии с использованием метода роя частиц и преобразования Абеля</t>
         </is>
       </c>
     </row>
     <row r="103" ht="290" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S3-01</t>
+          <t>S3-05</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8629,43 +9041,43 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Ковалев</t>
+          <t>Олейников</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Владислав</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Петрович</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>ИЯФ Новосиб</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>physics1818@yandex.ru</t>
+          <t>V.P.Oleynikov@inp.nsk.su</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>Исследование эффекта наложения сигналов (pile-up) при регистрации ат-мосферных мюонов в нейтринном телескопе Baikal-GVD.</t>
+          <t>Измерение ионизационных выходов ядер отдачи в аргоне</t>
         </is>
       </c>
     </row>
     <row r="104" ht="232" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S3-02</t>
+          <t>S3-06</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8674,43 +9086,38 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Скобляков</t>
+          <t>Петров</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Алексей</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Викторович</t>
+          <t>Григорий</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>МИФИ</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>dinAlt220@yandex.ru</t>
+          <t>grigoriy.6.petrov@gmail.com</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>Виртуальный генератор потока АТМОСФЕРНЫХ мюонов В варьируемом диапазоне энергий до 100 ТэВ</t>
+          <t>Development of machine learning tool for photon identification using the electromagnetic calorimeter at SPD detector</t>
         </is>
       </c>
     </row>
     <row r="105" ht="319" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S3-03</t>
+          <t>S3-07</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8719,43 +9126,43 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Канцырев</t>
+          <t>Мальцев</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Николай</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Викторович</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>kantsyrev@itep.ru</t>
+          <t>n.maltsev@spbu.ru</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>Мюонная томография крупномасштабных объектов с применением компактных цилиндрических позиционно-чувствительных детекторов</t>
+          <t>Особенности изучения свойств пучков тяжёлых ионов высоких энергий</t>
         </is>
       </c>
     </row>
     <row r="106" ht="333.5" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S3-04</t>
+          <t>S3-08</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8764,38 +9171,43 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Лашин</t>
+          <t>Семенов</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Константин</t>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>ВНИИЭФ</t>
+          <t>НИЦ КИ</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>kosty2112@gmail.com</t>
+          <t>kindr_cool@mail.ru</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>Реконструкция плотности многокомпонентных объектов в протонной радиографии с использованием метода роя частиц и преобразования Абеля</t>
+          <t>Критический стенд «П»: современное состояние, особенности и роль исследований для развития технологии ВВЭР</t>
         </is>
       </c>
     </row>
     <row r="107" ht="145" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S3-05</t>
+          <t>S3-09</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8804,43 +9216,38 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Олейников</t>
+          <t>Бурякова</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Владислав</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Петрович</t>
+          <t>Елена</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ИЯФ Новосиб</t>
+          <t>ВНИИЭф</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>V.P.Oleynikov@inp.nsk.su</t>
+          <t>suyazova.elena@mail.ru</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>Измерение ионизационных выходов ядер отдачи в аргоне</t>
+          <t>Результаты экспериментов с тепловыми трубами с цезиевым теплоносителем</t>
         </is>
       </c>
     </row>
     <row r="108" ht="246.5" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S3-06</t>
+          <t>S3-10</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8849,38 +9256,43 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Петров</t>
+          <t>Розов</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>МИФИ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>grigoriy.6.petrov@gmail.com</t>
+          <t>rozovs@jinr.ru</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>Development of machine learning tool for photon identification using the electromagnetic calorimeter at SPD detector</t>
+          <t>Низкофоновый детектор нейтронов на основе гелия-3</t>
         </is>
       </c>
     </row>
     <row r="109" ht="145" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S3-07</t>
+          <t>S3-11</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8889,43 +9301,43 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Мальцев</t>
+          <t>Каретников</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Николай</t>
+          <t>Максим</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Донатович</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ВНИИА</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>n.maltsev@spbu.ru</t>
+          <t>mcsym01@gmail.com</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>Особенности изучения свойств пучков тяжёлых ионов высоких энергий</t>
+          <t>Нейтрон-нейтронные методы дистанционного контроля с использованием меченых нейтронов</t>
         </is>
       </c>
     </row>
     <row r="110" ht="275.5" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S3-08</t>
+          <t>S3-12</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8934,43 +9346,38 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Семенов</t>
+          <t>Данилкин</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Сергей</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Владимирович</t>
+          <t>Владислав</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>kindr_cool@mail.ru</t>
+          <t>donyvlad@gmail.com</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>Критический стенд «П»: современное состояние, особенности и роль исследований для развития технологии ВВЭР</t>
+          <t>Моделирование ионной оптики сепаратора STAR с помощью программы SHEMAT</t>
         </is>
       </c>
     </row>
     <row r="111" ht="188.5" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S3-09</t>
+          <t>S3-13</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8979,38 +9386,43 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Бурякова</t>
+          <t>Веденеев</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Вячеслав</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Юрьевич</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ВНИИЭф</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>suyazova.elena@mail.ru</t>
+          <t>vvedeneyev@gmail.com</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>Результаты экспериментов с тепловыми трубами с цезиевым теплоносителем</t>
+          <t>Криогенная газовая ячейка охлаждения ионов. Особенности конструкции, вакуумная система, система газового обеспечения, система охлаждения</t>
         </is>
       </c>
     </row>
     <row r="112" ht="116" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S3-10</t>
+          <t>S3-14</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9019,21 +9431,21 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Розов</t>
+          <t>Новоселов</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Сергеевич</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9043,19 +9455,19 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>rozovs@jinr.ru</t>
+          <t>noval@jinr.ru</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>Низкофоновый детектор нейтронов на основе гелия-3</t>
+          <t>Измерение времени экстракции ионов из криогенной газовой ячейки охлаждения</t>
         </is>
       </c>
     </row>
     <row r="113" ht="246.5" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S3-11</t>
+          <t>S3-15</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9064,43 +9476,38 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Каретников</t>
+          <t>Зимин</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Максим</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Донатович</t>
+          <t>Илья</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>ВНИИА</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>mcsym01@gmail.com</t>
+          <t>zimin@jinr.ru</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>Нейтрон-нейтронные методы дистанционного контроля с использованием меченых нейтронов</t>
+          <t>Нейтронные сцинтилляторы на основе кристалла ZnS(Ag)</t>
         </is>
       </c>
     </row>
     <row r="114" ht="188.5" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S3-12</t>
+          <t>S3-16</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9109,16 +9516,21 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Данилкин</t>
+          <t>Сидорова</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Владислав</t>
+          <t>Ольга</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Викторовна</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -9128,19 +9540,19 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>donyvlad@gmail.com</t>
+          <t>sidorova@jinr.ru</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>Моделирование ионной оптики сепаратора STAR с помощью программы SHEMAT</t>
+          <t>Физическая структура кросс-толка гамма-квантов в сферических многодетекторных сцинтилляционных системах</t>
         </is>
       </c>
     </row>
     <row r="115" ht="333.5" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S3-13</t>
+          <t>S3-17</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9149,43 +9561,38 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Веденеев</t>
+          <t>Strizhak</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Вячеслав</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Юрьевич</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ИЯИ</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>vvedeneyev@gmail.com</t>
+          <t>strizhak@inr.ru</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>Криогенная газовая ячейка охлаждения ионов. Особенности конструкции, вакуумная система, система газового обеспечения, система охлаждения</t>
+          <t>Performance and light yield of CsI(pure) scintillation module prototypes at LN2 temperature</t>
         </is>
       </c>
     </row>
     <row r="116" ht="203" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S3-14</t>
+          <t>S3-18</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9194,21 +9601,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Новоселов</t>
+          <t>Суслов</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Алексей</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Сергеевич</t>
+          <t>Иван</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -9218,19 +9620,19 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>noval@jinr.ru</t>
+          <t>ivsuslov@jinr.ru</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>Измерение времени экстракции ионов из криогенной газовой ячейки охлаждения</t>
+          <t>Пласстмассовые сцинтилляторы с возможностью разделения частиц по форме импульса</t>
         </is>
       </c>
     </row>
     <row r="117" ht="130.5" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S3-15</t>
+          <t>S3-19</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9239,16 +9641,21 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Зимин</t>
+          <t>Евсеев</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Илья</t>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -9258,19 +9665,19 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>zimin@jinr.ru</t>
+          <t>evseevsa@jinr.ru</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>Нейтронные сцинтилляторы на основе кристалла ZnS(Ag)</t>
+          <t>Исследование радиационной стойкости SiC- и Si-детекторов после облучения альфа-частицами</t>
         </is>
       </c>
     </row>
     <row r="118" ht="275.5" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S3-16</t>
+          <t>S3-20</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9279,43 +9686,43 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Сидорова</t>
+          <t>Смирнов</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ольга</t>
+          <t>Игорь</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Викторовна</t>
+          <t>Борисович</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ПИЯФ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>sidorova@jinr.ru</t>
+          <t>smirnov_ib@pnpi.nrcki.ru</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>Физическая структура кросс-толка гамма-квантов в сферических многодетекторных сцинтилляционных системах</t>
+          <t>Average Spatial Resolution of Detector Layers of Four-Layer Position-Sensitive Detectors</t>
         </is>
       </c>
     </row>
     <row r="119" ht="203" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S3-17</t>
+          <t>S3-21</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9324,38 +9731,43 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Strizhak</t>
+          <t>Стрекаловский</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Олег</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Викторович</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ИЯИ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>strizhak@inr.ru</t>
+          <t>stroleg1@yandex.ru</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>Performance and light yield of CsI(pure) scintillation module prototypes at LN2 temperature</t>
+          <t>Применение диджитайзеров CAEN-ХХ42 для регистрации заряженных частиц</t>
         </is>
       </c>
     </row>
     <row r="120" ht="203" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S3-18</t>
+          <t>S3-22</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9364,38 +9776,38 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Суслов</t>
+          <t>Шимко</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Павел</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>ivsuslov@jinr.ru</t>
+          <t>pashashimko0306@gmail.com</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>Пласстмассовые сцинтилляторы с возможностью разделения частиц по форме импульса</t>
+          <t>Исследование распределения поглощённой дозы в полимерных материалах при облучении ускоренными электронами</t>
         </is>
       </c>
     </row>
     <row r="121" ht="217.5" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S3-19</t>
+          <t>S3-23</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9404,43 +9816,38 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Евсеев</t>
+          <t>Цыганкова</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Сергей</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Александрович</t>
+          <t>Валерия</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>СВКНИИ ДВО</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>evseevsa@jinr.ru</t>
+          <t>tsigankova.valeriya@mail.ru</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>Исследование радиационной стойкости SiC- и Si-детекторов после облучения альфа-частицами</t>
+          <t>Влияние ²²²Rn на расчёт радиоуглеродного возраста древесных углей</t>
         </is>
       </c>
     </row>
     <row r="122" ht="188.5" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S3-20</t>
+          <t>S3-24</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9449,43 +9856,43 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Смирнов</t>
+          <t>Пухаева</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Нелли</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Ефимовна</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ПИЯФ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>smirnov_ib@pnpi.nrcki.ru</t>
+          <t>pukhaeva@jinr.ru</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>Average Spatial Resolution of Detector Layers of Four-Layer Position-Sensitive Detectors</t>
+          <t>Nd/ZnS-модифицированные квантовые точки CdZnSeS как нанокомпоненты сцинтилляционных сред для поиска безнейтринного двойного β-распада ¹⁵⁰Nd</t>
         </is>
       </c>
     </row>
     <row r="123" ht="174" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S3-21</t>
+          <t>S3-25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9494,21 +9901,21 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Стрекаловский</t>
+          <t>Пухаева</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Олег</t>
+          <t>Нелли</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Викторович</t>
+          <t>Ефимовна</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9518,19 +9925,19 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>stroleg1@yandex.ru</t>
+          <t>pukhaeva@jinr.ru</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>Применение диджитайзеров CAEN-ХХ42 для регистрации заряженных частиц</t>
+          <t>Results of ARFIM experiment setup for applied research of NOSU</t>
         </is>
       </c>
     </row>
     <row r="124" ht="261" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S3-22</t>
+          <t>S3-26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9539,38 +9946,43 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Шимко</t>
+          <t>Пухаева</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Павел</t>
+          <t>Нелли</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Ефимовна</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pashashimko0306@gmail.com</t>
+          <t>pukhaeva@jinr.ru</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>Исследование распределения поглощённой дозы в полимерных материалах при облучении ускоренными электронами</t>
+          <t>Neodymium-modified CdZnSeS/ZnS quantum dots: evolution of optical response and evidence limits for core/shell architecture</t>
         </is>
       </c>
     </row>
     <row r="125" ht="174" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S3-23</t>
+          <t>S3-27</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9579,61 +9991,61 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Цыганкова</t>
+          <t>Петровская</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Валерия</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>СВКНИИ ДВО</t>
+          <t>Анна</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Станиславовна</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>tsigankova.valeriya@mail.ru</t>
+          <t>anita3425@yandex.ru</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>Влияние ²²²Rn на расчёт радиоуглеродного возраста древесных углей</t>
+          <t>Перспективы применения сухой ионно-плазменной технологии дезактивации оборудования ЯЭУ из титановых сплавов</t>
         </is>
       </c>
     </row>
     <row r="126" ht="362.5" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S3-24</t>
+          <t>S4-01</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Пухаева</t>
+          <t>Бикметов</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Нелли</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ефимовна</t>
+          <t>Рафальевич</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9643,149 +10055,149 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pukhaeva@jinr.ru</t>
+          <t>bikmetov@jinr.ru</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>Nd/ZnS-модифицированные квантовые точки CdZnSeS как нанокомпоненты сцинтилляционных сред для поиска безнейтринного двойного β-распада ¹⁵⁰Nd</t>
+          <t>Investigation of nuclear deformation influence on anisotropic flows in heavy-ion collisions at NICA energies</t>
         </is>
       </c>
     </row>
     <row r="127" ht="145" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S3-25</t>
+          <t>S4-02</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Пухаева</t>
+          <t>Вечернин</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Нелли</t>
+          <t>Владимир</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ефимовна</t>
+          <t>Викторович</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>pukhaeva@jinr.ru</t>
+          <t>v.vechernin@spbu.ru</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>Results of ARFIM experiment setup for applied research of NOSU</t>
+          <t>Кумулятивные явления в области больших поперечных импульсов и их наблюдение в столкновениях ядер на коллайдере NICA</t>
         </is>
       </c>
     </row>
     <row r="128" ht="290" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S3-26</t>
+          <t>S4-03</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Пухаева</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Нелли</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Ефимовна</t>
+          <t>Shubham</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>pukhaeva@jinr.ru</t>
+          <t>s.sharma.hep@gmail.com</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>Neodymium-modified CdZnSeS/ZnS quantum dots: evolution of optical response and evidence limits for core/shell architecture</t>
+          <t>Inclusive J/ψ Production as a Probe of Gluon Dynamics at NICA</t>
         </is>
       </c>
     </row>
     <row r="129" ht="261" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S3-27</t>
+          <t>S4-04</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Петровская</t>
+          <t>Жаров</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Михаил</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Станиславовна</t>
+          <t>Андреевич</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>anita3425@yandex.ru</t>
+          <t>m.zharov@spbu.ru</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>Перспективы применения сухой ионно-плазменной технологии дезактивации оборудования ЯЭУ из титановых сплавов</t>
+          <t>Моделирование кумулятивных эффектов в столкновениях тяжелых ионов при энергиях коллайдера NICA</t>
         </is>
       </c>
     </row>
     <row r="130" ht="232" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S4-01</t>
+          <t>S4-05</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9794,43 +10206,43 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Бикметов</t>
+          <t>Идрисов</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Дим</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Рафальевич</t>
+          <t>Маратович</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>bikmetov@jinr.ru</t>
+          <t>idrisov.dim@mail.ru</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>Investigation of nuclear deformation influence on anisotropic flows in heavy-ion collisions at NICA energies</t>
+          <t>Методы определения центральности с использованием передних детекторов в эксперименте BM@N</t>
         </is>
       </c>
     </row>
     <row r="131" ht="275.5" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S4-02</t>
+          <t>S4-06</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9839,43 +10251,43 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Вечернин</t>
+          <t>Plotnikov</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Vasilii</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Викторович</t>
+          <t>Alexandrovich</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>v.vechernin@spbu.ru</t>
+          <t>vplotnikov@jinr.ru</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>Кумулятивные явления в области больших поперечных импульсов и их наблюдение в столкновениях ядер на коллайдере NICA</t>
+          <t>Λd сorrelation function in Xe+CsI collisions at 3.8 AGeV in the BM@N experiment</t>
         </is>
       </c>
     </row>
     <row r="132" ht="130.5" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S4-03</t>
+          <t>S4-07</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9884,38 +10296,43 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Зубанков</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Shubham</t>
+          <t>Александр</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>s.sharma.hep@gmail.com</t>
+          <t>zubankov@inr.ru</t>
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>Inclusive J/ψ Production as a Probe of Gluon Dynamics at NICA</t>
+          <t>Measurement of double differential inclusive cross sections of forward neutron emission in the BM@N experiment</t>
         </is>
       </c>
     </row>
     <row r="133" ht="246.5" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S4-04</t>
+          <t>S4-08</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9924,21 +10341,21 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Жаров</t>
+          <t>Андронов</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Евгений</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9948,19 +10365,19 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>m.zharov@spbu.ru</t>
+          <t>e.v.andronov@spbu.ru</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>Моделирование кумулятивных эффектов в столкновениях тяжелых ионов при энергиях коллайдера NICA</t>
+          <t>Influence of colour string configurations on rapidity multiplicity correlations</t>
         </is>
       </c>
     </row>
     <row r="134" ht="217.5" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S4-05</t>
+          <t>S4-10</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9968,44 +10385,46 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C134" t="n">
-        <v>5</v>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Идрисов</t>
+          <t>Герасименюк</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Дим</t>
+          <t>Николай</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Маратович</t>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ДВФУ</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>idrisov.dim@mail.ru</t>
+          <t>gerasimenyuk.nv@dvfu.ru</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>Методы определения центральности с использованием передних детекторов в эксперименте BM@N</t>
+          <t>Экранирование заряда в многокомпонентной аблелевой модели Хиггса</t>
         </is>
       </c>
     </row>
     <row r="135" ht="188.5" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S4-06</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10013,22 +10432,24 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C135" t="n">
-        <v>6</v>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Plotnikov</t>
+          <t>Зайцев</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Vasilii</t>
+          <t>Андрей</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Alexandrovich</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10038,19 +10459,19 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>vplotnikov@jinr.ru</t>
+          <t>zaicev@jinr.ru</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>Λd сorrelation function in Xe+CsI collisions at 3.8 AGeV in the BM@N experiment</t>
+          <t>Ядро ⁸Be и состояние Хойла в диссоциации релятивистских ядер</t>
         </is>
       </c>
     </row>
     <row r="136" ht="246.5" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S4-07</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10058,22 +10479,24 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C136" t="n">
-        <v>7</v>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Зубанков</t>
+          <t>Скородько</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Татьяна</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Юрьевна</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10083,19 +10506,19 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>zubankov@inr.ru</t>
+          <t>tatiskor@mail.ru</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>Measurement of double differential inclusive cross sections of forward neutron emission in the BM@N experiment</t>
+          <t>Dibaryon d*(2380) : prediction, detection, understanding</t>
         </is>
       </c>
     </row>
     <row r="137" ht="174" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S4-08</t>
+          <t>S4-14</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10103,44 +10526,46 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C137" t="n">
-        <v>8</v>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Андронов</t>
+          <t>Friesen</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Евгений</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Vadimovna</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>e.v.andronov@spbu.ru</t>
+          <t>avfriesen@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>Influence of colour string configurations on rapidity multiplicity correlations</t>
+          <t>Mass spectrum of noncharmed and charmed meson states at finite temperature in extended linear-sigma model</t>
         </is>
       </c>
     </row>
     <row r="138" ht="246.5" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S4-09</t>
+          <t>S4-15</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10149,16 +10574,21 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Бытьев</t>
+          <t>Авдеев</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Петрович</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10168,24 +10598,19 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>bvv@jinr.ru</t>
+          <t>avdeyev@jinr.ru</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>Эффективность и математические аналоги процедуры ИБП при вычислении интегралов Фейнмана</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>отменён</t>
+          <t>Source velocity in collisions of 2.1 GeV and 3.6 GeV protons with gold target.</t>
         </is>
       </c>
     </row>
     <row r="139" ht="174" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S4-10</t>
+          <t>S4-16</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10194,43 +10619,43 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Герасименюк</t>
+          <t>Иванищев</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Николай</t>
+          <t>Дмитрий</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>ДВФУ</t>
+          <t>НИЦ КИ-ПИЯФ</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>gerasimenyuk.nv@dvfu.ru</t>
+          <t>ivanishchev_da@pnpi.nrcki.ru</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>Экранирование заряда в многокомпонентной аблелевой модели Хиггса</t>
+          <t>Особенности измерения свойств резонансов в эксперименте MPD в Xe+W столкновениях при энергии 2,5 A*ГэВ</t>
         </is>
       </c>
     </row>
     <row r="140" ht="145" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>S4-17</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10239,43 +10664,43 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Зайцев</t>
+          <t>Силагадзе</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Зураб</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Карлоевич</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ИЯФ Новосиб</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>zaicev@jinr.ru</t>
+          <t>silagadze@inp.nsk.su</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>Ядро ⁸Be и состояние Хойла в диссоциации релятивистских ядер</t>
+          <t>Pauli equation in spaces of constant curvature and extended Nikiforov-Uvarov method</t>
         </is>
       </c>
     </row>
     <row r="141" ht="145" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>S4-18</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10284,43 +10709,43 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Скородько</t>
+          <t>Феофилов</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Татьяна</t>
+          <t>Григорий</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Юрьевна</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>tatiskor@mail.ru</t>
+          <t>g.feofilov@spbu.ru</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>Dibaryon d*(2380) : prediction, detection, understanding</t>
+          <t>Минимизация объемных флуктуаций при поиске критической точки сильно взаимодействующей материи в релятивистских ядерных столкновениях</t>
         </is>
       </c>
     </row>
     <row r="142" ht="174" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S4-13</t>
+          <t>S4-19</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10329,43 +10754,38 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Uzikov</t>
+          <t>Prokhorova</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Yuriy</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Nikolaevich</t>
+          <t>Daria</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>Tsinghua Univ., China</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>uzikov@jinr.ru</t>
+          <t>daria-prokhorova@mail.tsinghua.edu.cn</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>pN spin amplitudes and spin observables of the pd →pd and dd →n+p+d processes</t>
+          <t>Heavy-flavor jet quenching in pre-equilibrium medium</t>
         </is>
       </c>
     </row>
     <row r="143" ht="232" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S4-14</t>
+          <t>S4-20</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10374,21 +10794,21 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Friesen</t>
+          <t>Недорезов</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Егор</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vadimovna</t>
+          <t>Вячеславович</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10398,19 +10818,19 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>avfriesen@theor.jinr.ru</t>
+          <t>nedorezov@jinr.ru</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>Mass spectrum of noncharmed and charmed meson states at finite temperature in extended linear-sigma model</t>
+          <t>Overview of the STAR hot QCD results</t>
         </is>
       </c>
     </row>
     <row r="144" ht="159.5" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S4-15</t>
+          <t>S4-21</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10419,43 +10839,43 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Авдеев</t>
+          <t>Ануфриев</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Антон</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Петрович</t>
+          <t>Витальевич</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>avdeyev@jinr.ru</t>
+          <t>antonman200@yandex.ru</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>Source velocity in collisions of 2.1 GeV and 3.6 GeV protons with gold target.</t>
+          <t>Исследование выходов заряженных адронов в рамках гидродинамического моделирования с применением голографического уравнения состояния</t>
         </is>
       </c>
     </row>
     <row r="145" ht="246.5" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S4-16</t>
+          <t>S4-22</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -10464,16 +10884,16 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Иванищев</t>
+          <t>Галактионов</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Кирилл</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -10483,24 +10903,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>НИЦ КИ-ПИЯФ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>ivanishchev_da@pnpi.nrcki.ru</t>
+          <t>kirill.galaktionov@spbu.ru</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>Особенности измерения свойств резонансов в эксперименте MPD в Xe+W столкновениях при энергии 2,5 A*ГэВ</t>
+          <t>Исследование нейросетевых подходов к оценке прицельного параметра в столкновениях тяжелых ионов на основе 4π информации о событии</t>
         </is>
       </c>
     </row>
     <row r="146" ht="203" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S4-17</t>
+          <t>S4-23</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10509,43 +10929,43 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Силагадзе</t>
+          <t>Дьяченко</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Зураб</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Карлоевич</t>
+          <t>Трофимович</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>ИЯФ Новосиб</t>
+          <t>НИЦ КИ-ПИЯФ</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>silagadze@inp.nsk.su</t>
+          <t>dyachenko_a@mail.ru</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>Pauli equation in spaces of constant curvature and extended Nikiforov-Uvarov method</t>
+          <t>Неравновесный квантовый гидродинамический подход и эмиссия фрагментов в столкновениях тяжелых ионов промежуточных энергий</t>
         </is>
       </c>
     </row>
     <row r="147" ht="319" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S4-18</t>
+          <t>S4-24</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10554,21 +10974,21 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Феофилов</t>
+          <t>Белокурова</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Светлана</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Николаевна</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -10578,19 +10998,19 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>g.feofilov@spbu.ru</t>
+          <t>s.belokurova@spbu.ru</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>Минимизация объемных флуктуаций при поиске критической точки сильно взаимодействующей материи в релятивистских ядерных столкновениях</t>
+          <t>Применение классического глауберовского подхода к описанию дейтрон-дейтронного взаимодействия</t>
         </is>
       </c>
     </row>
     <row r="148" ht="130.5" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S4-19</t>
+          <t>S4-25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10599,38 +11019,43 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Prokhorova</t>
+          <t>Размыслов</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Daria</t>
+          <t>Константин</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tsinghua Univ., China</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>daria-prokhorova@mail.tsinghua.edu.cn</t>
+          <t>yoitz@yandex.ru</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>Heavy-flavor jet quenching in pre-equilibrium medium</t>
+          <t>О применении генераторов EPOS4, UrQMD, PHQMD и PYTHIA для анализа событий в физике сверхвысоких энергий</t>
         </is>
       </c>
     </row>
     <row r="149" ht="72.5" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S4-20</t>
+          <t>S4-26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10639,43 +11064,43 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Недорезов</t>
+          <t>Мягков</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Егор</t>
+          <t>Данила</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Вячеславович</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИИЯФ МГУ</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>nedorezov@jinr.ru</t>
+          <t>danila.myagkov.msu@mail.ru</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>Overview of the STAR hot QCD results</t>
+          <t>Моделирование влияния деформации ядер на азимутальную анизотропию частиц в генераторе событий HYDJET++</t>
         </is>
       </c>
     </row>
     <row r="150" ht="348" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S4-21</t>
+          <t>S4-27</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10684,43 +11109,38 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Ануфриев</t>
+          <t>Vasilieva</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Антон</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Витальевич</t>
+          <t>Anastasiia</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>МИФИ</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>antonman200@yandex.ru</t>
+          <t>anastasiyavasileva00@gmail.com</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>Исследование выходов заряженных адронов в рамках гидродинамического моделирования с применением голографического уравнения состояния</t>
+          <t>Analysis of charged and identified hadron spectra with Tsallis distributions in O+O, Kr+Kr, and Xe+Xe collisions at √sₙₙ = 6 GeV using the UrQMD model</t>
         </is>
       </c>
     </row>
     <row r="151" ht="319" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S4-22</t>
+          <t>S4-28</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10729,196 +11149,196 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Галактионов</t>
+          <t>Калугин</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Кирилл</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Константинович</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>КИ ИФВЭ</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>kirill.galaktionov@spbu.ru</t>
+          <t>Nikita.Kalugin@ihep.ru</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>Исследование нейросетевых подходов к оценке прицельного параметра в столкновениях тяжелых ионов на основе 4π информации о событии</t>
+          <t>Измерение выстроенности K*⁻(892)-мезонов, образованных в каон-ядерных и пион-ядерных взаимодействиях на ускорительном комплексе У-70</t>
         </is>
       </c>
     </row>
     <row r="152" ht="290" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S4-23</t>
+          <t>S5-01</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Дьяченко</t>
+          <t>Чернышев</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Борис</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Трофимович</t>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>НИЦ КИ-ПИЯФ</t>
+          <t>МИФИ</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>dyachenko_a@mail.ru</t>
+          <t>chernyshev@mephi.ru</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>Неравновесный квантовый гидродинамический подход и эмиссия фрагментов в столкновениях тяжелых ионов промежуточных энергий</t>
+          <t>Поиск тринейтрона в реакциях поглощения остановившихся пионов ядрами ⁹Be</t>
         </is>
       </c>
     </row>
     <row r="153" ht="246.5" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S4-24</t>
+          <t>S5-02</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Белокурова</t>
+          <t>Борзаков</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Светлана</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Борисович</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>s.belokurova@spbu.ru</t>
+          <t>sbor@nf.jinr.ru</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>Применение классического глауберовского подхода к описанию дейтрон-дейтронного взаимодействия</t>
+          <t>Возможное существование синглетного дейтрона как дибарионного резонанса и проблема существования динейтрона</t>
         </is>
       </c>
     </row>
     <row r="154" ht="261" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S4-25</t>
+          <t>S5-03</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Размыслов</t>
+          <t>Ефименко</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Константин</t>
+          <t>Мария</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Константиновна</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ТОГУ</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>yoitz@yandex.ru</t>
+          <t>ef.maria97@yandex.ru</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>О применении генераторов EPOS4, UrQMD, PHQMD и PYTHIA для анализа событий в физике сверхвысоких энергий</t>
+          <t>Excited states of ⁶He nucleus in the SS-HORSE–NCSM approach</t>
         </is>
       </c>
     </row>
     <row r="155" ht="261" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S4-26</t>
+          <t>S5-04</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Мягков</t>
+          <t>Зайцев</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Данила</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -10928,109 +11348,109 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>НИИЯФ МГУ</t>
+          <t>ТОГУ</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>danila.myagkov.msu@mail.ru</t>
+          <t>000282@togudv.ru</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>Моделирование влияния деформации ядер на азимутальную анизотропию частиц в генераторе событий HYDJET++</t>
+          <t>Ионизация атомов протонным ударом в представлении параболических квазиштурмовских функций</t>
         </is>
       </c>
     </row>
     <row r="156" ht="348" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S4-27</t>
+          <t>S5-05</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Vasilieva</t>
+          <t>Зайцев</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Anastasiia</t>
+          <t>Александр</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Сергеевич</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>МИФИ</t>
+          <t>ТОГУ</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>anastasiyavasileva00@gmail.com</t>
+          <t>alzaytsev@togudv.ru</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>Analysis of charged and identified hadron spectra with Tsallis distributions in O+O, Kr+Kr, and Xe+Xe collisions at √sₙₙ = 6 GeV using the UrQMD model</t>
+          <t>Атом водорода в поле лазерного импульса в представлении параболических волновых пакетов</t>
         </is>
       </c>
     </row>
     <row r="157" ht="304.5" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S4-28</t>
+          <t>S5-06</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Калугин</t>
+          <t>Шалапинин</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Никита</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Константинович</t>
+          <t>Денис</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>КИ ИФВЭ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Nikita.Kalugin@ihep.ru</t>
+          <t>shalapinin@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>Измерение выстроенности K*⁻(892)-мезонов, образованных в каон-ядерных и пион-ядерных взаимодействиях на ускорительном комплексе У-70</t>
+          <t>Van der Waals dimers of neon</t>
         </is>
       </c>
     </row>
     <row r="158" ht="188.5" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S5-01</t>
+          <t>S5-07</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11039,43 +11459,43 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Чернышев</t>
+          <t>Рубцова</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Борис</t>
+          <t>Ольга</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Андреевна</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>МИФИ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>chernyshev@mephi.ru</t>
+          <t>rubtsova-olga@yandex.ru</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>Поиск тринейтрона в реакциях поглощения остановившихся пионов ядрами ⁹Be</t>
+          <t>Finding virtual states via wave-packet continuum discretization</t>
         </is>
       </c>
     </row>
     <row r="159" ht="261" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S5-02</t>
+          <t>S5-08</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11084,21 +11504,21 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Борзаков</t>
+          <t>Мотовилов</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Константинович</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11108,19 +11528,19 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>sbor@nf.jinr.ru</t>
+          <t>motovilv@gmail.com</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>Возможное существование синглетного дейтрона как дибарионного резонанса и проблема существования динейтрона</t>
+          <t>Resonances of a two-particle system on a 1D lattice</t>
         </is>
       </c>
     </row>
     <row r="160" ht="130.5" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S5-03</t>
+          <t>S5-09</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11129,151 +11549,156 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Ефименко</t>
+          <t>Яковлев</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Мария</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Константиновна</t>
+          <t>Леонидович</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>ТОГУ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>ef.maria97@yandex.ru</t>
+          <t>s.yakovlev@spbu.ru</t>
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>Excited states of ⁶He nucleus in the SS-HORSE–NCSM approach</t>
+          <t>3-3 рассеяние в системах трёх частиц с короткодействующими и кулоновскими взаимодействиями</t>
         </is>
       </c>
     </row>
     <row r="161" ht="246.5" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S5-04</t>
+          <t>S6-01</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Зайцев</t>
+          <t>Дербин</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>ТОГУ</t>
+          <t>ПИЯФ</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>000282@togudv.ru</t>
+          <t>derbin_av@pnpi.nrcki.ru</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>Ионизация атомов протонным ударом в представлении параболических квазиштурмовских функций</t>
+          <t>Поиск тяжелого стерильного нейтрино в бета-распаде ¹⁴⁴Pr</t>
         </is>
       </c>
     </row>
     <row r="162" ht="232" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S5-05</t>
+          <t>S6-02</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Зайцев</t>
+          <t>Кондратьев</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Владимир</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Сергеевич</t>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>ТОГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>alzaytsev@togudv.ru</t>
+          <t>vkondrat@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>Атом водорода в поле лазерного импульса в представлении параболических волновых пакетов</t>
+          <t>Эффекты динамо и осцилляций в спектрах нейтрино сверхновых</t>
         </is>
       </c>
     </row>
     <row r="163" ht="58" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S5-06</t>
+          <t>S6-03</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Шалапинин</t>
+          <t>Кондратьев</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Денис</t>
+          <t>Владимир</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -11283,154 +11708,149 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>shalapinin@theor.jinr.ru</t>
+          <t>vkondrat@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>Van der Waals dimers of neon</t>
+          <t>Эффекты намагниченности ядер во взрывном нуклеосинтезе</t>
         </is>
       </c>
     </row>
     <row r="164" ht="130.5" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S5-07</t>
+          <t>S6-04</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Рубцова</t>
+          <t>Лубашевский</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Ольга</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Андреевна</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>rubtsova-olga@yandex.ru</t>
+          <t>lubashev@jinr.ru</t>
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>Finding virtual states via wave-packet continuum discretization</t>
+          <t>Search for rare processes within the νGeN experiment at Kalinin nuclear power plant</t>
         </is>
       </c>
     </row>
     <row r="165" ht="101.5" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S5-08</t>
+          <t>S6-05</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Мотовилов</t>
+          <t>Громов</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Максим</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Константинович</t>
+          <t>Борисович</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>motovilv@gmail.com</t>
+          <t>gromov@physics.msu.ru</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>Resonances of a two-particle system on a 1D lattice</t>
+          <t>Precise reactor antineutrino spectrum measurement with TAO detector</t>
         </is>
       </c>
     </row>
     <row r="166" ht="217.5" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S5-09</t>
+          <t>S6-06</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Яковлев</t>
+          <t>Михеев</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Семён</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Леонидович</t>
+          <t>Алексеевич</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>s.yakovlev@spbu.ru</t>
+          <t>semenmihey@gmail.com</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>3-3 рассеяние в системах трёх частиц с короткодействующими и кулоновскими взаимодействиями</t>
+          <t>Условия появления Λ-гиперонов в материи нейтронных звёзд в моделях среднего поля</t>
         </is>
       </c>
     </row>
     <row r="167" ht="145" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S6-01</t>
+          <t>S6-07</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11439,43 +11859,38 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Дербин</t>
+          <t>Kabir</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Александр</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Владимирович</t>
+          <t>Abdul</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>ПИЯФ</t>
+          <t>Пакистан</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>derbin_av@pnpi.nrcki.ru</t>
+          <t>kabirkhanak1@gmail.com</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>Поиск тяжелого стерильного нейтрино в бета-распаде ¹⁴⁴Pr</t>
+          <t>Analysis of radiative capture of proton ¹¹B (p, γ) ¹²C at low energy</t>
         </is>
       </c>
     </row>
     <row r="168" ht="174" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S6-02</t>
+          <t>S6-08</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11484,21 +11899,16 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Кондратьев</t>
+          <t>Le</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Владимир</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Николаевич</t>
+          <t>Huy Viet</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -11508,77 +11918,72 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>vkondrat@theor.jinr.ru</t>
+          <t>leviethuy1@duytan.edu.vn</t>
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>Эффекты динамо и осцилляций в спектрах нейтрино сверхновых</t>
+          <t>Characterization of the cosmic muon background in the νGeN experiment</t>
         </is>
       </c>
     </row>
     <row r="169" ht="145" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S6-03</t>
+          <t>S7-01</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Кондратьев</t>
+          <t>Киселев</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Василий</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Николаевич</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>ОИЯИ</t>
+          <t>Алексеевич</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>vkondrat@theor.jinr.ru</t>
+          <t>kiselevva@fnkcrio.ru</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>Эффекты намагниченности ядер во взрывном нуклеосинтезе</t>
+          <t>Подход к оптимизации распределения поглощенной дозы в биологическом объекте в лучевой терапии пучком ускоренных протонов</t>
         </is>
       </c>
     </row>
     <row r="170" ht="188.5" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S6-04</t>
+          <t>S7-02</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Лубашевский</t>
+          <t>Щербаков</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -11586,196 +11991,211 @@
           <t>Алексей</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Александрович</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>lubashev@jinr.ru</t>
+          <t>sherbakov.aa15@physics.msu.ru</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>Search for rare processes within the νGeN experiment at Kalinin nuclear power plant</t>
+          <t>Оценка рисков развития радиационно-индуцированных заболеваний при проведении лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="171" ht="159.5" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S6-05</t>
+          <t>S7-03</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Громов</t>
+          <t>Васильева</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Алина</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Геннадиевна</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>НИЦ КИ ИФВЭ</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>gromov@physics.msu.ru</t>
+          <t>vasilyeva-ag@ihep.ru</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>Precise reactor antineutrino spectrum measurement with TAO detector</t>
+          <t>Измерение сечения реакции ¹²C(¹²C,X)¹¹C: особенности эксперимента и оценка неопределенностей</t>
         </is>
       </c>
     </row>
     <row r="172" ht="203" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S6-06</t>
+          <t>S7-04</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Михеев</t>
+          <t>Парменова</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Семён</t>
+          <t>Екатерина</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Алексеевич</t>
+          <t>Владимировна</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>НИЦ КИ ИФВЭ</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>semenmihey@gmail.com</t>
+          <t>Ekaterina.Parmenova@ihep.ru</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>Условия появления Λ-гиперонов в материи нейтронных звёзд в моделях среднего поля</t>
+          <t>Реализация работы с данными КТ в системе планирования ионной лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="173" ht="159.5" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S6-07</t>
+          <t>S7-05</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Петров</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Abdul</t>
+          <t>Виталий</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Валерьевич</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Пакистан</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>kabirkhanak1@gmail.com</t>
+          <t>vitalii17@bk.ru</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>Analysis of radiative capture of proton ¹¹B (p, γ) ¹²C at low energy</t>
+          <t>Трекинг, измерение энергии и получение диагностических изображений с использованием кремниевых пиксельных сенсоров</t>
         </is>
       </c>
     </row>
     <row r="174" ht="159.5" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S6-08</t>
+          <t>S7-06</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Le</t>
+          <t>Мерзликин</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Huy Viet</t>
+          <t>Григорий</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Васильевич</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>leviethuy1@duytan.edu.vn</t>
+          <t>grishamerzlikin@gmail.com</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>Characterization of the cosmic muon background in the νGeN experiment</t>
+          <t>Реконструкция трёхмерного дозового рапсределения при облучении биологических объектов пучками протонов высокой интенсивности</t>
         </is>
       </c>
     </row>
     <row r="175" ht="290" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S7-01</t>
+          <t>S7-07</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11784,38 +12204,43 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Киселев</t>
+          <t>Яковлев</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Василий</t>
+          <t>Иван</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Алексеевич</t>
+          <t>Андреевич</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>kiselevva@fnkcrio.ru</t>
+          <t>iv.a.yakovlev@gmail.com</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>Подход к оптимизации распределения поглощенной дозы в биологическом объекте в лучевой терапии пучком ускоренных протонов</t>
+          <t>Расчет характеристик черенковского детектора для контроля пучков протонов, используемых для флэш-терапии</t>
         </is>
       </c>
     </row>
     <row r="176" ht="232" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S7-02</t>
+          <t>S7-08</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11824,43 +12249,43 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Щербаков</t>
+          <t>Зябченков</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Владислав</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Олегович</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>sherbakov.aa15@physics.msu.ru</t>
+          <t>vladislavzyabchenkov@mail.ru</t>
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>Оценка рисков развития радиационно-индуцированных заболеваний при проведении лучевой терапии</t>
+          <t>Количественная оценка содержания тория и урана в свинце для радиационной защиты методом ИСП-МС</t>
         </is>
       </c>
     </row>
     <row r="177" ht="217.5" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S7-03</t>
+          <t>S7-09</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11869,43 +12294,43 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Васильева</t>
+          <t>Копылова</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Алина</t>
+          <t>Екатерина</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Геннадиевна</t>
+          <t>Александровна</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>НИЦ КИ ИФВЭ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>vasilyeva-ag@ihep.ru</t>
+          <t>ekaterinakalip@gmail.com</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>Измерение сечения реакции ¹²C(¹²C,X)¹¹C: особенности эксперимента и оценка неопределенностей</t>
+          <t>Применение деформируемой регистрации изображений в лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="178" ht="174" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S7-04</t>
+          <t>S7-10</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11914,43 +12339,38 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Парменова</t>
+          <t>Мамаева</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Екатерина</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Владимировна</t>
+          <t>Саргылана</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>НИЦ КИ ИФВЭ</t>
+          <t>СФВУ (Якутия)</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Ekaterina.Parmenova@ihep.ru</t>
+          <t>sargylana_mamaeva@mail.ru</t>
         </is>
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>Реализация работы с данными КТ в системе планирования ионной лучевой терапии</t>
+          <t>Биофизическая модель электрических характеристик эритроцитов при лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="179" ht="319" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S7-05</t>
+          <t>S7-11</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11959,43 +12379,43 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Петров</t>
+          <t>Мерзликин</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Виталий</t>
+          <t>Григорий</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Валерьевич</t>
+          <t>Васильевич</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>vitalii17@bk.ru</t>
+          <t>grishamerzlikin@gmail.com</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>Трекинг, измерение энергии и получение диагностических изображений с использованием кремниевых пиксельных сенсоров</t>
+          <t>Корректировка и валидация алгоритма оценки прбега протонов в различных матералах на основании КТ-исследований</t>
         </is>
       </c>
     </row>
     <row r="180" ht="319" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S7-06</t>
+          <t>S7-12</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12004,43 +12424,43 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Мерзликин</t>
+          <t>Ашрапов</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Улугбек</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Товфикович</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>INR Uzbekistan</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>grishamerzlikin@gmail.com</t>
+          <t>ashrapov@inp.uz</t>
         </is>
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>Реконструкция трёхмерного дозового рапсределения при облучении биологических объектов пучками протонов высокой интенсивности</t>
+          <t>Использование гамма-облученного оксида алюминия для изготовления генераторов технеция-99М</t>
         </is>
       </c>
     </row>
     <row r="181" ht="232" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S7-07</t>
+          <t>S7-13</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12049,43 +12469,38 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Яковлев</t>
+          <t>Кузьменков</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Антон</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Андреевич</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>ИЯИ РАН</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>iv.a.yakovlev@gmail.com</t>
+          <t>zhelton@yandex.ru</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>Расчет характеристик черенковского детектора для контроля пучков протонов, используемых для флэш-терапии</t>
+          <t>Фотоядерное получение медицинских изотопов рения на осмиевых и иридиевых мишенях</t>
         </is>
       </c>
     </row>
     <row r="182" ht="217.5" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>S7-08</t>
+          <t>S7-14</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12094,43 +12509,38 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Зябченков</t>
+          <t>Yusupov</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Владислав</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Олегович</t>
+          <t>Mirjalol</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>vladislavzyabchenkov@mail.ru</t>
+          <t>ymirjalol@bk.ru</t>
         </is>
       </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>Количественная оценка содержания тория и урана в свинце для радиационной защиты методом ИСП-МС</t>
+          <t>Ядерные реакции на кислороде, углероде, азоте и боре при облучении протонным пучком 160 МэВ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="159.5" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>S7-09</t>
+          <t>S7-15</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12139,43 +12549,43 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Копылова</t>
+          <t>Пятаев</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Екатерина</t>
+          <t>Дмитрий</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Александровна</t>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>МКНЦ, МГУ</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>ekaterinakalip@gmail.com</t>
+          <t>pataevdima2@gmail.com</t>
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>Применение деформируемой регистрации изображений в лучевой терапии</t>
+          <t>Исследование влияния термопластических масок на поверхностную дозу и дозовое распределение в лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="184" ht="174" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>S7-10</t>
+          <t>S7-16</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12184,38 +12594,43 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Мамаева</t>
+          <t>Оганян</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Саргылана</t>
+          <t>Ваге</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Робертович</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>СФВУ (Якутия)</t>
+          <t>МИФИ, МКНЦ</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>sargylana_mamaeva@mail.ru</t>
+          <t>vahe.ohanyan2000@yandex.ru</t>
         </is>
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>Биофизическая модель электрических характеристик эритроцитов при лучевой терапии</t>
+          <t>Биофизическое моделирование распределения температуры при гипертермии: обзор алгоритмов и проектирование расчётного модуля.</t>
         </is>
       </c>
     </row>
     <row r="185" ht="275.5" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>S7-11</t>
+          <t>S7-17</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12224,43 +12639,43 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Мерзликин</t>
+          <t>Онищук</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Елена</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Александровна</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ИАЭ Обнинск</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>grishamerzlikin@gmail.com</t>
+          <t>elenaonischuk@yandex.ru</t>
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>Корректировка и валидация алгоритма оценки прбега протонов в различных матералах на основании КТ-исследований</t>
+          <t>Optimization of photoneutron source parameters for boron neutron capture therapy</t>
         </is>
       </c>
     </row>
     <row r="186" ht="203" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>S7-12</t>
+          <t>S7-18</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12269,43 +12684,43 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Ашрапов</t>
+          <t>Балачков</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Улугбек</t>
+          <t>Максим</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Товфикович</t>
+          <t>Михайлович</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>INR Uzbekistan</t>
+          <t>ТПУ (Томск)</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>ashrapov@inp.uz</t>
+          <t>mmb2@tpu.ru</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>Использование гамма-облученного оксида алюминия для изготовления генераторов технеция-99М</t>
+          <t>Спектральные измерения пучка быстрых нейтронов циклотрона У-120</t>
         </is>
       </c>
     </row>
     <row r="187" ht="217.5" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>S7-13</t>
+          <t>S7-19</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12314,38 +12729,43 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Кузьменков</t>
+          <t>Сабуров</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Антон</t>
+          <t>Вячеслав</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Олегович</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>РМНЦ им. Цыба</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>zhelton@yandex.ru</t>
+          <t>vosaburov@gmail.com</t>
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>Фотоядерное получение медицинских изотопов рения на осмиевых и иридиевых мишенях</t>
+          <t>Статус проекта по созданию комплекса нейтронной терапии на базе компактного нейтронного генератора НГ-24МТ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="232" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>S7-14</t>
+          <t>S7-20</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12354,38 +12774,43 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Yusupov</t>
+          <t>Соловьев</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Mirjalol</t>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>РМНЦ им. Цыба</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>ymirjalol@bk.ru</t>
+          <t>salonf@mrrc.obninsk.ru</t>
         </is>
       </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>Ядерные реакции на кислороде, углероде, азоте и боре при облучении протонным пучком 160 МэВ</t>
+          <t>Особенности вычислительного прогнозирования отклика ионизационных камер для радиотерапевтического применения</t>
         </is>
       </c>
     </row>
     <row r="189" ht="246.5" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>S7-15</t>
+          <t>S7-21</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12394,43 +12819,43 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Пятаев</t>
+          <t>Хуцистова</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Алана</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Отариевна</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>МКНЦ, МГУ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>pataevdima2@gmail.com</t>
+          <t>www.alanakhutS1@mail.ru</t>
         </is>
       </c>
       <c r="I189" s="4" t="inlineStr">
         <is>
-          <t>Исследование влияния термопластических масок на поверхностную дозу и дозовое распределение в лучевой терапии</t>
+          <t>Моделирование комбинированного воздействия ионизирующего излучения и озона для стерилизации биоматериалов</t>
         </is>
       </c>
     </row>
     <row r="190" ht="304.5" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>S7-16</t>
+          <t>S7-22</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12439,43 +12864,43 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Оганян</t>
+          <t>Запорожская</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Ваге</t>
+          <t>Ксения</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Робертович</t>
+          <t>Васильевна</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>МИФИ, МКНЦ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>vahe.ohanyan2000@yandex.ru</t>
+          <t>zaporozhskayakv@my.msu.ru</t>
         </is>
       </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
-          <t>Биофизическое моделирование распределения температуры при гипертермии: обзор алгоритмов и проектирование расчётного модуля.</t>
+          <t>Применение шумоподавляющих фильтров при плёночной дозиметрии радиохирургических планов лечения</t>
         </is>
       </c>
     </row>
     <row r="191" ht="159.5" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>S7-17</t>
+          <t>S7-23</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12484,43 +12909,43 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Онищук</t>
+          <t>Новикова</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Евгения</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Александровна</t>
+          <t>Антоновна</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>ИАЭ Обнинск</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>elenaonischuk@yandex.ru</t>
+          <t>evgeniyanovikovazar@gmail.com</t>
         </is>
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t>Optimization of photoneutron source parameters for boron neutron capture therapy</t>
+          <t>Методика дозиметрии источника для электронной поверхностной брахитерапии</t>
         </is>
       </c>
     </row>
     <row r="192" ht="174" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>S7-18</t>
+          <t>S7-24</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12529,309 +12954,45 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Балачков</t>
+          <t>Петрова</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Кристина</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Михайлович</t>
+          <t>Алексеевна</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>ТПУ (Томск)</t>
+          <t>СФВУ (Якутия)</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>mmb2@tpu.ru</t>
+          <t>kristinan_1604@mail.ru</t>
         </is>
       </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
-          <t>Спектральные измерения пучка быстрых нейтронов циклотрона У-120</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="261" customHeight="1">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>S7-19</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>19</v>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Сабуров</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Вячеслав</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Олегович</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>РМНЦ им. Цыба</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>vosaburov@gmail.com</t>
-        </is>
-      </c>
-      <c r="I193" s="4" t="inlineStr">
-        <is>
-          <t>Статус проекта по созданию комплекса нейтронной терапии на базе компактного нейтронного генератора НГ-24МТ</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="261" customHeight="1">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>S7-20</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
-        <v>20</v>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Соловьев</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Алексей</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>Николаевич</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>РМНЦ им. Цыба</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>salonf@mrrc.obninsk.ru</t>
-        </is>
-      </c>
-      <c r="I194" s="4" t="inlineStr">
-        <is>
-          <t>Особенности вычислительного прогнозирования отклика ионизационных камер для радиотерапевтического применения</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="290" customHeight="1">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>S7-21</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C195" t="n">
-        <v>21</v>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Хуцистова</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Алана</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Отариевна</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>МГУ</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>www.alanakhutS1@mail.ru</t>
-        </is>
-      </c>
-      <c r="I195" s="4" t="inlineStr">
-        <is>
-          <t>Моделирование комбинированного воздействия ионизирующего излучения и озона для стерилизации биоматериалов</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="232" customHeight="1">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>S7-22</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
-        <v>22</v>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Запорожская</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Ксения</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Васильевна</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>МГУ</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>zaporozhskayakv@my.msu.ru</t>
-        </is>
-      </c>
-      <c r="I196" s="4" t="inlineStr">
-        <is>
-          <t>Применение шумоподавляющих фильтров при плёночной дозиметрии радиохирургических планов лечения</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="174" customHeight="1">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>S7-23</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C197" t="n">
-        <v>23</v>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Новикова</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Евгения</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Антоновна</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>МГУ</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>evgeniyanovikovazar@gmail.com</t>
-        </is>
-      </c>
-      <c r="I197" s="4" t="inlineStr">
-        <is>
-          <t>Методика дозиметрии источника для электронной поверхностной брахитерапии</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="246.5" customHeight="1">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>S7-24</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>24</v>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Петрова</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Кристина</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Алексеевна</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>СФВУ (Якутия)</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>kristinan_1604@mail.ru</t>
-        </is>
-      </c>
-      <c r="I198" s="4" t="inlineStr">
-        <is>
           <t>Накопление золошлаковых отходов и выбросов котельного комплекса и рост онкологической заболеваемости</t>
         </is>
       </c>
     </row>
+    <row r="193" ht="261" customHeight="1"/>
+    <row r="194" ht="261" customHeight="1"/>
+    <row r="195" ht="290" customHeight="1"/>
+    <row r="196" ht="232" customHeight="1"/>
+    <row r="197" ht="174" customHeight="1"/>
+    <row r="198" ht="246.5" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="J2:J499" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -13378,16 +13539,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>отменён</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Соавтор/пометка в исходнике: Гаганов</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="174" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -13600,11 +13751,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>отменён</t>
-        </is>
-      </c>
     </row>
     <row r="21" ht="145" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -13674,16 +13820,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>отменён</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Соавтор/пометка в исходнике: Залозная</t>
-        </is>
-      </c>
     </row>
     <row r="23" ht="203" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -13780,11 +13916,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>отменён</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="290" customHeight="1">
       <c r="A26" t="inlineStr">
@@ -13822,11 +13953,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>отменён</t>
-        </is>
-      </c>
     </row>
     <row r="27" ht="174" customHeight="1">
       <c r="A27" t="inlineStr">
@@ -13864,11 +13990,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>отменён</t>
-        </is>
-      </c>
     </row>
     <row r="28" ht="87" customHeight="1">
       <c r="A28" t="inlineStr">
@@ -14614,11 +14735,6 @@
       <c r="H48" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>отменён</t>
         </is>
       </c>
     </row>
@@ -14638,7 +14754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14663,30 +14779,45 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>46272.81944444445</v>
+      <c r="A2" s="8" t="n">
+        <v>46279.71037037037</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Опубликована предварительная программа.</t>
+          <t>Обновление по программе 14.09: комнаты секций 1–2, читальный зал библиотеки, регистрация в вестибюле, постеры в холле 2 этажа (восстановлены в программе), председатели пленарных заседаний, правки списков докладов.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Preliminary programme published.</t>
+          <t>Update from the 14.09 programme: sections 1–2 rooms, library reading hall, registration in the central lobby, posters in the 2nd-floor hallway (restored), plenary session chairs, talk-list edits.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
+        <v>46272.81944444445</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Опубликована предварительная программа.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Preliminary programme published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
         <v>46276.86666666667</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Указаны аудитории. Не приедут (доклады отменены): Варламов, Мардыбан, Безбах А. Н., Данилов, Каманин, Бытьев; постеры Долгополов, Торилов, Дормидонов, Землин, Комарова, Кострыгина, Ibraimova.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Rooms added. Cancelled (will not attend): Varlamov, Mardyban, Bezbakh A. N., Danilov, Kamanin, Bytiev; posters Dolgopolov, Torilov, Dormidonov, Zemlin, Komarova, Kostrygina, Ibraimova.</t>
         </is>

--- a/data/programme.xlsx
+++ b/data/programme.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="HH:MM"/>
     <numFmt numFmtId="168" formatCode="YYYY-MM-DD HH:MM"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +41,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +56,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -81,6 +90,9 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4339,7 +4351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O192"/>
+  <dimension ref="A1:S192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4354,6 +4366,10 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="13"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4432,6 +4448,26 @@
           <t>Примечание (EN)</t>
         </is>
       </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>Сайт</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>Логотип</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>Спонсор (RU)</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>Спонсор (EN)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="43.5" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -4812,6 +4848,26 @@
       <c r="J9" t="n">
         <v>15</v>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://gammatech.pro/</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>gammatech.png</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Гамматек</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Gammatech</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="174" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -4857,6 +4913,26 @@
       <c r="J10" t="n">
         <v>15</v>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://edigitizer.ru/</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>digitizer.svg</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Диджитайзер</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Digitizer</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="72.5" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -4896,6 +4972,26 @@
       </c>
       <c r="J11" t="n">
         <v>15</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://spegroup.ru/</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>spegroup.svg</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Научное оборудование</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Scientific Equipment</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="261" customHeight="1">

--- a/data/programme.xlsx
+++ b/data/programme.xlsx
@@ -20,12 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
     <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy\ hh:mm"/>
     <numFmt numFmtId="167" formatCode="HH:MM"/>
     <numFmt numFmtId="168" formatCode="YYYY-MM-DD HH:MM"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -76,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -93,6 +94,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2564,6 +2566,11 @@
           <t>Concert</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>235ц</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -3497,6 +3504,11 @@
           <t>Boat excursion on the Amur River</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>причал</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -3521,6 +3533,11 @@
       <c r="F63" t="inlineStr">
         <is>
           <t>Conference dinner</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>интурист</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4528,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" ht="29" customHeight="1">
@@ -4556,7 +4573,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" ht="116" customHeight="1">
@@ -14850,7 +14867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14919,6 +14936,21 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
+        <v>46280.72569444445</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Юбилейные доклады — 30 мин. Концерт в актовом зале. Экскурсия — 4-й причал; банкет — ресторан «Интурист».</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Anniversary talks are 30 min. Concert in the Assembly Hall. Excursion: Pier 4; conference dinner: Restaurant Inturist.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/programme.xlsx
+++ b/data/programme.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11220" yWindow="3910" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,13 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
     <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy\ hh:mm"/>
-    <numFmt numFmtId="167" formatCode="HH:MM"/>
-    <numFmt numFmtId="168" formatCode="YYYY-MM-DD HH:MM"/>
-    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -43,8 +42,10 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -61,7 +62,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -89,12 +90,10 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,7 +460,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="3"/>
@@ -694,7 +693,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="3"/>
@@ -1019,7 +1018,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M84"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="3"/>
@@ -1029,7 +1028,6 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="11"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2305,7 +2303,7 @@
       <c r="B31" s="3" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="C31" s="3" t="n">
         <v>0.6458333333333334</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -2486,7 +2484,7 @@
       <c r="B37" s="3" t="n">
         <v>0.6770833333333334</v>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="C37" s="3" t="n">
         <v>0.7291666666666666</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -2968,7 +2966,7 @@
       <c r="B49" s="3" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C49" s="6" t="n">
+      <c r="C49" s="3" t="n">
         <v>0.65625</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -3906,7 +3904,7 @@
       <c r="B72" s="3" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="C72" s="6" t="n">
+      <c r="C72" s="3" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -4369,7 +4367,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:S192"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -4379,14 +4377,13 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="37.140625" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="13"/>
     <col width="28" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="18" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4465,22 +4462,22 @@
           <t>Примечание (EN)</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="Q1" s="9" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>Логотип</t>
         </is>
       </c>
-      <c r="R1" s="9" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>Спонсор (RU)</t>
         </is>
       </c>
-      <c r="S1" s="9" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>Спонсор (EN)</t>
         </is>
@@ -4531,7 +4528,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" ht="29" customHeight="1">
+    <row r="3" ht="29.1" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>P-J2</t>
@@ -4576,7 +4573,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" ht="116" customHeight="1">
+    <row r="4" ht="116.1" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>P-01</t>
@@ -4721,7 +4718,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="290" customHeight="1">
+    <row r="7" ht="290.1" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>P-04</t>
@@ -4771,7 +4768,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="232" customHeight="1">
+    <row r="8" ht="231.95" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>P-05</t>
@@ -4951,7 +4948,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="72.5" customHeight="1">
+    <row r="11" ht="72.59999999999999" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>P-S3</t>
@@ -5061,7 +5058,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="145" customHeight="1">
+    <row r="13" ht="144.95" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>P-07</t>
@@ -5111,7 +5108,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="145" customHeight="1">
+    <row r="14" ht="144.95" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>P-08</t>
@@ -5161,7 +5158,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="203" customHeight="1">
+    <row r="15" ht="203.1" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>P-09</t>
@@ -5211,7 +5208,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="203" customHeight="1">
+    <row r="16" ht="203.1" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>P-10</t>
@@ -5361,7 +5358,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="232" customHeight="1">
+    <row r="19" ht="231.95" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
           <t>P-13</t>
@@ -5461,7 +5458,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="203" customHeight="1">
+    <row r="21" ht="203.1" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
           <t>P-15</t>
@@ -5511,7 +5508,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="145" customHeight="1">
+    <row r="22" ht="144.95" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>P-16</t>
@@ -5561,7 +5558,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="101.5" customHeight="1">
+    <row r="23" ht="101.45" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>P-17</t>
@@ -5761,7 +5758,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="145" customHeight="1">
+    <row r="27" ht="144.95" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
           <t>P-21</t>
@@ -5811,7 +5808,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="290" customHeight="1">
+    <row r="28" ht="290.1" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>P-22</t>
@@ -5861,7 +5858,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="145" customHeight="1">
+    <row r="29" ht="144.95" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
           <t>P-23</t>
@@ -5911,7 +5908,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="72.5" customHeight="1">
+    <row r="30" ht="72.59999999999999" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
           <t>P-24</t>
@@ -6006,7 +6003,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="275.5" customHeight="1">
+    <row r="32" ht="275.45" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
           <t>P-26</t>
@@ -6106,7 +6103,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="116" customHeight="1">
+    <row r="34" ht="116.1" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
           <t>P-28</t>
@@ -6467,7 +6464,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Эстония</t>
+          <t>Garon Sci. Lab., Fonoriton LtD (Tallinn, Estonia)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6481,7 +6478,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="116" customHeight="1">
+    <row r="42" ht="116.1" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>S1-04</t>
@@ -6606,7 +6603,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="159.5" customHeight="1">
+    <row r="45" ht="159.6" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
           <t>S1-07</t>
@@ -6696,7 +6693,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="246.5" customHeight="1">
+    <row r="47" ht="246.6" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
           <t>S1-09</t>
@@ -6741,7 +6738,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="377" customHeight="1">
+    <row r="48" ht="377.1" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
           <t>S1-10</t>
@@ -6786,7 +6783,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="159.5" customHeight="1">
+    <row r="49" ht="159.6" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
           <t>S1-11</t>
@@ -6831,7 +6828,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="159.5" customHeight="1">
+    <row r="50" ht="159.6" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
           <t>S1-12</t>
@@ -6876,7 +6873,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="72.5" customHeight="1">
+    <row r="51" ht="72.59999999999999" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
           <t>S1-13</t>
@@ -6961,7 +6958,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="116" customHeight="1">
+    <row r="53" ht="116.1" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
           <t>S1-15</t>
@@ -7046,7 +7043,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="203" customHeight="1">
+    <row r="55" ht="203.1" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
           <t>S1-17</t>
@@ -7091,7 +7088,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="203" customHeight="1">
+    <row r="56" ht="203.1" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
           <t>S1-18</t>
@@ -7162,7 +7159,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Узбекистан</t>
+          <t>Наманганский государственный технический университет (Наманган, Узбекистан)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7176,7 +7173,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="246.5" customHeight="1">
+    <row r="58" ht="246.6" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
           <t>S1-20</t>
@@ -7261,7 +7258,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="145" customHeight="1">
+    <row r="60" ht="144.95" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
           <t>S1-22</t>
@@ -7396,7 +7393,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="101.5" customHeight="1">
+    <row r="63" ht="101.45" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
           <t>S1-25</t>
@@ -7476,7 +7473,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="116" customHeight="1">
+    <row r="65" ht="116.1" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
           <t>S1-27</t>
@@ -7568,7 +7565,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="319" customHeight="1">
+    <row r="67" ht="318.95" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
           <t>S2-03</t>
@@ -7615,7 +7612,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="290" customHeight="1">
+    <row r="68" ht="290.1" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
           <t>S2-04</t>
@@ -7662,7 +7659,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="362.5" customHeight="1">
+    <row r="69" ht="362.45" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
           <t>S2-05</t>
@@ -7704,7 +7701,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="275.5" customHeight="1">
+    <row r="70" ht="275.45" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
           <t>S2-06</t>
@@ -7751,7 +7748,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="72.5" customHeight="1">
+    <row r="71" ht="72.59999999999999" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
           <t>S2-07</t>
@@ -7843,7 +7840,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="232" customHeight="1">
+    <row r="73" ht="231.95" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
           <t>S2-10</t>
@@ -7885,7 +7882,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="203" customHeight="1">
+    <row r="74" ht="203.1" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
           <t>S2-11</t>
@@ -7932,7 +7929,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="203" customHeight="1">
+    <row r="75" ht="203.1" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
           <t>S2-12</t>
@@ -7979,7 +7976,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="203" customHeight="1">
+    <row r="76" ht="203.1" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
           <t>S2-13</t>
@@ -8243,7 +8240,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="290" customHeight="1">
+    <row r="82" ht="290.1" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
           <t>S2-20</t>
@@ -8288,7 +8285,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="145" customHeight="1">
+    <row r="83" ht="144.95" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
           <t>S2-21</t>
@@ -8333,7 +8330,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="145" customHeight="1">
+    <row r="84" ht="144.95" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
           <t>S2-22</t>
@@ -8359,7 +8356,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Бангладеш</t>
+          <t>Department of Physics, Jagannath University (Dhaka, Bangladesh)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8415,7 +8412,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="203" customHeight="1">
+    <row r="86" ht="203.1" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
           <t>S2-24</t>
@@ -8457,7 +8454,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="188.5" customHeight="1">
+    <row r="87" ht="188.45" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
           <t>S2-25</t>
@@ -8551,7 +8548,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="290" customHeight="1">
+    <row r="89" ht="290.1" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
           <t>S2-27</t>
@@ -8593,7 +8590,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="159.5" customHeight="1">
+    <row r="90" ht="159.6" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
           <t>S2-28</t>
@@ -8635,7 +8632,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="145" customHeight="1">
+    <row r="91" ht="144.95" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
           <t>S2-29</t>
@@ -8717,7 +8714,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="232" customHeight="1">
+    <row r="93" ht="231.95" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
           <t>S2-31</t>
@@ -8797,7 +8794,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="203" customHeight="1">
+    <row r="95" ht="203.1" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
           <t>S2-33</t>
@@ -8837,7 +8834,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="145" customHeight="1">
+    <row r="96" ht="144.95" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
           <t>S2-34</t>
@@ -8877,7 +8874,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="188.5" customHeight="1">
+    <row r="97" ht="188.45" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
           <t>S2-35</t>
@@ -8922,7 +8919,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="188.5" customHeight="1">
+    <row r="98" ht="188.45" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
           <t>S2-36</t>
@@ -8967,7 +8964,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="246.5" customHeight="1">
+    <row r="99" ht="246.6" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
           <t>S3-01</t>
@@ -9012,7 +9009,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="159.5" customHeight="1">
+    <row r="100" ht="159.6" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
           <t>S3-02</t>
@@ -9057,7 +9054,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="188.5" customHeight="1">
+    <row r="101" ht="188.45" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
           <t>S3-03</t>
@@ -9102,7 +9099,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="290" customHeight="1">
+    <row r="102" ht="290.1" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
           <t>S3-04</t>
@@ -9142,7 +9139,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="290" customHeight="1">
+    <row r="103" ht="290.1" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
           <t>S3-05</t>
@@ -9187,7 +9184,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="232" customHeight="1">
+    <row r="104" ht="231.95" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
           <t>S3-06</t>
@@ -9227,7 +9224,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="319" customHeight="1">
+    <row r="105" ht="318.95" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
           <t>S3-07</t>
@@ -9272,7 +9269,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="333.5" customHeight="1">
+    <row r="106" ht="333.6" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
           <t>S3-08</t>
@@ -9317,7 +9314,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="145" customHeight="1">
+    <row r="107" ht="144.95" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
           <t>S3-09</t>
@@ -9357,7 +9354,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="246.5" customHeight="1">
+    <row r="108" ht="246.6" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
           <t>S3-10</t>
@@ -9402,7 +9399,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="145" customHeight="1">
+    <row r="109" ht="144.95" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
           <t>S3-11</t>
@@ -9447,7 +9444,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="275.5" customHeight="1">
+    <row r="110" ht="275.45" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
           <t>S3-12</t>
@@ -9487,7 +9484,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="188.5" customHeight="1">
+    <row r="111" ht="188.45" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
           <t>S3-13</t>
@@ -9532,7 +9529,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="116" customHeight="1">
+    <row r="112" ht="116.1" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
           <t>S3-14</t>
@@ -9577,7 +9574,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="246.5" customHeight="1">
+    <row r="113" ht="246.6" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
           <t>S3-15</t>
@@ -9617,7 +9614,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="188.5" customHeight="1">
+    <row r="114" ht="188.45" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
           <t>S3-16</t>
@@ -9662,7 +9659,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="333.5" customHeight="1">
+    <row r="115" ht="333.6" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
           <t>S3-17</t>
@@ -9702,7 +9699,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="203" customHeight="1">
+    <row r="116" ht="203.1" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
           <t>S3-18</t>
@@ -9787,7 +9784,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="275.5" customHeight="1">
+    <row r="118" ht="275.45" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
           <t>S3-20</t>
@@ -9832,7 +9829,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="203" customHeight="1">
+    <row r="119" ht="203.1" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
           <t>S3-21</t>
@@ -9877,7 +9874,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="203" customHeight="1">
+    <row r="120" ht="203.1" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
           <t>S3-22</t>
@@ -9957,7 +9954,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="188.5" customHeight="1">
+    <row r="122" ht="188.45" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
           <t>S3-24</t>
@@ -10132,7 +10129,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="362.5" customHeight="1">
+    <row r="126" ht="362.45" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
           <t>S4-01</t>
@@ -10177,7 +10174,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="145" customHeight="1">
+    <row r="127" ht="144.95" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
           <t>S4-02</t>
@@ -10222,7 +10219,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="290" customHeight="1">
+    <row r="128" ht="290.1" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
           <t>S4-03</t>
@@ -10307,7 +10304,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="232" customHeight="1">
+    <row r="130" ht="231.95" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
           <t>S4-05</t>
@@ -10352,7 +10349,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="275.5" customHeight="1">
+    <row r="131" ht="275.45" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
           <t>S4-06</t>
@@ -10442,7 +10439,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="246.5" customHeight="1">
+    <row r="133" ht="246.6" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
           <t>S4-08</t>
@@ -10534,7 +10531,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="188.5" customHeight="1">
+    <row r="135" ht="188.45" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
           <t>S4-11</t>
@@ -10581,7 +10578,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="246.5" customHeight="1">
+    <row r="136" ht="246.6" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
           <t>S4-12</t>
@@ -10675,7 +10672,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="246.5" customHeight="1">
+    <row r="138" ht="246.6" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
           <t>S4-15</t>
@@ -10765,7 +10762,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="145" customHeight="1">
+    <row r="140" ht="144.95" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
           <t>S4-17</t>
@@ -10810,7 +10807,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="145" customHeight="1">
+    <row r="141" ht="144.95" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
           <t>S4-18</t>
@@ -10895,7 +10892,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="232" customHeight="1">
+    <row r="143" ht="231.95" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
           <t>S4-20</t>
@@ -10940,7 +10937,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="159.5" customHeight="1">
+    <row r="144" ht="159.6" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
           <t>S4-21</t>
@@ -10985,7 +10982,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="246.5" customHeight="1">
+    <row r="145" ht="246.6" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
           <t>S4-22</t>
@@ -11030,7 +11027,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="203" customHeight="1">
+    <row r="146" ht="203.1" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
           <t>S4-23</t>
@@ -11075,7 +11072,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="319" customHeight="1">
+    <row r="147" ht="318.95" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
           <t>S4-24</t>
@@ -11165,7 +11162,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="72.5" customHeight="1">
+    <row r="149" ht="72.59999999999999" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
           <t>S4-26</t>
@@ -11250,7 +11247,7 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="319" customHeight="1">
+    <row r="151" ht="318.95" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
           <t>S4-28</t>
@@ -11295,7 +11292,7 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="290" customHeight="1">
+    <row r="152" ht="290.1" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
           <t>S5-01</t>
@@ -11340,7 +11337,7 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="246.5" customHeight="1">
+    <row r="153" ht="246.6" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
           <t>S5-02</t>
@@ -11560,7 +11557,7 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="188.5" customHeight="1">
+    <row r="158" ht="188.45" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
           <t>S5-07</t>
@@ -11695,7 +11692,7 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="246.5" customHeight="1">
+    <row r="161" ht="246.6" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
           <t>S6-01</t>
@@ -11740,7 +11737,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="232" customHeight="1">
+    <row r="162" ht="231.95" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
           <t>S6-02</t>
@@ -11785,7 +11782,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="58" customHeight="1">
+    <row r="163" ht="57.95" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
           <t>S6-03</t>
@@ -11870,7 +11867,7 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="101.5" customHeight="1">
+    <row r="165" ht="101.45" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
           <t>S6-05</t>
@@ -11960,7 +11957,7 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="145" customHeight="1">
+    <row r="167" ht="144.95" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
           <t>S6-07</t>
@@ -11986,7 +11983,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Пакистан</t>
+          <t>Institute of Space Technology (Islamabad, Pakistan)</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12040,7 +12037,7 @@
         </is>
       </c>
     </row>
-    <row r="169" ht="145" customHeight="1">
+    <row r="169" ht="144.95" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
           <t>S7-01</t>
@@ -12080,7 +12077,7 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="188.5" customHeight="1">
+    <row r="170" ht="188.45" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
           <t>S7-02</t>
@@ -12125,7 +12122,7 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="159.5" customHeight="1">
+    <row r="171" ht="159.6" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
           <t>S7-03</t>
@@ -12170,7 +12167,7 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="203" customHeight="1">
+    <row r="172" ht="203.1" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
           <t>S7-04</t>
@@ -12215,7 +12212,7 @@
         </is>
       </c>
     </row>
-    <row r="173" ht="159.5" customHeight="1">
+    <row r="173" ht="159.6" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
           <t>S7-05</t>
@@ -12260,7 +12257,7 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="159.5" customHeight="1">
+    <row r="174" ht="159.6" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
           <t>S7-06</t>
@@ -12305,7 +12302,7 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="290" customHeight="1">
+    <row r="175" ht="290.1" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
           <t>S7-07</t>
@@ -12350,7 +12347,7 @@
         </is>
       </c>
     </row>
-    <row r="176" ht="232" customHeight="1">
+    <row r="176" ht="231.95" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
           <t>S7-08</t>
@@ -12480,7 +12477,7 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="319" customHeight="1">
+    <row r="179" ht="318.95" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
           <t>S7-11</t>
@@ -12525,7 +12522,7 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="319" customHeight="1">
+    <row r="180" ht="318.95" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
           <t>S7-12</t>
@@ -12570,7 +12567,7 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="232" customHeight="1">
+    <row r="181" ht="231.95" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
           <t>S7-13</t>
@@ -12650,7 +12647,7 @@
         </is>
       </c>
     </row>
-    <row r="183" ht="159.5" customHeight="1">
+    <row r="183" ht="159.6" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
           <t>S7-15</t>
@@ -12740,7 +12737,7 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="275.5" customHeight="1">
+    <row r="185" ht="275.45" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
           <t>S7-17</t>
@@ -12785,7 +12782,7 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="203" customHeight="1">
+    <row r="186" ht="203.1" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
           <t>S7-18</t>
@@ -12861,7 +12858,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>РМНЦ им. Цыба</t>
+          <t>МРНЦ им. А.Ф. Цыба</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12875,7 +12872,7 @@
         </is>
       </c>
     </row>
-    <row r="188" ht="232" customHeight="1">
+    <row r="188" ht="231.95" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
           <t>S7-20</t>
@@ -12906,7 +12903,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>РМНЦ им. Цыба</t>
+          <t>МРНЦ им. А.Ф. Цыба</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12920,7 +12917,7 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="246.5" customHeight="1">
+    <row r="189" ht="246.6" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
           <t>S7-21</t>
@@ -13010,7 +13007,7 @@
         </is>
       </c>
     </row>
-    <row r="191" ht="159.5" customHeight="1">
+    <row r="191" ht="159.6" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
           <t>S7-23</t>
@@ -13102,10 +13099,10 @@
     </row>
     <row r="193" ht="261" customHeight="1"/>
     <row r="194" ht="261" customHeight="1"/>
-    <row r="195" ht="290" customHeight="1"/>
-    <row r="196" ht="232" customHeight="1"/>
+    <row r="195" ht="290.1" customHeight="1"/>
+    <row r="196" ht="231.95" customHeight="1"/>
     <row r="197" ht="174" customHeight="1"/>
-    <row r="198" ht="246.5" customHeight="1"/>
+    <row r="198" ht="246.6" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="J2:J499" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -13123,7 +13120,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -13197,7 +13194,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="188.5" customHeight="1">
+    <row r="2" ht="188.45" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>POST-01</t>
@@ -13229,7 +13226,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="101.5" customHeight="1">
+    <row r="3" ht="101.45" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>POST-02</t>
@@ -13261,7 +13258,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="101.5" customHeight="1">
+    <row r="4" ht="101.45" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>POST-03</t>
@@ -13399,7 +13396,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="203" customHeight="1">
+    <row r="8" ht="203.1" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>POST-07</t>
@@ -13436,7 +13433,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="159.5" customHeight="1">
+    <row r="9" ht="159.6" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>POST-08</t>
@@ -13473,7 +13470,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="101.5" customHeight="1">
+    <row r="10" ht="101.45" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>POST-09</t>
@@ -13505,7 +13502,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="101.5" customHeight="1">
+    <row r="11" ht="101.45" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>POST-10</t>
@@ -13616,7 +13613,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="232" customHeight="1">
+    <row r="14" ht="231.95" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>POST-13</t>
@@ -13685,7 +13682,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="159.5" customHeight="1">
+    <row r="16" ht="159.6" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>POST-15</t>
@@ -13722,7 +13719,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="116" customHeight="1">
+    <row r="17" ht="116.1" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>POST-16</t>
@@ -13759,7 +13756,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="145" customHeight="1">
+    <row r="18" ht="144.95" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>POST-17</t>
@@ -13796,7 +13793,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="188.5" customHeight="1">
+    <row r="19" ht="188.45" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
           <t>POST-18</t>
@@ -13833,7 +13830,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="101.5" customHeight="1">
+    <row r="20" ht="101.45" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
           <t>POST-19</t>
@@ -13865,7 +13862,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="145" customHeight="1">
+    <row r="21" ht="144.95" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
           <t>POST-20</t>
@@ -13897,7 +13894,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="319" customHeight="1">
+    <row r="22" ht="318.95" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>POST-21</t>
@@ -13934,7 +13931,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="203" customHeight="1">
+    <row r="23" ht="203.1" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>POST-22</t>
@@ -13966,7 +13963,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="290" customHeight="1">
+    <row r="24" ht="290.1" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
           <t>POST-23</t>
@@ -13998,7 +13995,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="232" customHeight="1">
+    <row r="25" ht="231.95" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>POST-24</t>
@@ -14030,7 +14027,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="290" customHeight="1">
+    <row r="26" ht="290.1" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>POST-25</t>
@@ -14136,7 +14133,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="246.5" customHeight="1">
+    <row r="29" ht="246.6" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
           <t>POST-28</t>
@@ -14210,7 +14207,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="232" customHeight="1">
+    <row r="31" ht="231.95" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
           <t>POST-30</t>
@@ -14247,7 +14244,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="203" customHeight="1">
+    <row r="32" ht="203.1" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
           <t>POST-31</t>
@@ -14284,7 +14281,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="203" customHeight="1">
+    <row r="33" ht="203.1" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
           <t>POST-32</t>
@@ -14321,7 +14318,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="246.5" customHeight="1">
+    <row r="34" ht="246.6" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
           <t>POST-33</t>
@@ -14358,7 +14355,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="290" customHeight="1">
+    <row r="35" ht="290.1" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
           <t>POST-34</t>
@@ -14390,7 +14387,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="159.5" customHeight="1">
+    <row r="36" ht="159.6" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
           <t>POST-35</t>
@@ -14427,7 +14424,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="290" customHeight="1">
+    <row r="37" ht="290.1" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
           <t>POST-36</t>
@@ -14464,7 +14461,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="145" customHeight="1">
+    <row r="38" ht="144.95" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
           <t>POST-37</t>
@@ -14575,7 +14572,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="145" customHeight="1">
+    <row r="41" ht="144.95" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
           <t>POST-40</t>
@@ -14612,7 +14609,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="145" customHeight="1">
+    <row r="42" ht="144.95" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
           <t>POST-41</t>
@@ -14649,7 +14646,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="232" customHeight="1">
+    <row r="43" ht="231.95" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
           <t>POST-42</t>
@@ -14686,7 +14683,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="232" customHeight="1">
+    <row r="44" ht="231.95" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
           <t>POST-43</t>
@@ -14787,7 +14784,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="232" customHeight="1">
+    <row r="47" ht="231.95" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
           <t>POST-46</t>
@@ -14819,7 +14816,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="116" customHeight="1">
+    <row r="48" ht="116.1" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
           <t>POST-47</t>
@@ -14868,7 +14865,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="3"/>
@@ -14892,7 +14889,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="n">
+      <c r="A2" s="6" t="n">
         <v>46279.71037037037</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -14937,7 +14934,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="8" t="n">
         <v>46280.72569444445</v>
       </c>
       <c r="B5" t="inlineStr">

--- a/data/programme.xlsx
+++ b/data/programme.xlsx
@@ -20,12 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
     <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy\ hh:mm"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd\ hh:mm"/>
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -78,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -94,6 +95,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1787,6 +1789,16 @@
           <t>библиотека</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>И. Н. Изосимов</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>I. N. Izosimov</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1818,6 +1830,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>И. А. Митропольский</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>I. A. Mitropolsky</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1827,7 +1849,7 @@
         <v>0.6770833333333334</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.75</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1841,12 +1863,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1-7</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>117л</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>А. А. Дзюба</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>A. A. Dzyuba</t>
         </is>
       </c>
     </row>
@@ -1880,6 +1912,16 @@
           <t>315л</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>В. О. Сабуров</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>V. O. Saburov</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2295,6 +2337,16 @@
           <t>библиотека</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>И. А. Мазур</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>I. A. Mazur</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2326,6 +2378,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>А. С. Демьянова</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>A. S. Demyanova</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2357,6 +2419,16 @@
           <t>117л</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Г. А. Феофилов</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>G. A. Feofilov</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2388,6 +2460,16 @@
           <t>315л</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>О. В. Белов</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O. V. Belov</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2445,6 +2527,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>А. С. Демьянова</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>A. S. Demyanova</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2476,6 +2568,16 @@
           <t>библиотека</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>В. И. Жеребчевский</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>V. I. Zherebchevsky</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2507,6 +2609,16 @@
           <t>117л</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Д. Прохорова</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>D. Prokhorova</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2538,6 +2650,16 @@
           <t>315л</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>А. П. Черняев</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>A. P. Chernyaev</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -2958,6 +3080,16 @@
           <t>библиотека</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Д. М. Родкин</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>D. M. Rodkin</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2989,6 +3121,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Д. Е. Любашевский</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>D. E. Lyubashevsky</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -3020,6 +3162,16 @@
           <t>117л</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>А. И. Мазур</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>A. I. Mazur</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -3051,6 +3203,16 @@
           <t>315л</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>А. С. Чепурнов</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>A. S. Chepurnov</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -3108,16 +3270,8 @@
           <t>холл2</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Время уточняется</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Time to be confirmed</t>
-        </is>
-      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -3927,6 +4081,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>О. А. Рубцова</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O. A. Rubtsova</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -3958,6 +4122,16 @@
           <t>235ц</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>М. А. Науменко</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>M. A. Naumenko</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -3989,6 +4163,16 @@
           <t>117л</t>
         </is>
       </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>А. В. Канцырев</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>A. V. Kantsyrev</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -4020,6 +4204,16 @@
           <t>библиотека</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>А. А. Зайцев</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>A. A. Zaitsev</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -4077,6 +4271,16 @@
           <t>117л</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>А. В. Канцырев</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>A. V. Kantsyrev</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -4108,6 +4312,16 @@
           <t>библиотека</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>А. А. Зайцев</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>A. A. Zaitsev</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -4137,6 +4351,16 @@
       <c r="I79" t="inlineStr">
         <is>
           <t>315л</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>С. Мамаева</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>S. Mamaeva</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S192"/>
+  <dimension ref="A1:S191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9227,7 +9451,7 @@
     <row r="105" ht="318.95" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S3-07</t>
+          <t>S3-08</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9236,43 +9460,43 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Мальцев</t>
+          <t>Семенов</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Николай</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>НИЦ КИ</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>n.maltsev@spbu.ru</t>
+          <t>kindr_cool@mail.ru</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>Особенности изучения свойств пучков тяжёлых ионов высоких энергий</t>
+          <t>Критический стенд «П»: современное состояние, особенности и роль исследований для развития технологии ВВЭР</t>
         </is>
       </c>
     </row>
     <row r="106" ht="333.6" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S3-08</t>
+          <t>S3-09</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9281,43 +9505,38 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Семенов</t>
+          <t>Бурякова</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Сергей</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Владимирович</t>
+          <t>Елена</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>ВНИИЭф</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>kindr_cool@mail.ru</t>
+          <t>suyazova.elena@mail.ru</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>Критический стенд «П»: современное состояние, особенности и роль исследований для развития технологии ВВЭР</t>
+          <t>Результаты экспериментов с тепловыми трубами с цезиевым теплоносителем</t>
         </is>
       </c>
     </row>
     <row r="107" ht="144.95" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S3-09</t>
+          <t>S3-10</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9326,38 +9545,43 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Бурякова</t>
+          <t>Розов</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ВНИИЭф</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>suyazova.elena@mail.ru</t>
+          <t>rozovs@jinr.ru</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>Результаты экспериментов с тепловыми трубами с цезиевым теплоносителем</t>
+          <t>Низкофоновый детектор нейтронов на основе гелия-3</t>
         </is>
       </c>
     </row>
     <row r="108" ht="246.6" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S3-10</t>
+          <t>S3-11</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9366,43 +9590,43 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Розов</t>
+          <t>Каретников</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Максим</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Донатович</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ВНИИА</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>rozovs@jinr.ru</t>
+          <t>mcsym01@gmail.com</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>Низкофоновый детектор нейтронов на основе гелия-3</t>
+          <t>Нейтрон-нейтронные методы дистанционного контроля с использованием меченых нейтронов</t>
         </is>
       </c>
     </row>
     <row r="109" ht="144.95" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S3-11</t>
+          <t>S3-12</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9411,43 +9635,38 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Каретников</t>
+          <t>Данилкин</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Максим</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Донатович</t>
+          <t>Владислав</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>ВНИИА</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>mcsym01@gmail.com</t>
+          <t>donyvlad@gmail.com</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>Нейтрон-нейтронные методы дистанционного контроля с использованием меченых нейтронов</t>
+          <t>Моделирование ионной оптики сепаратора STAR с помощью программы SHEMAT</t>
         </is>
       </c>
     </row>
     <row r="110" ht="275.45" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S3-12</t>
+          <t>S3-13</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9456,16 +9675,21 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Данилкин</t>
+          <t>Веденеев</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Владислав</t>
+          <t>Вячеслав</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Юрьевич</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9475,19 +9699,19 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>donyvlad@gmail.com</t>
+          <t>vvedeneyev@gmail.com</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>Моделирование ионной оптики сепаратора STAR с помощью программы SHEMAT</t>
+          <t>Криогенная газовая ячейка охлаждения ионов. Особенности конструкции, вакуумная система, система газового обеспечения, система охлаждения</t>
         </is>
       </c>
     </row>
     <row r="111" ht="188.45" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S3-13</t>
+          <t>S3-14</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9496,21 +9720,21 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Веденеев</t>
+          <t>Новоселов</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Вячеслав</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Юрьевич</t>
+          <t>Сергеевич</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9520,19 +9744,19 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>vvedeneyev@gmail.com</t>
+          <t>noval@jinr.ru</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>Криогенная газовая ячейка охлаждения ионов. Особенности конструкции, вакуумная система, система газового обеспечения, система охлаждения</t>
+          <t>Измерение времени экстракции ионов из криогенной газовой ячейки охлаждения</t>
         </is>
       </c>
     </row>
     <row r="112" ht="116.1" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S3-14</t>
+          <t>S3-15</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9541,21 +9765,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Новоселов</t>
+          <t>Зимин</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Алексей</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Сергеевич</t>
+          <t>Илья</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9565,19 +9784,19 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>noval@jinr.ru</t>
+          <t>zimin@jinr.ru</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>Измерение времени экстракции ионов из криогенной газовой ячейки охлаждения</t>
+          <t>Нейтронные сцинтилляторы на основе кристалла ZnS(Ag)</t>
         </is>
       </c>
     </row>
     <row r="113" ht="246.6" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S3-15</t>
+          <t>S3-16</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9586,16 +9805,21 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Зимин</t>
+          <t>Сидорова</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Илья</t>
+          <t>Ольга</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Викторовна</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -9605,19 +9829,19 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>zimin@jinr.ru</t>
+          <t>sidorova@jinr.ru</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>Нейтронные сцинтилляторы на основе кристалла ZnS(Ag)</t>
+          <t>Физическая структура кросс-толка гамма-квантов в сферических многодетекторных сцинтилляционных системах</t>
         </is>
       </c>
     </row>
     <row r="114" ht="188.45" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S3-16</t>
+          <t>S3-17</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9626,43 +9850,38 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Сидорова</t>
+          <t>Strizhak</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ольга</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Викторовна</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ИЯИ</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>sidorova@jinr.ru</t>
+          <t>strizhak@inr.ru</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>Физическая структура кросс-толка гамма-квантов в сферических многодетекторных сцинтилляционных системах</t>
+          <t>Performance and light yield of CsI(pure) scintillation module prototypes at LN2 temperature</t>
         </is>
       </c>
     </row>
     <row r="115" ht="333.6" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S3-17</t>
+          <t>S3-18</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9671,38 +9890,38 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Strizhak</t>
+          <t>Суслов</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Иван</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ИЯИ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>strizhak@inr.ru</t>
+          <t>ivsuslov@jinr.ru</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>Performance and light yield of CsI(pure) scintillation module prototypes at LN2 temperature</t>
+          <t>Пласстмассовые сцинтилляторы с возможностью разделения частиц по форме импульса</t>
         </is>
       </c>
     </row>
     <row r="116" ht="203.1" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S3-18</t>
+          <t>S3-19</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9711,16 +9930,21 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Суслов</t>
+          <t>Евсеев</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -9730,19 +9954,19 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ivsuslov@jinr.ru</t>
+          <t>evseevsa@jinr.ru</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>Пласстмассовые сцинтилляторы с возможностью разделения частиц по форме импульса</t>
+          <t>Исследование радиационной стойкости SiC- и Si-детекторов после облучения альфа-частицами</t>
         </is>
       </c>
     </row>
     <row r="117" ht="130.5" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S3-19</t>
+          <t>S3-20</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9751,43 +9975,43 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Евсеев</t>
+          <t>Смирнов</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Игорь</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Борисович</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ПИЯФ</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>evseevsa@jinr.ru</t>
+          <t>smirnov_ib@pnpi.nrcki.ru</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>Исследование радиационной стойкости SiC- и Si-детекторов после облучения альфа-частицами</t>
+          <t>Average Spatial Resolution of Detector Layers of Four-Layer Position-Sensitive Detectors</t>
         </is>
       </c>
     </row>
     <row r="118" ht="275.45" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S3-20</t>
+          <t>S3-21</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9796,43 +10020,43 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Смирнов</t>
+          <t>Стрекаловский</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Олег</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Викторович</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>ПИЯФ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>smirnov_ib@pnpi.nrcki.ru</t>
+          <t>stroleg1@yandex.ru</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>Average Spatial Resolution of Detector Layers of Four-Layer Position-Sensitive Detectors</t>
+          <t>Применение диджитайзеров CAEN-ХХ42 для регистрации заряженных частиц</t>
         </is>
       </c>
     </row>
     <row r="119" ht="203.1" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S3-21</t>
+          <t>S3-22</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9841,43 +10065,38 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Стрекаловский</t>
+          <t>Шимко</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Олег</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Викторович</t>
+          <t>Павел</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>stroleg1@yandex.ru</t>
+          <t>pashashimko0306@gmail.com</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>Применение диджитайзеров CAEN-ХХ42 для регистрации заряженных частиц</t>
+          <t>Исследование распределения поглощённой дозы в полимерных материалах при облучении ускоренными электронами</t>
         </is>
       </c>
     </row>
     <row r="120" ht="203.1" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S3-22</t>
+          <t>S3-23</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9886,38 +10105,38 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Шимко</t>
+          <t>Цыганкова</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Павел</t>
+          <t>Валерия</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>СВКНИИ ДВО</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pashashimko0306@gmail.com</t>
+          <t>tsigankova.valeriya@mail.ru</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>Исследование распределения поглощённой дозы в полимерных материалах при облучении ускоренными электронами</t>
+          <t>Влияние ²²²Rn на расчёт радиоуглеродного возраста древесных углей</t>
         </is>
       </c>
     </row>
     <row r="121" ht="217.5" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S3-23</t>
+          <t>S3-24</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9926,38 +10145,43 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Цыганкова</t>
+          <t>Пухаева</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Валерия</t>
+          <t>Нелли</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Ефимовна</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>СВКНИИ ДВО</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>tsigankova.valeriya@mail.ru</t>
+          <t>pukhaeva@jinr.ru</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>Влияние ²²²Rn на расчёт радиоуглеродного возраста древесных углей</t>
+          <t>Nd/ZnS-модифицированные квантовые точки CdZnSeS как нанокомпоненты сцинтилляционных сред для поиска безнейтринного двойного β-распада ¹⁵⁰Nd</t>
         </is>
       </c>
     </row>
     <row r="122" ht="188.45" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S3-24</t>
+          <t>S3-25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9966,7 +10190,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9995,14 +10219,14 @@
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>Nd/ZnS-модифицированные квантовые точки CdZnSeS как нанокомпоненты сцинтилляционных сред для поиска безнейтринного двойного β-распада ¹⁵⁰Nd</t>
+          <t>Results of ARFIM experiment setup for applied research of NOSU</t>
         </is>
       </c>
     </row>
     <row r="123" ht="174" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S3-25</t>
+          <t>S3-26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10011,7 +10235,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10040,14 +10264,14 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>Results of ARFIM experiment setup for applied research of NOSU</t>
+          <t>Neodymium-modified CdZnSeS/ZnS quantum dots: evolution of optical response and evidence limits for core/shell architecture</t>
         </is>
       </c>
     </row>
     <row r="124" ht="261" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S3-26</t>
+          <t>S3-27</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10056,83 +10280,83 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Пухаева</t>
+          <t>Петровская</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Нелли</t>
+          <t>Анна</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ефимовна</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>ОИЯИ</t>
+          <t>Станиславовна</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>pukhaeva@jinr.ru</t>
+          <t>anita3425@yandex.ru</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>Neodymium-modified CdZnSeS/ZnS quantum dots: evolution of optical response and evidence limits for core/shell architecture</t>
+          <t>Перспективы применения сухой ионно-плазменной технологии дезактивации оборудования ЯЭУ из титановых сплавов</t>
         </is>
       </c>
     </row>
     <row r="125" ht="174" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S3-27</t>
+          <t>S4-01</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Петровская</t>
+          <t>Бикметов</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Станиславовна</t>
+          <t>Рафальевич</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>anita3425@yandex.ru</t>
+          <t>bikmetov@jinr.ru</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>Перспективы применения сухой ионно-плазменной технологии дезактивации оборудования ЯЭУ из титановых сплавов</t>
+          <t>Investigation of nuclear deformation influence on anisotropic flows in heavy-ion collisions at NICA energies</t>
         </is>
       </c>
     </row>
     <row r="126" ht="362.45" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S4-01</t>
+          <t>S4-02</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10141,43 +10365,43 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Бикметов</t>
+          <t>Вечернин</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Владимир</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Рафальевич</t>
+          <t>Викторович</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>bikmetov@jinr.ru</t>
+          <t>v.vechernin@spbu.ru</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>Investigation of nuclear deformation influence on anisotropic flows in heavy-ion collisions at NICA energies</t>
+          <t>Кумулятивные явления в области больших поперечных импульсов и их наблюдение в столкновениях ядер на коллайдере NICA</t>
         </is>
       </c>
     </row>
     <row r="127" ht="144.95" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S4-02</t>
+          <t>S4-03</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10186,43 +10410,38 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Вечернин</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Владимир</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Викторович</t>
+          <t>Shubham</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>v.vechernin@spbu.ru</t>
+          <t>s.sharma.hep@gmail.com</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>Кумулятивные явления в области больших поперечных импульсов и их наблюдение в столкновениях ядер на коллайдере NICA</t>
+          <t>Inclusive J/ψ Production as a Probe of Gluon Dynamics at NICA</t>
         </is>
       </c>
     </row>
     <row r="128" ht="290.1" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S4-03</t>
+          <t>S4-04</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10231,38 +10450,43 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Жаров</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Shubham</t>
+          <t>Михаил</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>s.sharma.hep@gmail.com</t>
+          <t>m.zharov@spbu.ru</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>Inclusive J/ψ Production as a Probe of Gluon Dynamics at NICA</t>
+          <t>Моделирование кумулятивных эффектов в столкновениях тяжелых ионов при энергиях коллайдера NICA</t>
         </is>
       </c>
     </row>
     <row r="129" ht="261" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S4-04</t>
+          <t>S4-05</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10271,43 +10495,43 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Жаров</t>
+          <t>Идрисов</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Дим</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Маратович</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>m.zharov@spbu.ru</t>
+          <t>idrisov.dim@mail.ru</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>Моделирование кумулятивных эффектов в столкновениях тяжелых ионов при энергиях коллайдера NICA</t>
+          <t>Методы определения центральности с использованием передних детекторов в эксперименте BM@N</t>
         </is>
       </c>
     </row>
     <row r="130" ht="231.95" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S4-05</t>
+          <t>S4-06</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10316,43 +10540,43 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Идрисов</t>
+          <t>Plotnikov</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Дим</t>
+          <t>Vasilii</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Маратович</t>
+          <t>Alexandrovich</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>idrisov.dim@mail.ru</t>
+          <t>vplotnikov@jinr.ru</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>Методы определения центральности с использованием передних детекторов в эксперименте BM@N</t>
+          <t>Λd сorrelation function in Xe+CsI collisions at 3.8 AGeV in the BM@N experiment</t>
         </is>
       </c>
     </row>
     <row r="131" ht="275.45" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S4-06</t>
+          <t>S4-07</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10361,43 +10585,43 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Plotnikov</t>
+          <t>Зубанков</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Vasilii</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Alexandrovich</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>vplotnikov@jinr.ru</t>
+          <t>zubankov@inr.ru</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>Λd сorrelation function in Xe+CsI collisions at 3.8 AGeV in the BM@N experiment</t>
+          <t>Measurement of double differential inclusive cross sections of forward neutron emission in the BM@N experiment</t>
         </is>
       </c>
     </row>
     <row r="132" ht="130.5" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S4-07</t>
+          <t>S4-08</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10406,43 +10630,43 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Зубанков</t>
+          <t>Андронов</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Евгений</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>zubankov@inr.ru</t>
+          <t>e.v.andronov@spbu.ru</t>
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>Measurement of double differential inclusive cross sections of forward neutron emission in the BM@N experiment</t>
+          <t>Influence of colour string configurations on rapidity multiplicity correlations</t>
         </is>
       </c>
     </row>
     <row r="133" ht="246.6" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S4-08</t>
+          <t>S4-10</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10450,17 +10674,19 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C133" t="n">
-        <v>8</v>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Андронов</t>
+          <t>Герасименюк</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Евгений</t>
+          <t>Николай</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -10470,24 +10696,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ДВФУ</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>e.v.andronov@spbu.ru</t>
+          <t>gerasimenyuk.nv@dvfu.ru</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>Influence of colour string configurations on rapidity multiplicity correlations</t>
+          <t>Экранирование заряда в многокомпонентной аблелевой модели Хиггса</t>
         </is>
       </c>
     </row>
     <row r="134" ht="217.5" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S4-10</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10497,44 +10723,44 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Герасименюк</t>
+          <t>Зайцев</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Николай</t>
+          <t>Андрей</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>ДВФУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>gerasimenyuk.nv@dvfu.ru</t>
+          <t>zaicev@jinr.ru</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>Экранирование заряда в многокомпонентной аблелевой модели Хиггса</t>
+          <t>Ядро ⁸Be и состояние Хойла в диссоциации релятивистских ядер</t>
         </is>
       </c>
     </row>
     <row r="135" ht="188.45" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10544,44 +10770,44 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Зайцев</t>
+          <t>Скородько</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Татьяна</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Юрьевна</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>zaicev@jinr.ru</t>
+          <t>tatiskor@mail.ru</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>Ядро ⁸Be и состояние Хойла в диссоциации релятивистских ядер</t>
+          <t>Dibaryon d*(2380) : prediction, detection, understanding</t>
         </is>
       </c>
     </row>
     <row r="136" ht="246.6" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>S4-14</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10591,44 +10817,44 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Скородько</t>
+          <t>Friesen</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Татьяна</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Юрьевна</t>
+          <t>Vadimovna</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>tatiskor@mail.ru</t>
+          <t>avfriesen@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>Dibaryon d*(2380) : prediction, detection, understanding</t>
+          <t>Mass spectrum of noncharmed and charmed meson states at finite temperature in extended linear-sigma model</t>
         </is>
       </c>
     </row>
     <row r="137" ht="174" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S4-14</t>
+          <t>S4-15</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10636,24 +10862,22 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C137" t="n">
+        <v>15</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Friesen</t>
+          <t>Авдеев</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vadimovna</t>
+          <t>Петрович</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10663,19 +10887,19 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>avfriesen@theor.jinr.ru</t>
+          <t>avdeyev@jinr.ru</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>Mass spectrum of noncharmed and charmed meson states at finite temperature in extended linear-sigma model</t>
+          <t>Source velocity in collisions of 2.1 GeV and 3.6 GeV protons with gold target.</t>
         </is>
       </c>
     </row>
     <row r="138" ht="246.6" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S4-15</t>
+          <t>S4-16</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10684,43 +10908,43 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Авдеев</t>
+          <t>Иванищев</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Дмитрий</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Петрович</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИЦ КИ-ПИЯФ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>avdeyev@jinr.ru</t>
+          <t>ivanishchev_da@pnpi.nrcki.ru</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>Source velocity in collisions of 2.1 GeV and 3.6 GeV protons with gold target.</t>
+          <t>Особенности измерения свойств резонансов в эксперименте MPD в Xe+W столкновениях при энергии 2,5 A*ГэВ</t>
         </is>
       </c>
     </row>
     <row r="139" ht="174" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S4-16</t>
+          <t>S4-17</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10729,43 +10953,43 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Иванищев</t>
+          <t>Силагадзе</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Зураб</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Карлоевич</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>НИЦ КИ-ПИЯФ</t>
+          <t>ИЯФ Новосиб</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>ivanishchev_da@pnpi.nrcki.ru</t>
+          <t>silagadze@inp.nsk.su</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>Особенности измерения свойств резонансов в эксперименте MPD в Xe+W столкновениях при энергии 2,5 A*ГэВ</t>
+          <t>Pauli equation in spaces of constant curvature and extended Nikiforov-Uvarov method</t>
         </is>
       </c>
     </row>
     <row r="140" ht="144.95" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S4-17</t>
+          <t>S4-18</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10774,43 +10998,43 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Силагадзе</t>
+          <t>Феофилов</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Зураб</t>
+          <t>Григорий</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Карлоевич</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>ИЯФ Новосиб</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>silagadze@inp.nsk.su</t>
+          <t>g.feofilov@spbu.ru</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>Pauli equation in spaces of constant curvature and extended Nikiforov-Uvarov method</t>
+          <t>Минимизация объемных флуктуаций при поиске критической точки сильно взаимодействующей материи в релятивистских ядерных столкновениях</t>
         </is>
       </c>
     </row>
     <row r="141" ht="144.95" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S4-18</t>
+          <t>S4-19</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10819,43 +11043,38 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Феофилов</t>
+          <t>Prokhorova</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Григорий</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Александрович</t>
+          <t>Daria</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>Tsinghua Univ., China</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>g.feofilov@spbu.ru</t>
+          <t>daria-prokhorova@mail.tsinghua.edu.cn</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>Минимизация объемных флуктуаций при поиске критической точки сильно взаимодействующей материи в релятивистских ядерных столкновениях</t>
+          <t>Heavy-flavor jet quenching in pre-equilibrium medium</t>
         </is>
       </c>
     </row>
     <row r="142" ht="174" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S4-19</t>
+          <t>S4-20</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10864,38 +11083,43 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Prokhorova</t>
+          <t>Недорезов</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Daria</t>
+          <t>Егор</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Вячеславович</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tsinghua Univ., China</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>daria-prokhorova@mail.tsinghua.edu.cn</t>
+          <t>nedorezov@jinr.ru</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>Heavy-flavor jet quenching in pre-equilibrium medium</t>
+          <t>Overview of the STAR hot QCD results</t>
         </is>
       </c>
     </row>
     <row r="143" ht="231.95" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S4-20</t>
+          <t>S4-21</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10904,43 +11128,43 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Недорезов</t>
+          <t>Ануфриев</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Егор</t>
+          <t>Антон</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Вячеславович</t>
+          <t>Витальевич</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>nedorezov@jinr.ru</t>
+          <t>antonman200@yandex.ru</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>Overview of the STAR hot QCD results</t>
+          <t>Исследование выходов заряженных адронов в рамках гидродинамического моделирования с применением голографического уравнения состояния</t>
         </is>
       </c>
     </row>
     <row r="144" ht="159.6" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S4-21</t>
+          <t>S4-22</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10949,21 +11173,21 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Ануфриев</t>
+          <t>Галактионов</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Антон</t>
+          <t>Кирилл</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Витальевич</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10973,19 +11197,19 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>antonman200@yandex.ru</t>
+          <t>kirill.galaktionov@spbu.ru</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>Исследование выходов заряженных адронов в рамках гидродинамического моделирования с применением голографического уравнения состояния</t>
+          <t>Исследование нейросетевых подходов к оценке прицельного параметра в столкновениях тяжелых ионов на основе 4π информации о событии</t>
         </is>
       </c>
     </row>
     <row r="145" ht="246.6" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S4-22</t>
+          <t>S4-23</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -10994,43 +11218,43 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Галактионов</t>
+          <t>Дьяченко</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Кирилл</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Трофимович</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>НИЦ КИ-ПИЯФ</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>kirill.galaktionov@spbu.ru</t>
+          <t>dyachenko_a@mail.ru</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>Исследование нейросетевых подходов к оценке прицельного параметра в столкновениях тяжелых ионов на основе 4π информации о событии</t>
+          <t>Неравновесный квантовый гидродинамический подход и эмиссия фрагментов в столкновениях тяжелых ионов промежуточных энергий</t>
         </is>
       </c>
     </row>
     <row r="146" ht="203.1" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S4-23</t>
+          <t>S4-24</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11039,43 +11263,43 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Дьяченко</t>
+          <t>Белокурова</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Светлана</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Трофимович</t>
+          <t>Николаевна</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>НИЦ КИ-ПИЯФ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>dyachenko_a@mail.ru</t>
+          <t>s.belokurova@spbu.ru</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>Неравновесный квантовый гидродинамический подход и эмиссия фрагментов в столкновениях тяжелых ионов промежуточных энергий</t>
+          <t>Применение классического глауберовского подхода к описанию дейтрон-дейтронного взаимодействия</t>
         </is>
       </c>
     </row>
     <row r="147" ht="318.95" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S4-24</t>
+          <t>S4-25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11084,21 +11308,21 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Белокурова</t>
+          <t>Размыслов</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Светлана</t>
+          <t>Константин</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11108,19 +11332,19 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>s.belokurova@spbu.ru</t>
+          <t>yoitz@yandex.ru</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>Применение классического глауберовского подхода к описанию дейтрон-дейтронного взаимодействия</t>
+          <t>О применении генераторов EPOS4, UrQMD, PHQMD и PYTHIA для анализа событий в физике сверхвысоких энергий</t>
         </is>
       </c>
     </row>
     <row r="148" ht="130.5" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S4-25</t>
+          <t>S4-26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11129,43 +11353,43 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Размыслов</t>
+          <t>Мягков</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Константин</t>
+          <t>Данила</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>НИИЯФ МГУ</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>yoitz@yandex.ru</t>
+          <t>danila.myagkov.msu@mail.ru</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>О применении генераторов EPOS4, UrQMD, PHQMD и PYTHIA для анализа событий в физике сверхвысоких энергий</t>
+          <t>Моделирование влияния деформации ядер на азимутальную анизотропию частиц в генераторе событий HYDJET++</t>
         </is>
       </c>
     </row>
     <row r="149" ht="72.59999999999999" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S4-26</t>
+          <t>S4-27</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11174,43 +11398,38 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Мягков</t>
+          <t>Vasilieva</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Данила</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Александрович</t>
+          <t>Anastasiia</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>НИИЯФ МГУ</t>
+          <t>МИФИ</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>danila.myagkov.msu@mail.ru</t>
+          <t>anastasiyavasileva00@gmail.com</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>Моделирование влияния деформации ядер на азимутальную анизотропию частиц в генераторе событий HYDJET++</t>
+          <t>Analysis of charged and identified hadron spectra with Tsallis distributions in O+O, Kr+Kr, and Xe+Xe collisions at √sₙₙ = 6 GeV using the UrQMD model</t>
         </is>
       </c>
     </row>
     <row r="150" ht="348" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S4-27</t>
+          <t>S4-28</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11219,83 +11438,88 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Vasilieva</t>
+          <t>Калугин</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Anastasiia</t>
+          <t>Никита</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Константинович</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>МИФИ</t>
+          <t>КИ ИФВЭ</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>anastasiyavasileva00@gmail.com</t>
+          <t>Nikita.Kalugin@ihep.ru</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>Analysis of charged and identified hadron spectra with Tsallis distributions in O+O, Kr+Kr, and Xe+Xe collisions at √sₙₙ = 6 GeV using the UrQMD model</t>
+          <t>Измерение выстроенности K*⁻(892)-мезонов, образованных в каон-ядерных и пион-ядерных взаимодействиях на ускорительном комплексе У-70</t>
         </is>
       </c>
     </row>
     <row r="151" ht="318.95" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S4-28</t>
+          <t>S5-01</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Калугин</t>
+          <t>Чернышев</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Борис</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Константинович</t>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>КИ ИФВЭ</t>
+          <t>МИФИ</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Nikita.Kalugin@ihep.ru</t>
+          <t>chernyshev@mephi.ru</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>Измерение выстроенности K*⁻(892)-мезонов, образованных в каон-ядерных и пион-ядерных взаимодействиях на ускорительном комплексе У-70</t>
+          <t>Поиск тринейтрона в реакциях поглощения остановившихся пионов ядрами ⁹Be</t>
         </is>
       </c>
     </row>
     <row r="152" ht="290.1" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S5-01</t>
+          <t>S5-02</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11304,43 +11528,43 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Чернышев</t>
+          <t>Борзаков</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Борис</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Борисович</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>МИФИ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>chernyshev@mephi.ru</t>
+          <t>sbor@nf.jinr.ru</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>Поиск тринейтрона в реакциях поглощения остановившихся пионов ядрами ⁹Be</t>
+          <t>Возможное существование синглетного дейтрона как дибарионного резонанса и проблема существования динейтрона</t>
         </is>
       </c>
     </row>
     <row r="153" ht="246.6" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S5-02</t>
+          <t>S5-03</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11349,43 +11573,43 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Борзаков</t>
+          <t>Ефименко</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Мария</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Константиновна</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ТОГУ</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>sbor@nf.jinr.ru</t>
+          <t>ef.maria97@yandex.ru</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>Возможное существование синглетного дейтрона как дибарионного резонанса и проблема существования динейтрона</t>
+          <t>Excited states of ⁶He nucleus in the SS-HORSE–NCSM approach</t>
         </is>
       </c>
     </row>
     <row r="154" ht="261" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S5-03</t>
+          <t>S5-04</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11394,21 +11618,21 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Ефименко</t>
+          <t>Зайцев</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Мария</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Константиновна</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11418,19 +11642,19 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>ef.maria97@yandex.ru</t>
+          <t>000282@togudv.ru</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>Excited states of ⁶He nucleus in the SS-HORSE–NCSM approach</t>
+          <t>Ионизация атомов протонным ударом в представлении параболических квазиштурмовских функций</t>
         </is>
       </c>
     </row>
     <row r="155" ht="261" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S5-04</t>
+          <t>S5-05</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11439,7 +11663,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11448,12 +11672,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Сергеевич</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11463,19 +11687,19 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>000282@togudv.ru</t>
+          <t>alzaytsev@togudv.ru</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>Ионизация атомов протонным ударом в представлении параболических квазиштурмовских функций</t>
+          <t>Атом водорода в поле лазерного импульса в представлении параболических волновых пакетов</t>
         </is>
       </c>
     </row>
     <row r="156" ht="348" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S5-05</t>
+          <t>S5-06</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11484,43 +11708,38 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Зайцев</t>
+          <t>Шалапинин</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Александр</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Сергеевич</t>
+          <t>Денис</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>ТОГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>alzaytsev@togudv.ru</t>
+          <t>shalapinin@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>Атом водорода в поле лазерного импульса в представлении параболических волновых пакетов</t>
+          <t>Van der Waals dimers of neon</t>
         </is>
       </c>
     </row>
     <row r="157" ht="304.5" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S5-06</t>
+          <t>S5-07</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11529,38 +11748,43 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Шалапинин</t>
+          <t>Рубцова</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Денис</t>
+          <t>Ольга</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Андреевна</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>shalapinin@theor.jinr.ru</t>
+          <t>rubtsova-olga@yandex.ru</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>Van der Waals dimers of neon</t>
+          <t>Finding virtual states via wave-packet continuum discretization</t>
         </is>
       </c>
     </row>
     <row r="158" ht="188.45" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S5-07</t>
+          <t>S5-08</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11569,43 +11793,43 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Рубцова</t>
+          <t>Мотовилов</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ольга</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Андреевна</t>
+          <t>Константинович</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>rubtsova-olga@yandex.ru</t>
+          <t>motovilv@gmail.com</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>Finding virtual states via wave-packet continuum discretization</t>
+          <t>Resonances of a two-particle system on a 1D lattice</t>
         </is>
       </c>
     </row>
     <row r="159" ht="261" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S5-08</t>
+          <t>S5-09</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11614,88 +11838,88 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Мотовилов</t>
+          <t>Яковлев</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Константинович</t>
+          <t>Леонидович</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>motovilv@gmail.com</t>
+          <t>s.yakovlev@spbu.ru</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>Resonances of a two-particle system on a 1D lattice</t>
+          <t>3-3 рассеяние в системах трёх частиц с короткодействующими и кулоновскими взаимодействиями</t>
         </is>
       </c>
     </row>
     <row r="160" ht="130.5" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S5-09</t>
+          <t>S6-01</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Яковлев</t>
+          <t>Дербин</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Леонидович</t>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ПИЯФ</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>s.yakovlev@spbu.ru</t>
+          <t>derbin_av@pnpi.nrcki.ru</t>
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>3-3 рассеяние в системах трёх частиц с короткодействующими и кулоновскими взаимодействиями</t>
+          <t>Поиск тяжелого стерильного нейтрино в бета-распаде ¹⁴⁴Pr</t>
         </is>
       </c>
     </row>
     <row r="161" ht="246.6" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S6-01</t>
+          <t>S6-02</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11704,43 +11928,43 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Дербин</t>
+          <t>Кондратьев</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Владимир</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>ПИЯФ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>derbin_av@pnpi.nrcki.ru</t>
+          <t>vkondrat@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>Поиск тяжелого стерильного нейтрино в бета-распаде ¹⁴⁴Pr</t>
+          <t>Эффекты динамо и осцилляций в спектрах нейтрино сверхновых</t>
         </is>
       </c>
     </row>
     <row r="162" ht="231.95" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S6-02</t>
+          <t>S6-03</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11749,7 +11973,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11778,14 +12002,14 @@
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>Эффекты динамо и осцилляций в спектрах нейтрино сверхновых</t>
+          <t>Эффекты намагниченности ядер во взрывном нуклеосинтезе</t>
         </is>
       </c>
     </row>
     <row r="163" ht="57.95" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S6-03</t>
+          <t>S6-04</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11794,21 +12018,16 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Кондратьев</t>
+          <t>Лубашевский</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Владимир</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Николаевич</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -11818,19 +12037,19 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>vkondrat@theor.jinr.ru</t>
+          <t>lubashev@jinr.ru</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>Эффекты намагниченности ядер во взрывном нуклеосинтезе</t>
+          <t>Search for rare processes within the νGeN experiment at Kalinin nuclear power plant</t>
         </is>
       </c>
     </row>
     <row r="164" ht="130.5" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S6-04</t>
+          <t>S6-05</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11839,38 +12058,43 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Лубашевский</t>
+          <t>Громов</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Максим</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Борисович</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>lubashev@jinr.ru</t>
+          <t>gromov@physics.msu.ru</t>
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>Search for rare processes within the νGeN experiment at Kalinin nuclear power plant</t>
+          <t>Precise reactor antineutrino spectrum measurement with TAO detector</t>
         </is>
       </c>
     </row>
     <row r="165" ht="101.45" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S6-05</t>
+          <t>S6-06</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11879,21 +12103,21 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Громов</t>
+          <t>Михеев</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Семён</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Алексеевич</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -11903,19 +12127,19 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>gromov@physics.msu.ru</t>
+          <t>semenmihey@gmail.com</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>Precise reactor antineutrino spectrum measurement with TAO detector</t>
+          <t>Условия появления Λ-гиперонов в материи нейтронных звёзд в моделях среднего поля</t>
         </is>
       </c>
     </row>
     <row r="166" ht="217.5" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S6-06</t>
+          <t>S6-07</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11924,43 +12148,38 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Михеев</t>
+          <t>Kabir</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Семён</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Алексеевич</t>
+          <t>Abdul</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>Institute of Space Technology (Islamabad, Pakistan)</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>semenmihey@gmail.com</t>
+          <t>kabirkhanak1@gmail.com</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>Условия появления Λ-гиперонов в материи нейтронных звёзд в моделях среднего поля</t>
+          <t>Analysis of radiative capture of proton ¹¹B (p, γ) ¹²C at low energy</t>
         </is>
       </c>
     </row>
     <row r="167" ht="144.95" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S6-07</t>
+          <t>S6-08</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11969,78 +12188,78 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Le</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Abdul</t>
+          <t>Huy Viet</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Institute of Space Technology (Islamabad, Pakistan)</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>kabirkhanak1@gmail.com</t>
+          <t>leviethuy1@duytan.edu.vn</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>Analysis of radiative capture of proton ¹¹B (p, γ) ¹²C at low energy</t>
+          <t>Characterization of the cosmic muon background in the νGeN experiment</t>
         </is>
       </c>
     </row>
     <row r="168" ht="174" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S6-08</t>
+          <t>S7-01</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Le</t>
+          <t>Киселев</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Huy Viet</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>ОИЯИ</t>
+          <t>Василий</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Алексеевич</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>leviethuy1@duytan.edu.vn</t>
+          <t>kiselevva@fnkcrio.ru</t>
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>Characterization of the cosmic muon background in the νGeN experiment</t>
+          <t>Подход к оптимизации распределения поглощенной дозы в биологическом объекте в лучевой терапии пучком ускоренных протонов</t>
         </is>
       </c>
     </row>
     <row r="169" ht="144.95" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S7-01</t>
+          <t>S7-02</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -12049,38 +12268,43 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Киселев</t>
+          <t>Щербаков</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Василий</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Алексеевич</t>
+          <t>Александрович</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>kiselevva@fnkcrio.ru</t>
+          <t>sherbakov.aa15@physics.msu.ru</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>Подход к оптимизации распределения поглощенной дозы в биологическом объекте в лучевой терапии пучком ускоренных протонов</t>
+          <t>Оценка рисков развития радиационно-индуцированных заболеваний при проведении лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="170" ht="188.45" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S7-02</t>
+          <t>S7-03</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -12089,43 +12313,43 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Щербаков</t>
+          <t>Васильева</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Алина</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Геннадиевна</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>НИЦ КИ ИФВЭ</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>sherbakov.aa15@physics.msu.ru</t>
+          <t>vasilyeva-ag@ihep.ru</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>Оценка рисков развития радиационно-индуцированных заболеваний при проведении лучевой терапии</t>
+          <t>Измерение сечения реакции ¹²C(¹²C,X)¹¹C: особенности эксперимента и оценка неопределенностей</t>
         </is>
       </c>
     </row>
     <row r="171" ht="159.6" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S7-03</t>
+          <t>S7-04</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -12134,21 +12358,21 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Васильева</t>
+          <t>Парменова</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Алина</t>
+          <t>Екатерина</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Геннадиевна</t>
+          <t>Владимировна</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12158,19 +12382,19 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>vasilyeva-ag@ihep.ru</t>
+          <t>Ekaterina.Parmenova@ihep.ru</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>Измерение сечения реакции ¹²C(¹²C,X)¹¹C: особенности эксперимента и оценка неопределенностей</t>
+          <t>Реализация работы с данными КТ в системе планирования ионной лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="172" ht="203.1" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S7-04</t>
+          <t>S7-05</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -12179,43 +12403,43 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Парменова</t>
+          <t>Петров</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Екатерина</t>
+          <t>Виталий</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Владимировна</t>
+          <t>Валерьевич</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>НИЦ КИ ИФВЭ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Ekaterina.Parmenova@ihep.ru</t>
+          <t>vitalii17@bk.ru</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>Реализация работы с данными КТ в системе планирования ионной лучевой терапии</t>
+          <t>Трекинг, измерение энергии и получение диагностических изображений с использованием кремниевых пиксельных сенсоров</t>
         </is>
       </c>
     </row>
     <row r="173" ht="159.6" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S7-05</t>
+          <t>S7-06</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -12224,43 +12448,43 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Петров</t>
+          <t>Мерзликин</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Виталий</t>
+          <t>Григорий</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Валерьевич</t>
+          <t>Васильевич</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>vitalii17@bk.ru</t>
+          <t>grishamerzlikin@gmail.com</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>Трекинг, измерение энергии и получение диагностических изображений с использованием кремниевых пиксельных сенсоров</t>
+          <t>Реконструкция трёхмерного дозового рапсределения при облучении биологических объектов пучками протонов высокой интенсивности</t>
         </is>
       </c>
     </row>
     <row r="174" ht="159.6" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S7-06</t>
+          <t>S7-07</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -12269,21 +12493,21 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Мерзликин</t>
+          <t>Яковлев</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Иван</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -12293,19 +12517,19 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>grishamerzlikin@gmail.com</t>
+          <t>iv.a.yakovlev@gmail.com</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>Реконструкция трёхмерного дозового рапсределения при облучении биологических объектов пучками протонов высокой интенсивности</t>
+          <t>Расчет характеристик черенковского детектора для контроля пучков протонов, используемых для флэш-терапии</t>
         </is>
       </c>
     </row>
     <row r="175" ht="290.1" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S7-07</t>
+          <t>S7-08</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -12314,43 +12538,43 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Яковлев</t>
+          <t>Зябченков</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Владислав</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Олегович</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>iv.a.yakovlev@gmail.com</t>
+          <t>vladislavzyabchenkov@mail.ru</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>Расчет характеристик черенковского детектора для контроля пучков протонов, используемых для флэш-терапии</t>
+          <t>Количественная оценка содержания тория и урана в свинце для радиационной защиты методом ИСП-МС</t>
         </is>
       </c>
     </row>
     <row r="176" ht="231.95" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S7-08</t>
+          <t>S7-09</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -12359,43 +12583,43 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Зябченков</t>
+          <t>Копылова</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Владислав</t>
+          <t>Екатерина</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Олегович</t>
+          <t>Александровна</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>vladislavzyabchenkov@mail.ru</t>
+          <t>ekaterinakalip@gmail.com</t>
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>Количественная оценка содержания тория и урана в свинце для радиационной защиты методом ИСП-МС</t>
+          <t>Применение деформируемой регистрации изображений в лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="177" ht="217.5" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S7-09</t>
+          <t>S7-10</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -12404,43 +12628,38 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Копылова</t>
+          <t>Мамаева</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Екатерина</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Александровна</t>
+          <t>Саргылана</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>СФВУ (Якутия)</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>ekaterinakalip@gmail.com</t>
+          <t>sargylana_mamaeva@mail.ru</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>Применение деформируемой регистрации изображений в лучевой терапии</t>
+          <t>Биофизическая модель электрических характеристик эритроцитов при лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="178" ht="174" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S7-10</t>
+          <t>S7-11</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12449,38 +12668,43 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Мамаева</t>
+          <t>Мерзликин</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Саргылана</t>
+          <t>Григорий</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Васильевич</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>СФВУ (Якутия)</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>sargylana_mamaeva@mail.ru</t>
+          <t>grishamerzlikin@gmail.com</t>
         </is>
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>Биофизическая модель электрических характеристик эритроцитов при лучевой терапии</t>
+          <t>Корректировка и валидация алгоритма оценки прбега протонов в различных матералах на основании КТ-исследований</t>
         </is>
       </c>
     </row>
     <row r="179" ht="318.95" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S7-11</t>
+          <t>S7-12</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12489,43 +12713,43 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Мерзликин</t>
+          <t>Ашрапов</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Улугбек</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Товфикович</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>INR Uzbekistan</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>grishamerzlikin@gmail.com</t>
+          <t>ashrapov@inp.uz</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>Корректировка и валидация алгоритма оценки прбега протонов в различных матералах на основании КТ-исследований</t>
+          <t>Использование гамма-облученного оксида алюминия для изготовления генераторов технеция-99М</t>
         </is>
       </c>
     </row>
     <row r="180" ht="318.95" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S7-12</t>
+          <t>S7-13</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12534,43 +12758,38 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Ашрапов</t>
+          <t>Кузьменков</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Улугбек</t>
+          <t>Антон</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Товфикович</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>INR Uzbekistan</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>ashrapov@inp.uz</t>
+          <t>zhelton@yandex.ru</t>
         </is>
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>Использование гамма-облученного оксида алюминия для изготовления генераторов технеция-99М</t>
+          <t>Фотоядерное получение медицинских изотопов рения на осмиевых и иридиевых мишенях</t>
         </is>
       </c>
     </row>
     <row r="181" ht="231.95" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S7-13</t>
+          <t>S7-14</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12579,38 +12798,38 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Кузьменков</t>
+          <t>Yusupov</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Антон</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Александрович</t>
+          <t>Mirjalol</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>zhelton@yandex.ru</t>
+          <t>ymirjalol@bk.ru</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>Фотоядерное получение медицинских изотопов рения на осмиевых и иридиевых мишенях</t>
+          <t>Ядерные реакции на кислороде, углероде, азоте и боре при облучении протонным пучком 160 МэВ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="217.5" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>S7-14</t>
+          <t>S7-15</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12619,38 +12838,43 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Yusupov</t>
+          <t>Пятаев</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Mirjalol</t>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>МКНЦ, МГУ</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>ymirjalol@bk.ru</t>
+          <t>pataevdima2@gmail.com</t>
         </is>
       </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>Ядерные реакции на кислороде, углероде, азоте и боре при облучении протонным пучком 160 МэВ</t>
+          <t>Исследование влияния термопластических масок на поверхностную дозу и дозовое распределение в лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="183" ht="159.6" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>S7-15</t>
+          <t>S7-16</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12659,43 +12883,43 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Пятаев</t>
+          <t>Оганян</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Ваге</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Робертович</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>МКНЦ, МГУ</t>
+          <t>МИФИ, МКНЦ</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>pataevdima2@gmail.com</t>
+          <t>vahe.ohanyan2000@yandex.ru</t>
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>Исследование влияния термопластических масок на поверхностную дозу и дозовое распределение в лучевой терапии</t>
+          <t>Биофизическое моделирование распределения температуры при гипертермии: обзор алгоритмов и проектирование расчётного модуля.</t>
         </is>
       </c>
     </row>
     <row r="184" ht="174" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>S7-16</t>
+          <t>S7-17</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12704,43 +12928,43 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Оганян</t>
+          <t>Онищук</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ваге</t>
+          <t>Елена</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Робертович</t>
+          <t>Александровна</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>МИФИ, МКНЦ</t>
+          <t>ИАЭ Обнинск</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>vahe.ohanyan2000@yandex.ru</t>
+          <t>elenaonischuk@yandex.ru</t>
         </is>
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>Биофизическое моделирование распределения температуры при гипертермии: обзор алгоритмов и проектирование расчётного модуля.</t>
+          <t>Optimization of photoneutron source parameters for boron neutron capture therapy</t>
         </is>
       </c>
     </row>
     <row r="185" ht="275.45" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>S7-17</t>
+          <t>S7-18</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12749,43 +12973,43 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Онищук</t>
+          <t>Балачков</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Максим</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Александровна</t>
+          <t>Михайлович</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>ИАЭ Обнинск</t>
+          <t>ТПУ (Томск)</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>elenaonischuk@yandex.ru</t>
+          <t>mmb2@tpu.ru</t>
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>Optimization of photoneutron source parameters for boron neutron capture therapy</t>
+          <t>Спектральные измерения пучка быстрых нейтронов циклотрона У-120</t>
         </is>
       </c>
     </row>
     <row r="186" ht="203.1" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>S7-18</t>
+          <t>S7-19</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12794,43 +13018,43 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Балачков</t>
+          <t>Сабуров</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Вячеслав</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Михайлович</t>
+          <t>Олегович</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>ТПУ (Томск)</t>
+          <t>МРНЦ им. А.Ф. Цыба</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>mmb2@tpu.ru</t>
+          <t>vosaburov@gmail.com</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>Спектральные измерения пучка быстрых нейтронов циклотрона У-120</t>
+          <t>Статус проекта по созданию комплекса нейтронной терапии на базе компактного нейтронного генератора НГ-24МТ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="217.5" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>S7-19</t>
+          <t>S7-20</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12839,21 +13063,21 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Сабуров</t>
+          <t>Соловьев</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Вячеслав</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Олегович</t>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -12863,19 +13087,19 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>vosaburov@gmail.com</t>
+          <t>salonf@mrrc.obninsk.ru</t>
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>Статус проекта по созданию комплекса нейтронной терапии на базе компактного нейтронного генератора НГ-24МТ</t>
+          <t>Особенности вычислительного прогнозирования отклика ионизационных камер для радиотерапевтического применения</t>
         </is>
       </c>
     </row>
     <row r="188" ht="231.95" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>S7-20</t>
+          <t>S7-21</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12884,43 +13108,43 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Соловьев</t>
+          <t>Хуцистова</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Алана</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Отариевна</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>МРНЦ им. А.Ф. Цыба</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>salonf@mrrc.obninsk.ru</t>
+          <t>www.alanakhutS1@mail.ru</t>
         </is>
       </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>Особенности вычислительного прогнозирования отклика ионизационных камер для радиотерапевтического применения</t>
+          <t>Моделирование комбинированного воздействия ионизирующего излучения и озона для стерилизации биоматериалов</t>
         </is>
       </c>
     </row>
     <row r="189" ht="246.6" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>S7-21</t>
+          <t>S7-22</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12929,21 +13153,21 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Хуцистова</t>
+          <t>Запорожская</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Алана</t>
+          <t>Ксения</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Отариевна</t>
+          <t>Васильевна</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -12953,19 +13177,19 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>www.alanakhutS1@mail.ru</t>
+          <t>zaporozhskayakv@my.msu.ru</t>
         </is>
       </c>
       <c r="I189" s="4" t="inlineStr">
         <is>
-          <t>Моделирование комбинированного воздействия ионизирующего излучения и озона для стерилизации биоматериалов</t>
+          <t>Применение шумоподавляющих фильтров при плёночной дозиметрии радиохирургических планов лечения</t>
         </is>
       </c>
     </row>
     <row r="190" ht="304.5" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>S7-22</t>
+          <t>S7-23</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12974,21 +13198,21 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Запорожская</t>
+          <t>Новикова</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Ксения</t>
+          <t>Евгения</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Васильевна</t>
+          <t>Антоновна</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -12998,19 +13222,19 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>zaporozhskayakv@my.msu.ru</t>
+          <t>evgeniyanovikovazar@gmail.com</t>
         </is>
       </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
-          <t>Применение шумоподавляющих фильтров при плёночной дозиметрии радиохирургических планов лечения</t>
+          <t>Методика дозиметрии источника для электронной поверхностной брахитерапии</t>
         </is>
       </c>
     </row>
     <row r="191" ht="159.6" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>S7-23</t>
+          <t>S7-24</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -13019,84 +13243,40 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Новикова</t>
+          <t>Петрова</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Евгения</t>
+          <t>Кристина</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Антоновна</t>
+          <t>Алексеевна</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>СФВУ (Якутия)</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>evgeniyanovikovazar@gmail.com</t>
+          <t>kristinan_1604@mail.ru</t>
         </is>
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t>Методика дозиметрии источника для электронной поверхностной брахитерапии</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="174" customHeight="1">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>S7-24</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
-        <v>24</v>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Петрова</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Кристина</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Алексеевна</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>СФВУ (Якутия)</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>kristinan_1604@mail.ru</t>
-        </is>
-      </c>
-      <c r="I192" s="4" t="inlineStr">
-        <is>
           <t>Накопление золошлаковых отходов и выбросов котельного комплекса и рост онкологической заболеваемости</t>
         </is>
       </c>
     </row>
+    <row r="192" ht="174" customHeight="1"/>
     <row r="193" ht="261" customHeight="1"/>
     <row r="194" ht="261" customHeight="1"/>
     <row r="195" ht="290.1" customHeight="1"/>
@@ -13119,7 +13299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14845,6 +15025,48 @@
       <c r="H48" t="inlineStr">
         <is>
           <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>POST-48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Мальцев</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Николай</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Александрович</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>СПбГУ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>n.maltsev@spbu.ru</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Особенности изучения свойств пучков тяжёлых ионов высоких энергий</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -14864,7 +15086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14948,6 +15170,21 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>46283.86111111111</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Председатели секционных заседаний. Доклад Н. А. Мальцева перенесён в постерную сессию. Время постеров 23.09, 16:45–18:00.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Section session chairs published. N. A. Maltsev’s talk moved to the poster session. Poster session time 23 Sep, 16:45–18:00.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/programme.xlsx
+++ b/data/programme.xlsx
@@ -79,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -96,6 +96,9 @@
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3270,8 +3273,6 @@
           <t>холл2</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -5643,10 +5644,8 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="C20" t="n">
+        <v>31</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6438,10 +6437,8 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="C36" t="n">
+        <v>14</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -8031,7 +8028,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8164,10 +8161,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C75" t="n">
+        <v>8</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10927,7 +10922,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>НИЦ КИ-ПИЯФ</t>
+          <t>НИЦ КИ-ПИЯФ, СПбПУ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -15086,7 +15081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15185,6 +15180,21 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>46286.56041666667</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Перестановки докладов: И. Н. Изосимов (секция 2) и Е. А. Шевчик поменялись местами во вторник; пленарные М. И. Шитова и А. Ефимова — среда и суббота. Организация Д. А. Иванищева: НИЦ КИ-ПИЯФ, СПбПУ.</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Talks swapped: I. N. Izosimov (section 2) and E. A. Shevchik on Tuesday; plenaries of M. I. Shitov and A. Efimov — Wednesday and Saturday. Affiliation of D. A. Ivanishchev: NRC KI–PNPI, SPbPU.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/programme.xlsx
+++ b/data/programme.xlsx
@@ -1301,6 +1301,11 @@
           <t>Coffee break</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>235ц</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1761,6 +1766,11 @@
           <t>Coffee break</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>235ц</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -2130,6 +2140,11 @@
           <t>Coffee break</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>235ц</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2499,6 +2514,11 @@
           <t>Coffee break</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>235ц</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -2873,6 +2893,11 @@
           <t>Coffee break</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>235ц</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -3242,6 +3267,11 @@
           <t>Coffee break</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>235ц</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -3452,6 +3482,11 @@
           <t>Coffee break</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>235ц</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3872,6 +3907,11 @@
           <t>Coffee break</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>235ц</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -4241,6 +4281,11 @@
           <t>Coffee break</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>235ц</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -4541,6 +4586,11 @@
       <c r="F83" t="inlineStr">
         <is>
           <t>Coffee break</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>235ц</t>
         </is>
       </c>
     </row>

--- a/data/programme.xlsx
+++ b/data/programme.xlsx
@@ -20,13 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
     <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy\ hh:mm"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd\ hh:mm"/>
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="170" formatCode="HH:MM"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -79,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -99,6 +100,7 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1022,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2456,7 +2458,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.65625</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2470,7 +2472,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8-14</t>
+          <t>8,10-13</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2651,7 +2653,7 @@
         <v>0.6770833333333334</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.75</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2665,7 +2667,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>15-21</t>
+          <t>18-19</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3209,7 +3211,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.65625</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3223,7 +3225,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1-8</t>
+          <t>1-7</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4201,7 +4203,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>117л</t>
+          <t>315л</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4295,7 +4297,7 @@
         <v>0.6770833333333334</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>0.75</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4309,12 +4311,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>22-27</t>
+          <t>22-26</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>117л</t>
+          <t>315л</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4377,7 +4379,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.65625</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4391,12 +4393,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>22-24</t>
+          <t>22-28</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>315л</t>
+          <t>117л</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4622,6 +4624,47 @@
       <c r="I84" t="inlineStr">
         <is>
           <t>235ц</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B85" s="11" t="n">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="C85" s="11" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>секция</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>29-32</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>117л</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>С. Мамаева</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>S. Mamaeva</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S191"/>
+  <dimension ref="A1:S190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10321,11 +10364,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11919,7 +11962,7 @@
     <row r="160" ht="130.5" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S6-01</t>
+          <t>S6-02</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11932,39 +11975,39 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Дербин</t>
+          <t>Кондратьев</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Владимир</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>ПИЯФ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>derbin_av@pnpi.nrcki.ru</t>
+          <t>vkondrat@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>Поиск тяжелого стерильного нейтрино в бета-распаде ¹⁴⁴Pr</t>
+          <t>Эффекты динамо и осцилляций в спектрах нейтрино сверхновых</t>
         </is>
       </c>
     </row>
     <row r="161" ht="246.6" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S6-02</t>
+          <t>S6-03</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12002,14 +12045,14 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>Эффекты динамо и осцилляций в спектрах нейтрино сверхновых</t>
+          <t>Эффекты намагниченности ядер во взрывном нуклеосинтезе</t>
         </is>
       </c>
     </row>
     <row r="162" ht="231.95" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S6-03</t>
+          <t>S6-04</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12022,17 +12065,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Кондратьев</t>
+          <t>Лубашевский</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Владимир</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Николаевич</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12042,19 +12080,19 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>vkondrat@theor.jinr.ru</t>
+          <t>lubashev@jinr.ru</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>Эффекты намагниченности ядер во взрывном нуклеосинтезе</t>
+          <t>Search for rare processes within the νGeN experiment at Kalinin nuclear power plant</t>
         </is>
       </c>
     </row>
     <row r="163" ht="57.95" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S6-04</t>
+          <t>S6-05</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12067,34 +12105,39 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Лубашевский</t>
+          <t>Громов</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Максим</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Борисович</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>lubashev@jinr.ru</t>
+          <t>gromov@physics.msu.ru</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>Search for rare processes within the νGeN experiment at Kalinin nuclear power plant</t>
+          <t>Precise reactor antineutrino spectrum measurement with TAO detector</t>
         </is>
       </c>
     </row>
     <row r="164" ht="130.5" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S6-05</t>
+          <t>S6-06</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12107,17 +12150,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Громов</t>
+          <t>Михеев</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Семён</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Алексеевич</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12127,19 +12170,19 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>gromov@physics.msu.ru</t>
+          <t>semenmihey@gmail.com</t>
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>Precise reactor antineutrino spectrum measurement with TAO detector</t>
+          <t>Условия появления Λ-гиперонов в материи нейтронных звёзд в моделях среднего поля</t>
         </is>
       </c>
     </row>
     <row r="165" ht="101.45" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S6-06</t>
+          <t>S6-07</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12152,39 +12195,34 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Михеев</t>
+          <t>Kabir</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Семён</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Алексеевич</t>
+          <t>Abdul</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>Institute of Space Technology (Islamabad, Pakistan)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>semenmihey@gmail.com</t>
+          <t>kabirkhanak1@gmail.com</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>Условия появления Λ-гиперонов в материи нейтронных звёзд в моделях среднего поля</t>
+          <t>Analysis of radiative capture of proton ¹¹B (p, γ) ¹²C at low energy</t>
         </is>
       </c>
     </row>
     <row r="166" ht="217.5" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S6-07</t>
+          <t>S6-08</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12197,74 +12235,74 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Le</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Abdul</t>
+          <t>Huy Viet</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Institute of Space Technology (Islamabad, Pakistan)</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>kabirkhanak1@gmail.com</t>
+          <t>leviethuy1@duytan.edu.vn</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>Analysis of radiative capture of proton ¹¹B (p, γ) ¹²C at low energy</t>
+          <t>Characterization of the cosmic muon background in the νGeN experiment</t>
         </is>
       </c>
     </row>
     <row r="167" ht="144.95" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S6-08</t>
+          <t>S7-01</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Le</t>
+          <t>Киселев</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Huy Viet</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>ОИЯИ</t>
+          <t>Василий</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Алексеевич</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>leviethuy1@duytan.edu.vn</t>
+          <t>kiselevva@fnkcrio.ru</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>Characterization of the cosmic muon background in the νGeN experiment</t>
+          <t>Подход к оптимизации распределения поглощенной дозы в биологическом объекте в лучевой терапии пучком ускоренных протонов</t>
         </is>
       </c>
     </row>
     <row r="168" ht="174" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S7-01</t>
+          <t>S7-02</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12273,38 +12311,43 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Киселев</t>
+          <t>Щербаков</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Василий</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Алексеевич</t>
+          <t>Александрович</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>kiselevva@fnkcrio.ru</t>
+          <t>sherbakov.aa15@physics.msu.ru</t>
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>Подход к оптимизации распределения поглощенной дозы в биологическом объекте в лучевой терапии пучком ускоренных протонов</t>
+          <t>Оценка рисков развития радиационно-индуцированных заболеваний при проведении лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="169" ht="144.95" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S7-02</t>
+          <t>S7-03</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -12313,43 +12356,43 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Щербаков</t>
+          <t>Васильева</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Алина</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Геннадиевна</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>НИЦ КИ ИФВЭ</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>sherbakov.aa15@physics.msu.ru</t>
+          <t>vasilyeva-ag@ihep.ru</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>Оценка рисков развития радиационно-индуцированных заболеваний при проведении лучевой терапии</t>
+          <t>Измерение сечения реакции ¹²C(¹²C,X)¹¹C: особенности эксперимента и оценка неопределенностей</t>
         </is>
       </c>
     </row>
     <row r="170" ht="188.45" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S7-03</t>
+          <t>S7-04</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -12358,21 +12401,21 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Васильева</t>
+          <t>Парменова</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Алина</t>
+          <t>Екатерина</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Геннадиевна</t>
+          <t>Владимировна</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12382,19 +12425,19 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>vasilyeva-ag@ihep.ru</t>
+          <t>Ekaterina.Parmenova@ihep.ru</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>Измерение сечения реакции ¹²C(¹²C,X)¹¹C: особенности эксперимента и оценка неопределенностей</t>
+          <t>Реализация работы с данными КТ в системе планирования ионной лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="171" ht="159.6" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S7-04</t>
+          <t>S7-05</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -12403,43 +12446,43 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Парменова</t>
+          <t>Петров</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Екатерина</t>
+          <t>Виталий</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Владимировна</t>
+          <t>Валерьевич</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>НИЦ КИ ИФВЭ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Ekaterina.Parmenova@ihep.ru</t>
+          <t>vitalii17@bk.ru</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>Реализация работы с данными КТ в системе планирования ионной лучевой терапии</t>
+          <t>Трекинг, измерение энергии и получение диагностических изображений с использованием кремниевых пиксельных сенсоров</t>
         </is>
       </c>
     </row>
     <row r="172" ht="203.1" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S7-05</t>
+          <t>S7-06</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -12448,43 +12491,43 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Петров</t>
+          <t>Мерзликин</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Виталий</t>
+          <t>Григорий</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Валерьевич</t>
+          <t>Васильевич</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>vitalii17@bk.ru</t>
+          <t>grishamerzlikin@gmail.com</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>Трекинг, измерение энергии и получение диагностических изображений с использованием кремниевых пиксельных сенсоров</t>
+          <t>Реконструкция трёхмерного дозового рапсределения при облучении биологических объектов пучками протонов высокой интенсивности</t>
         </is>
       </c>
     </row>
     <row r="173" ht="159.6" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S7-06</t>
+          <t>S7-07</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -12493,21 +12536,21 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Мерзликин</t>
+          <t>Яковлев</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Иван</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12517,19 +12560,19 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>grishamerzlikin@gmail.com</t>
+          <t>iv.a.yakovlev@gmail.com</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>Реконструкция трёхмерного дозового рапсределения при облучении биологических объектов пучками протонов высокой интенсивности</t>
+          <t>Расчет характеристик черенковского детектора для контроля пучков протонов, используемых для флэш-терапии</t>
         </is>
       </c>
     </row>
     <row r="174" ht="159.6" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S7-07</t>
+          <t>S7-08</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -12538,43 +12581,43 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Яковлев</t>
+          <t>Зябченков</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Владислав</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Олегович</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>iv.a.yakovlev@gmail.com</t>
+          <t>vladislavzyabchenkov@mail.ru</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>Расчет характеристик черенковского детектора для контроля пучков протонов, используемых для флэш-терапии</t>
+          <t>Количественная оценка содержания тория и урана в свинце для радиационной защиты методом ИСП-МС</t>
         </is>
       </c>
     </row>
     <row r="175" ht="290.1" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S7-08</t>
+          <t>S7-09</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -12583,43 +12626,43 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Зябченков</t>
+          <t>Копылова</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Владислав</t>
+          <t>Екатерина</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Олегович</t>
+          <t>Александровна</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>vladislavzyabchenkov@mail.ru</t>
+          <t>ekaterinakalip@gmail.com</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>Количественная оценка содержания тория и урана в свинце для радиационной защиты методом ИСП-МС</t>
+          <t>Применение деформируемой регистрации изображений в лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="176" ht="231.95" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S7-09</t>
+          <t>S7-10</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -12628,43 +12671,38 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Копылова</t>
+          <t>Мамаева</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Екатерина</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Александровна</t>
+          <t>Саргылана</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>СФВУ (Якутия)</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>ekaterinakalip@gmail.com</t>
+          <t>sargylana_mamaeva@mail.ru</t>
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>Применение деформируемой регистрации изображений в лучевой терапии</t>
+          <t>Биофизическая модель электрических характеристик эритроцитов при лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="177" ht="217.5" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S7-10</t>
+          <t>S7-11</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -12673,38 +12711,43 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Мамаева</t>
+          <t>Мерзликин</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Саргылана</t>
+          <t>Григорий</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Васильевич</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>СФВУ (Якутия)</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>sargylana_mamaeva@mail.ru</t>
+          <t>grishamerzlikin@gmail.com</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>Биофизическая модель электрических характеристик эритроцитов при лучевой терапии</t>
+          <t>Корректировка и валидация алгоритма оценки прбега протонов в различных матералах на основании КТ-исследований</t>
         </is>
       </c>
     </row>
     <row r="178" ht="174" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S7-11</t>
+          <t>S7-12</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12713,43 +12756,43 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Мерзликин</t>
+          <t>Ашрапов</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Улугбек</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Товфикович</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>INR Uzbekistan</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>grishamerzlikin@gmail.com</t>
+          <t>ashrapov@inp.uz</t>
         </is>
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>Корректировка и валидация алгоритма оценки прбега протонов в различных матералах на основании КТ-исследований</t>
+          <t>Использование гамма-облученного оксида алюминия для изготовления генераторов технеция-99М</t>
         </is>
       </c>
     </row>
     <row r="179" ht="318.95" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S7-12</t>
+          <t>S7-13</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12758,43 +12801,38 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Ашрапов</t>
+          <t>Кузьменков</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Улугбек</t>
+          <t>Антон</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Товфикович</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>INR Uzbekistan</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>ashrapov@inp.uz</t>
+          <t>zhelton@yandex.ru</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>Использование гамма-облученного оксида алюминия для изготовления генераторов технеция-99М</t>
+          <t>Фотоядерное получение медицинских изотопов рения на осмиевых и иридиевых мишенях</t>
         </is>
       </c>
     </row>
     <row r="180" ht="318.95" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S7-13</t>
+          <t>S7-14</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12803,38 +12841,38 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Кузьменков</t>
+          <t>Yusupov</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Антон</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Александрович</t>
+          <t>Mirjalol</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>zhelton@yandex.ru</t>
+          <t>ymirjalol@bk.ru</t>
         </is>
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>Фотоядерное получение медицинских изотопов рения на осмиевых и иридиевых мишенях</t>
+          <t>Ядерные реакции на кислороде, углероде, азоте и боре при облучении протонным пучком 160 МэВ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="231.95" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S7-14</t>
+          <t>S7-15</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12843,38 +12881,43 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Yusupov</t>
+          <t>Пятаев</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Mirjalol</t>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>МКНЦ, МГУ</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>ymirjalol@bk.ru</t>
+          <t>pataevdima2@gmail.com</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>Ядерные реакции на кислороде, углероде, азоте и боре при облучении протонным пучком 160 МэВ</t>
+          <t>Исследование влияния термопластических масок на поверхностную дозу и дозовое распределение в лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="182" ht="217.5" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>S7-15</t>
+          <t>S7-16</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12883,43 +12926,43 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Пятаев</t>
+          <t>Оганян</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Ваге</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Робертович</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>МКНЦ, МГУ</t>
+          <t>МИФИ, МКНЦ</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>pataevdima2@gmail.com</t>
+          <t>vahe.ohanyan2000@yandex.ru</t>
         </is>
       </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>Исследование влияния термопластических масок на поверхностную дозу и дозовое распределение в лучевой терапии</t>
+          <t>Биофизическое моделирование распределения температуры при гипертермии: обзор алгоритмов и проектирование расчётного модуля.</t>
         </is>
       </c>
     </row>
     <row r="183" ht="159.6" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>S7-16</t>
+          <t>S7-17</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12928,43 +12971,43 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Оганян</t>
+          <t>Онищук</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ваге</t>
+          <t>Елена</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Робертович</t>
+          <t>Александровна</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>МИФИ, МКНЦ</t>
+          <t>ИАЭ Обнинск</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>vahe.ohanyan2000@yandex.ru</t>
+          <t>elenaonischuk@yandex.ru</t>
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>Биофизическое моделирование распределения температуры при гипертермии: обзор алгоритмов и проектирование расчётного модуля.</t>
+          <t>Optimization of photoneutron source parameters for boron neutron capture therapy</t>
         </is>
       </c>
     </row>
     <row r="184" ht="174" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>S7-17</t>
+          <t>S7-18</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12973,43 +13016,43 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Онищук</t>
+          <t>Балачков</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Максим</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Александровна</t>
+          <t>Михайлович</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>ИАЭ Обнинск</t>
+          <t>ТПУ (Томск)</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>elenaonischuk@yandex.ru</t>
+          <t>mmb2@tpu.ru</t>
         </is>
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>Optimization of photoneutron source parameters for boron neutron capture therapy</t>
+          <t>Спектральные измерения пучка быстрых нейтронов циклотрона У-120</t>
         </is>
       </c>
     </row>
     <row r="185" ht="275.45" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>S7-18</t>
+          <t>S7-19</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -13018,43 +13061,43 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Балачков</t>
+          <t>Сабуров</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Вячеслав</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Михайлович</t>
+          <t>Олегович</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>ТПУ (Томск)</t>
+          <t>МРНЦ им. А.Ф. Цыба</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>mmb2@tpu.ru</t>
+          <t>vosaburov@gmail.com</t>
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>Спектральные измерения пучка быстрых нейтронов циклотрона У-120</t>
+          <t>Статус проекта по созданию комплекса нейтронной терапии на базе компактного нейтронного генератора НГ-24МТ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="203.1" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>S7-19</t>
+          <t>S7-20</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -13063,21 +13106,21 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Сабуров</t>
+          <t>Соловьев</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Вячеслав</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Олегович</t>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13087,19 +13130,19 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>vosaburov@gmail.com</t>
+          <t>salonf@mrrc.obninsk.ru</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>Статус проекта по созданию комплекса нейтронной терапии на базе компактного нейтронного генератора НГ-24МТ</t>
+          <t>Особенности вычислительного прогнозирования отклика ионизационных камер для радиотерапевтического применения</t>
         </is>
       </c>
     </row>
     <row r="187" ht="217.5" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>S7-20</t>
+          <t>S7-21</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -13108,43 +13151,43 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Соловьев</t>
+          <t>Хуцистова</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Алана</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Отариевна</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>МРНЦ им. А.Ф. Цыба</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>salonf@mrrc.obninsk.ru</t>
+          <t>www.alanakhutS1@mail.ru</t>
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>Особенности вычислительного прогнозирования отклика ионизационных камер для радиотерапевтического применения</t>
+          <t>Моделирование комбинированного воздействия ионизирующего излучения и озона для стерилизации биоматериалов</t>
         </is>
       </c>
     </row>
     <row r="188" ht="231.95" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>S7-21</t>
+          <t>S7-22</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -13153,21 +13196,21 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Хуцистова</t>
+          <t>Запорожская</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Алана</t>
+          <t>Ксения</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Отариевна</t>
+          <t>Васильевна</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -13177,19 +13220,19 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>www.alanakhutS1@mail.ru</t>
+          <t>zaporozhskayakv@my.msu.ru</t>
         </is>
       </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>Моделирование комбинированного воздействия ионизирующего излучения и озона для стерилизации биоматериалов</t>
+          <t>Применение шумоподавляющих фильтров при плёночной дозиметрии радиохирургических планов лечения</t>
         </is>
       </c>
     </row>
     <row r="189" ht="246.6" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>S7-22</t>
+          <t>S7-23</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -13198,21 +13241,21 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Запорожская</t>
+          <t>Новикова</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ксения</t>
+          <t>Евгения</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Васильевна</t>
+          <t>Антоновна</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -13222,19 +13265,19 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>zaporozhskayakv@my.msu.ru</t>
+          <t>evgeniyanovikovazar@gmail.com</t>
         </is>
       </c>
       <c r="I189" s="4" t="inlineStr">
         <is>
-          <t>Применение шумоподавляющих фильтров при плёночной дозиметрии радиохирургических планов лечения</t>
+          <t>Методика дозиметрии источника для электронной поверхностной брахитерапии</t>
         </is>
       </c>
     </row>
     <row r="190" ht="304.5" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>S7-23</t>
+          <t>S7-24</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -13243,84 +13286,40 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Новикова</t>
+          <t>Петрова</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Евгения</t>
+          <t>Кристина</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Антоновна</t>
+          <t>Алексеевна</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>СФВУ (Якутия)</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>evgeniyanovikovazar@gmail.com</t>
+          <t>kristinan_1604@mail.ru</t>
         </is>
       </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
-          <t>Методика дозиметрии источника для электронной поверхностной брахитерапии</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="159.6" customHeight="1">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>S7-24</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>24</v>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Петрова</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Кристина</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Алексеевна</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>СФВУ (Якутия)</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>kristinan_1604@mail.ru</t>
-        </is>
-      </c>
-      <c r="I191" s="4" t="inlineStr">
-        <is>
           <t>Накопление золошлаковых отходов и выбросов котельного комплекса и рост онкологической заболеваемости</t>
         </is>
       </c>
     </row>
+    <row r="191" ht="159.6" customHeight="1"/>
     <row r="192" ht="174" customHeight="1"/>
     <row r="193" ht="261" customHeight="1"/>
     <row r="194" ht="261" customHeight="1"/>
@@ -15131,7 +15130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15245,6 +15244,51 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>46287.68680555555</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>А. В. Дербин не приедет: его доклад снят, секция 6 в среду начинается в 14:00 без него. В пятницу секция 3 — в 315л, секция 7 — в 117л.</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>A. V. Derbin will not attend: his talk is removed, and section 6 on Wednesday starts at 14:00 without it. On Friday, section 3 is in 315л and section 7 is in 117л.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>46287.71666666667</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Секция 7: Е. А. Копылова, M. Yusupov, Д. Н. Пятаев и В. Р. Оганян перенесены на пятницу, 14:45–15:45, после уже стоящих докладов. Остальные доклады секции 7 во вторник сдвинуты вперёд.</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Section 7: E. A. Kopylova, M. Yusupov, D. N. Pyataev and V. R. Ohanyan are moved to Friday 14:45–15:45, after the existing section 7 talks. The other Tuesday section 7 talks move up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>46287.73333333333</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Секция 7 в пятницу после кофе, 16:15–17:15, 117л: А. С. Петровская, затем Е. А. Онищук, А. Н. Соловьев и А. О. Хуцистова. Вечерняя секция 7 во вторник сокращена.</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Section 7 on Friday after coffee, 16:15–17:15, room 117л: A. S. Petrovskaya, then E. A. Onishchuk, A. N. Solovyev and A. O. Khutsistova. Tuesday evening section 7 is shortened.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/programme.xlsx
+++ b/data/programme.xlsx
@@ -20,7 +20,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
     <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy\ hh:mm"/>
@@ -28,6 +28,7 @@
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="170" formatCode="HH:MM"/>
+    <numFmt numFmtId="171" formatCode="DD.MM.YYYY HH:MM"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -80,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -101,6 +102,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15130,7 +15132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15289,6 +15291,21 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>46287.83541666667</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>В «Сетке» выделите день и нажмите «Подробный день»: время, аудитории и председатели заседаний. Печать этого дня — один альбомный лист A4.</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>In Overview, highlight a day and press Detailed day for times, rooms, and sitting chairs. Print that day as one landscape A4.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/programme.xlsx
+++ b/data/programme.xlsx
@@ -3676,10 +3676,10 @@
         <v>46289</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>0.625</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15306,6 +15306,21 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>46288.56111111111</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Экскурсия на теплоходе в четверг перенесена на 15:30–18:30.</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Thursday boat excursion moved to 15:30–18:30.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/programme.xlsx
+++ b/data/programme.xlsx
@@ -4104,7 +4104,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.625</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>23-27</t>
+          <t>23,25-27</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4686,7 +4686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S190"/>
+  <dimension ref="A1:S189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7667,7 +7667,7 @@
     <row r="62" ht="261" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S1-24</t>
+          <t>S1-25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7676,43 +7676,38 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Кострюков</t>
+          <t>Стегайлов</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Павел</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Владимирович</t>
+          <t>Владимир</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ВГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>kostryukov@phys.vsu.ru</t>
+          <t>stega@jinr.ru</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>Устойчивость оболочечной структуры сверхтяжёлых ядер в деформированных потенциалах Нильсона и Вудса–Саксона</t>
+          <t>Исследование структуры и изомерии ядер гольмия</t>
         </is>
       </c>
     </row>
     <row r="63" ht="101.45" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S1-25</t>
+          <t>S1-26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7721,16 +7716,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Стегайлов</t>
+          <t>Моисеев</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -7740,19 +7735,19 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stega@jinr.ru</t>
+          <t>moiseev@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>Исследование структуры и изомерии ядер гольмия</t>
+          <t>Эмпирическая систематика периодов полураспада спонтанного деления и альфа-распада тяжелых и сверхтяжелых ядер</t>
         </is>
       </c>
     </row>
     <row r="64" ht="261" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S1-26</t>
+          <t>S1-27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7761,16 +7756,21 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Моисеев</t>
+          <t>Молодцова</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Ирина</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Владимировна</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -7780,64 +7780,66 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>moiseev@theor.jinr.ru</t>
+          <t>molod@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>Эмпирическая систематика периодов полураспада спонтанного деления и альфа-распада тяжелых и сверхтяжелых ядер</t>
+          <t>Transition densities of spin-dipole excitations in ²⁰⁸Pb</t>
         </is>
       </c>
     </row>
     <row r="65" ht="116.1" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S1-27</t>
+          <t>S2-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>27</v>
-      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Молодцова</t>
+          <t>Демьянова</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ирина</t>
+          <t>Алла</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Владимировна</t>
+          <t>Сергеевна</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИЦ КИ</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>molod@theor.jinr.ru</t>
+          <t>a.s.demyanova@bk.ru</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>Transition densities of spin-dipole excitations in ²⁰⁸Pb</t>
+          <t>Анализ реакции срыва ¹³C(d,t)¹²C в области энергий 13–18 мэв: определение асимптотических нормировочных коэффициентов и структуры состояний ядра ¹²C</t>
         </is>
       </c>
     </row>
     <row r="66" ht="174" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S2-02</t>
+          <t>S2-03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7847,44 +7849,44 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Демьянова</t>
+          <t>Соловьев</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Алла</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Сергеевна</t>
+          <t>Сергеевич</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>ВНИИА</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>a.s.demyanova@bk.ru</t>
+          <t>alexander.solovyev@mail.ru</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>Анализ реакции срыва ¹³C(d,t)¹²C в области энергий 13–18 мэв: определение асимптотических нормировочных коэффициентов и структуры состояний ядра ¹²C</t>
+          <t>Полный и парциальные астрофизические S-факторы реакции ³He(d, p)⁴He в микроскопическом кластерном подходе</t>
         </is>
       </c>
     </row>
     <row r="67" ht="318.95" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S2-03</t>
+          <t>S2-04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7894,44 +7896,44 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Соловьев</t>
+          <t>Куликов</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Василий</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Сергеевич</t>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ВНИИА</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>alexander.solovyev@mail.ru</t>
+          <t>kulikov@nucl-th.sinp.msu.ru</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>Полный и парциальные астрофизические S-факторы реакции ³He(d, p)⁴He в микроскопическом кластерном подходе</t>
+          <t>Ab initio description of scattering</t>
         </is>
       </c>
     </row>
     <row r="68" ht="290.1" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S2-04</t>
+          <t>S2-05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7941,44 +7943,39 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Куликов</t>
+          <t>Shakhov</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Василий</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Андреевич</t>
+          <t>Aleksei</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>kulikov@nucl-th.sinp.msu.ru</t>
+          <t>shahov@jinr.ru</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>Ab initio description of scattering</t>
+          <t>Multinucleon transfer reactions in ⁷Li, ¹²C,⁴⁰Ar, ⁴⁰⸴ ⁴⁸Ca + ¹⁹⁷Au</t>
         </is>
       </c>
     </row>
     <row r="69" ht="362.45" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S2-05</t>
+          <t>S2-06</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7988,39 +7985,44 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Shakhov</t>
+          <t>Егоров</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aleksei</t>
+          <t>Михаил</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Викторович</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ТГУ(Томск)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>shahov@jinr.ru</t>
+          <t>egorovphys@mail.ru</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Multinucleon transfer reactions in ⁷Li, ¹²C,⁴⁰Ar, ⁴⁰⸴ ⁴⁸Ca + ¹⁹⁷Au</t>
+          <t>Мультикластерная реализация задачи трёх тел на примере ядерных реакций с лёгкими ядрами</t>
         </is>
       </c>
     </row>
     <row r="70" ht="275.45" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S2-06</t>
+          <t>S2-07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8030,44 +8032,44 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Егоров</t>
+          <t>Яников</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Устин</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Викторович</t>
+          <t>Михайлович</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ТГУ(Томск)</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>egorovphys@mail.ru</t>
+          <t>yanikov-u@yandex.ru</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>Мультикластерная реализация задачи трёх тел на примере ядерных реакций с лёгкими ядрами</t>
+          <t>Учет кулоновской асимптотики в формализме осцилляторного представления теории рассеяния</t>
         </is>
       </c>
     </row>
     <row r="71" ht="72.59999999999999" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S2-07</t>
+          <t>S2-08</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8075,46 +8077,44 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="C71" t="n">
+        <v>11</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Яников</t>
+          <t>Изосимов</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Устин</t>
+          <t>Игорь</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Михайлович</t>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>yanikov-u@yandex.ru</t>
+          <t>izosimov@jinr.ru</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Учет кулоновской асимптотики в формализме осцилляторного представления теории рассеяния</t>
+          <t>Excitation and decay of the Gamow-Teller resonance and its satellites in compaund nuclei</t>
         </is>
       </c>
     </row>
     <row r="72" ht="130.5" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S2-08</t>
+          <t>S2-10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8122,22 +8122,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C72" t="n">
-        <v>11</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Изосимов</t>
+          <t>Tran</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Игорь</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Николаевич</t>
+          <t>Ngoc TOan</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -8147,19 +8144,19 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>izosimov@jinr.ru</t>
+          <t>chan@jinr.ru</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>Excitation and decay of the Gamow-Teller resonance and its satellites in compaund nuclei</t>
+          <t>Theoretical and experimental investigation on the optimization of accelerator driven subcritical reactors</t>
         </is>
       </c>
     </row>
     <row r="73" ht="231.95" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S2-10</t>
+          <t>S2-11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8169,17 +8166,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tran</t>
+          <t>Уланова</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ngoc TOan</t>
+          <t>Ирина</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ивановна</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -8189,19 +8191,19 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>chan@jinr.ru</t>
+          <t>ulanova@jinr.ru</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>Theoretical and experimental investigation on the optimization of accelerator driven subcritical reactors</t>
+          <t>Время-проекционная камера для исследования свойств распада сверхтяжелых ядер</t>
         </is>
       </c>
     </row>
     <row r="74" ht="203.1" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S2-11</t>
+          <t>S2-12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8209,24 +8211,22 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C74" t="n">
+        <v>8</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Уланова</t>
+          <t>Шевчик</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ирина</t>
+          <t>Егор</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ивановна</t>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -8236,19 +8236,19 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ulanova@jinr.ru</t>
+          <t>shevchik@jinr.ru</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>Время-проекционная камера для исследования свойств распада сверхтяжелых ядер</t>
+          <t>Активная аргоновая защита в низкофоновых экспериментах по поиску двойного безнейтринного бета распада GERDA и LEGEND</t>
         </is>
       </c>
     </row>
     <row r="75" ht="203.1" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S2-12</t>
+          <t>S2-13</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8256,22 +8256,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>8</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Шевчик</t>
+          <t>Shehada</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Егор</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Андреевич</t>
+          <t>Abdullah</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -8281,19 +8278,19 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>shevchik@jinr.ru</t>
+          <t>shikhada@jinr.ru</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>Активная аргоновая защита в низкофоновых экспериментах по поиску двойного безнейтринного бета распада GERDA и LEGEND</t>
+          <t>Comparative study of simulated and measured isotope production in target and HPGe detector in muon capture experiments</t>
         </is>
       </c>
     </row>
     <row r="76" ht="203.1" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S2-13</t>
+          <t>S2-14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8303,17 +8300,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Shehada</t>
+          <t>Fedorov</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Abdullah</t>
+          <t>Nikita</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Alexandrovich</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -8323,19 +8325,19 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>shikhada@jinr.ru</t>
+          <t>na.fedorov@physics.msu.ru</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>Comparative study of simulated and measured isotope production in target and HPGe detector in muon capture experiments</t>
+          <t>Development of the evaluated cross sections database for (n,xγ)-type reactions</t>
         </is>
       </c>
     </row>
     <row r="77" ht="217.5" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S2-14</t>
+          <t>S2-15</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8343,24 +8345,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="C77" t="n">
+        <v>15</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Fedorov</t>
+          <t>Грозданов</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nikita</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Alexandrovich</t>
+          <t>Димитър</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -8370,19 +8365,19 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>na.fedorov@physics.msu.ru</t>
+          <t>dimitar@nf.jinr.ru</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>Development of the evaluated cross sections database for (n,xγ)-type reactions</t>
+          <t>Measurements of the gamma-ray emission cross sections and angular distributions from (n, xγ) reactions with 14.1 MeV neutrons</t>
         </is>
       </c>
     </row>
     <row r="78" ht="174" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S2-15</t>
+          <t>S2-16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8391,16 +8386,21 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Грозданов</t>
+          <t>Демичев</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Димитър</t>
+          <t>Михаил</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -8410,19 +8410,19 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>dimitar@nf.jinr.ru</t>
+          <t>mdemichev@jinr.ru</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>Measurements of the gamma-ray emission cross sections and angular distributions from (n, xγ) reactions with 14.1 MeV neutrons</t>
+          <t>Измерение выхода фотоядерной реакции (γ,p5n) на ядре висмута</t>
         </is>
       </c>
     </row>
     <row r="79" ht="304.5" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S2-16</t>
+          <t>S2-17</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8431,43 +8431,43 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Демичев</t>
+          <t>Ким</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Андрей</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>mdemichev@jinr.ru</t>
+          <t>kim@srd.sinp.msu.ru</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>Измерение выхода фотоядерной реакции (γ,p5n) на ядре висмута</t>
+          <t>Фотоядерные реакции с вылетом протонов на изотопах эрбия</t>
         </is>
       </c>
     </row>
     <row r="80" ht="261" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S2-17</t>
+          <t>S2-19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8476,43 +8476,43 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ким</t>
+          <t>Давыдов</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Иванович</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>kim@srd.sinp.msu.ru</t>
+          <t>aleksander.davydov@physmsu.ru</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>Фотоядерные реакции с вылетом протонов на изотопах эрбия</t>
+          <t>Особенности фоторасщепления изотопов рения ¹⁸⁵⸴ ¹⁸⁷Re</t>
         </is>
       </c>
     </row>
     <row r="81" ht="174" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S2-19</t>
+          <t>S2-20</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8521,43 +8521,43 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Давыдов</t>
+          <t>Титова</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Лариса</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Иванович</t>
+          <t>Витальевна</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ВГУ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>aleksander.davydov@physmsu.ru</t>
+          <t>titova_lv@phys.vsu.ru</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>Особенности фоторасщепления изотопов рения ¹⁸⁵⸴ ¹⁸⁷Re</t>
+          <t>Определение вероятностей формирования предразрывных конфигураций в тройном делении ядер</t>
         </is>
       </c>
     </row>
     <row r="82" ht="290.1" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S2-20</t>
+          <t>S2-21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8566,21 +8566,21 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Титова</t>
+          <t>Любашевский</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Лариса</t>
+          <t>Дмитрий</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Витальевна</t>
+          <t>Евгеньевич</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -8590,19 +8590,19 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>titova_lv@phys.vsu.ru</t>
+          <t>dima_physicist@mail.ru</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>Определение вероятностей формирования предразрывных конфигураций в тройном делении ядер</t>
+          <t>Моменты инерции bending-моды и их влияние на спины фрагментов деления</t>
         </is>
       </c>
     </row>
     <row r="83" ht="144.95" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S2-21</t>
+          <t>S2-22</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8611,43 +8611,38 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Любашевский</t>
+          <t>Abdullah</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Евгеньевич</t>
+          <t>Md. Nure Alam</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ВГУ</t>
+          <t>Department of Physics, Jagannath University (Dhaka, Bangladesh)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>dima_physicist@mail.ru</t>
+          <t>abdullah@phy.jnu.ac.bd</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>Моменты инерции bending-моды и их влияние на спины фрагментов деления</t>
+          <t>Potential description of α+¹⁹⁷Au elastic scattering</t>
         </is>
       </c>
     </row>
     <row r="84" ht="144.95" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S2-22</t>
+          <t>S2-23</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8655,39 +8650,41 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>22</v>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Abdullah</t>
+          <t>Галюзов</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Md. Nure Alam</t>
+          <t>Андрей</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Department of Physics, Jagannath University (Dhaka, Bangladesh)</t>
+          <t>ВНИИА</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>abdullah@phy.jnu.ac.bd</t>
+          <t>agar10@yandex.ru</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>Potential description of α+¹⁹⁷Au elastic scattering</t>
+          <t>Описание дифференциальных сечений упругого рассеяния изотопов водорода в теории прямых ядерных реакций</t>
         </is>
       </c>
     </row>
     <row r="85" ht="130.5" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>S2-23</t>
+          <t>S2-24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8697,39 +8694,39 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Галюзов</t>
+          <t>Музалевский</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Иван</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ВНИИА</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>agar10@yandex.ru</t>
+          <t>muzalevsky@jinr.ru</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>Описание дифференциальных сечений упругого рассеяния изотопов водорода в теории прямых ядерных реакций</t>
+          <t>Исследование рассеяния ⁶He - ⁴He на фрагмент-сепараторе АКУЛИНА-2</t>
         </is>
       </c>
     </row>
     <row r="86" ht="203.1" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>S2-24</t>
+          <t>S2-25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8739,17 +8736,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Музалевский</t>
+          <t>Naumenko</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Mikhail</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Alekseyevich</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -8759,19 +8761,19 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>muzalevsky@jinr.ru</t>
+          <t>anaumenko@jinr.ru</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>Исследование рассеяния ⁶He - ⁴He на фрагмент-сепараторе АКУЛИНА-2</t>
+          <t>Experimental studies of ¹⁰B(⁷Li, ⁸Li)⁹B transfer reaction at 58 MeV</t>
         </is>
       </c>
     </row>
     <row r="87" ht="188.45" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>S2-25</t>
+          <t>S2-26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8781,44 +8783,44 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Naumenko</t>
+          <t>Поташев</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mikhail</t>
+          <t>Станислав</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Alekseyevich</t>
+          <t>Ильич</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ИЯИ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>anaumenko@jinr.ru</t>
+          <t>s.potashev@mail.ru</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>Experimental studies of ¹⁰B(⁷Li, ⁸Li)⁹B transfer reaction at 58 MeV</t>
+          <t>Экспериментальный поиск аномалии при снятии возбуждения ядра ⁸Ве* с испусканием электрон-позитронной пары в реакции взаимодействия нейтронов с энергией свыше 20 МэВ с ядром ¹⁰В</t>
         </is>
       </c>
     </row>
     <row r="88" ht="130.5" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>S2-26</t>
+          <t>S2-27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8828,44 +8830,39 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Поташев</t>
+          <t>Макаров</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Станислав</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Ильич</t>
+          <t>Данила</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ИЯИ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>s.potashev@mail.ru</t>
+          <t>makarov-danila-2001@mail.ru</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>Экспериментальный поиск аномалии при снятии возбуждения ядра ⁸Ве* с испусканием электрон-позитронной пары в реакции взаимодействия нейтронов с энергией свыше 20 МэВ с ядром ¹⁰В</t>
+          <t>Изучение механизмов выбивания нейтрона в реакции ⁹Be(⁷Be, ⁶Be)X при промежуточной энергии</t>
         </is>
       </c>
     </row>
     <row r="89" ht="290.1" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S2-27</t>
+          <t>S2-28</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8875,17 +8872,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Макаров</t>
+          <t>Безбах</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Данила</t>
+          <t>Андрей</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -8895,19 +8892,19 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>makarov-danila-2001@mail.ru</t>
+          <t>bezbakh@jinr.ru</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>Изучение механизмов выбивания нейтрона в реакции ⁹Be(⁷Be, ⁶Be)X при промежуточной энергии</t>
+          <t>Измерение угловых распределений распада ⁷He заселяемого в реакции ⁶He(d,p)</t>
         </is>
       </c>
     </row>
     <row r="90" ht="159.6" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S2-28</t>
+          <t>S2-29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8917,17 +8914,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Безбах</t>
+          <t>Ryzhkov</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Nikita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -8937,19 +8934,19 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>bezbakh@jinr.ru</t>
+          <t>ryzhkov@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>Измерение угловых распределений распада ⁷He заселяемого в реакции ⁶He(d,p)</t>
+          <t>Analytical approach to the generation of angular momentum in spontaneous fission fragments</t>
         </is>
       </c>
     </row>
     <row r="91" ht="144.95" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S2-29</t>
+          <t>S2-30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8957,41 +8954,39 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="C91" t="n">
+        <v>30</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ryzhkov</t>
+          <t>Адоньев</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nikita</t>
+          <t>Степан</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ryzhkov@theor.jinr.ru</t>
+          <t>stepan1018@mail.ru</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>Analytical approach to the generation of angular momentum in spontaneous fission fragments</t>
+          <t>Исследование протон-индуцированных реакций на висмуте-209</t>
         </is>
       </c>
     </row>
     <row r="92" ht="409.5" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S2-30</t>
+          <t>S2-31</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9000,38 +8995,38 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Адоньев</t>
+          <t>Karanfil</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Степан</t>
+          <t>Ege</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stepan1018@mail.ru</t>
+          <t>karanfil@jinr.ru</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>Исследование протон-индуцированных реакций на висмуте-209</t>
+          <t>²³⁷Np+⁴⁸Ca reaction and decay properties of ²⁸²Nh and descendant nuclei at DGFRS‑2</t>
         </is>
       </c>
     </row>
     <row r="93" ht="231.95" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S2-31</t>
+          <t>S2-32</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9040,16 +9035,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Karanfil</t>
+          <t>Mikhailova</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ege</t>
+          <t>Tatiana</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -9059,19 +9054,19 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>karanfil@jinr.ru</t>
+          <t>tmikh@jinr.ru</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>²³⁷Np+⁴⁸Ca reaction and decay properties of ²⁸²Nh and descendant nuclei at DGFRS‑2</t>
+          <t>Modeling of isotopic scaling and target ratio in transport statistical approach</t>
         </is>
       </c>
     </row>
     <row r="94" ht="174" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S2-32</t>
+          <t>S2-33</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9080,38 +9075,38 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Mikhailova</t>
+          <t>Молоторенко</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tatiana</t>
+          <t>Ксения</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ВГУ, ОИЯИ</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>tmikh@jinr.ru</t>
+          <t>molotorenkoksenia@gmail.com</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>Modeling of isotopic scaling and target ratio in transport statistical approach</t>
+          <t>Роль нейтронного избытка в механизмах передачи нуклонов в реакциях тяжелых ионов ⁴⁰⸴ ⁴⁸Ca + ¹⁹⁷Au</t>
         </is>
       </c>
     </row>
     <row r="95" ht="203.1" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S2-33</t>
+          <t>S2-34</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9120,38 +9115,38 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Молоторенко</t>
+          <t>Унжакова</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ксения</t>
+          <t>Анна</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>ВГУ, ОИЯИ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>molotorenkoksenia@gmail.com</t>
+          <t>a.unzhakova@spbu.ru</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>Роль нейтронного избытка в механизмах передачи нуклонов в реакциях тяжелых ионов ⁴⁰⸴ ⁴⁸Ca + ¹⁹⁷Au</t>
+          <t>Multi-agent modeling of collective dynamics in heavy nuclei fission</t>
         </is>
       </c>
     </row>
     <row r="96" ht="144.95" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S2-34</t>
+          <t>S2-35</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9160,38 +9155,43 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Унжакова</t>
+          <t>Goncharenko</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Alexandrovich</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>a.unzhakova@spbu.ru</t>
+          <t>iv.gonch.0907@gmail.com</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>Multi-agent modeling of collective dynamics in heavy nuclei fission</t>
+          <t>Neutron yield uncertainty calculations for (α, n) reactions using the NeuCBOT program</t>
         </is>
       </c>
     </row>
     <row r="97" ht="188.45" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S2-35</t>
+          <t>S2-36</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9200,88 +9200,88 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Goncharenko</t>
+          <t>Андреев</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Alexandrovich</t>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>iv.gonch.0907@gmail.com</t>
+          <t>andreev.av20@physics.msu.ru</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>Neutron yield uncertainty calculations for (α, n) reactions using the NeuCBOT program</t>
+          <t>Theoretical calculation of the angular anisotropy of gamma radiation on carbon, cromium and iron nuclei in inelastic neutron scattering</t>
         </is>
       </c>
     </row>
     <row r="98" ht="188.45" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S2-36</t>
+          <t>S3-01</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Андреев</t>
+          <t>Ковалев</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Максим</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Борисович</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>andreev.av20@physics.msu.ru</t>
+          <t>physics1818@yandex.ru</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>Theoretical calculation of the angular anisotropy of gamma radiation on carbon, cromium and iron nuclei in inelastic neutron scattering</t>
+          <t>Исследование эффекта наложения сигналов (pile-up) при регистрации ат-мосферных мюонов в нейтринном телескопе Baikal-GVD.</t>
         </is>
       </c>
     </row>
     <row r="99" ht="246.6" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S3-01</t>
+          <t>S3-02</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9290,43 +9290,43 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Ковалев</t>
+          <t>Скобляков</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Викторович</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>НИЦ КИ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>physics1818@yandex.ru</t>
+          <t>dinAlt220@yandex.ru</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>Исследование эффекта наложения сигналов (pile-up) при регистрации ат-мосферных мюонов в нейтринном телескопе Baikal-GVD.</t>
+          <t>Виртуальный генератор потока АТМОСФЕРНЫХ мюонов В варьируемом диапазоне энергий до 100 ТэВ</t>
         </is>
       </c>
     </row>
     <row r="100" ht="159.6" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S3-02</t>
+          <t>S3-03</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9335,11 +9335,11 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Скобляков</t>
+          <t>Канцырев</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9359,19 +9359,19 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>dinAlt220@yandex.ru</t>
+          <t>kantsyrev@itep.ru</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>Виртуальный генератор потока АТМОСФЕРНЫХ мюонов В варьируемом диапазоне энергий до 100 ТэВ</t>
+          <t>Мюонная томография крупномасштабных объектов с применением компактных цилиндрических позиционно-чувствительных детекторов</t>
         </is>
       </c>
     </row>
     <row r="101" ht="188.45" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>S3-03</t>
+          <t>S3-04</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9380,43 +9380,38 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Канцырев</t>
+          <t>Лашин</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Алексей</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Викторович</t>
+          <t>Константин</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>ВНИИЭФ</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>kantsyrev@itep.ru</t>
+          <t>kosty2112@gmail.com</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>Мюонная томография крупномасштабных объектов с применением компактных цилиндрических позиционно-чувствительных детекторов</t>
+          <t>Реконструкция плотности многокомпонентных объектов в протонной радиографии с использованием метода роя частиц и преобразования Абеля</t>
         </is>
       </c>
     </row>
     <row r="102" ht="290.1" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S3-04</t>
+          <t>S3-05</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9425,38 +9420,43 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Лашин</t>
+          <t>Олейников</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Константин</t>
+          <t>Владислав</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Петрович</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ВНИИЭФ</t>
+          <t>ИЯФ Новосиб</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>kosty2112@gmail.com</t>
+          <t>V.P.Oleynikov@inp.nsk.su</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>Реконструкция плотности многокомпонентных объектов в протонной радиографии с использованием метода роя частиц и преобразования Абеля</t>
+          <t>Измерение ионизационных выходов ядер отдачи в аргоне</t>
         </is>
       </c>
     </row>
     <row r="103" ht="290.1" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>S3-05</t>
+          <t>S3-06</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9465,43 +9465,38 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Олейников</t>
+          <t>Петров</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Владислав</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Петрович</t>
+          <t>Григорий</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ИЯФ Новосиб</t>
+          <t>МИФИ</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>V.P.Oleynikov@inp.nsk.su</t>
+          <t>grigoriy.6.petrov@gmail.com</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>Измерение ионизационных выходов ядер отдачи в аргоне</t>
+          <t>Development of machine learning tool for photon identification using the electromagnetic calorimeter at SPD detector</t>
         </is>
       </c>
     </row>
     <row r="104" ht="231.95" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>S3-06</t>
+          <t>S3-08</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9510,38 +9505,43 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Петров</t>
+          <t>Семенов</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>МИФИ</t>
+          <t>НИЦ КИ</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>grigoriy.6.petrov@gmail.com</t>
+          <t>kindr_cool@mail.ru</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>Development of machine learning tool for photon identification using the electromagnetic calorimeter at SPD detector</t>
+          <t>Критический стенд «П»: современное состояние, особенности и роль исследований для развития технологии ВВЭР</t>
         </is>
       </c>
     </row>
     <row r="105" ht="318.95" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S3-08</t>
+          <t>S3-09</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9550,43 +9550,38 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Семенов</t>
+          <t>Бурякова</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Сергей</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Владимирович</t>
+          <t>Елена</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>ВНИИЭф</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>kindr_cool@mail.ru</t>
+          <t>suyazova.elena@mail.ru</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>Критический стенд «П»: современное состояние, особенности и роль исследований для развития технологии ВВЭР</t>
+          <t>Результаты экспериментов с тепловыми трубами с цезиевым теплоносителем</t>
         </is>
       </c>
     </row>
     <row r="106" ht="333.6" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>S3-09</t>
+          <t>S3-10</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9595,38 +9590,43 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Бурякова</t>
+          <t>Розов</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>ВНИИЭф</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>suyazova.elena@mail.ru</t>
+          <t>rozovs@jinr.ru</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>Результаты экспериментов с тепловыми трубами с цезиевым теплоносителем</t>
+          <t>Низкофоновый детектор нейтронов на основе гелия-3</t>
         </is>
       </c>
     </row>
     <row r="107" ht="144.95" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>S3-10</t>
+          <t>S3-11</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9635,43 +9635,43 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Розов</t>
+          <t>Каретников</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Максим</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Донатович</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ВНИИА</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>rozovs@jinr.ru</t>
+          <t>mcsym01@gmail.com</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>Низкофоновый детектор нейтронов на основе гелия-3</t>
+          <t>Нейтрон-нейтронные методы дистанционного контроля с использованием меченых нейтронов</t>
         </is>
       </c>
     </row>
     <row r="108" ht="246.6" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>S3-11</t>
+          <t>S3-12</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9680,43 +9680,38 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Каретников</t>
+          <t>Данилкин</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Максим</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Донатович</t>
+          <t>Владислав</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ВНИИА</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>mcsym01@gmail.com</t>
+          <t>donyvlad@gmail.com</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>Нейтрон-нейтронные методы дистанционного контроля с использованием меченых нейтронов</t>
+          <t>Моделирование ионной оптики сепаратора STAR с помощью программы SHEMAT</t>
         </is>
       </c>
     </row>
     <row r="109" ht="144.95" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>S3-12</t>
+          <t>S3-13</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9725,16 +9720,21 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Данилкин</t>
+          <t>Веденеев</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Владислав</t>
+          <t>Вячеслав</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Юрьевич</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9744,19 +9744,19 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>donyvlad@gmail.com</t>
+          <t>vvedeneyev@gmail.com</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>Моделирование ионной оптики сепаратора STAR с помощью программы SHEMAT</t>
+          <t>Криогенная газовая ячейка охлаждения ионов. Особенности конструкции, вакуумная система, система газового обеспечения, система охлаждения</t>
         </is>
       </c>
     </row>
     <row r="110" ht="275.45" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>S3-13</t>
+          <t>S3-14</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9765,21 +9765,21 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Веденеев</t>
+          <t>Новоселов</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Вячеслав</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Юрьевич</t>
+          <t>Сергеевич</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9789,19 +9789,19 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>vvedeneyev@gmail.com</t>
+          <t>noval@jinr.ru</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>Криогенная газовая ячейка охлаждения ионов. Особенности конструкции, вакуумная система, система газового обеспечения, система охлаждения</t>
+          <t>Измерение времени экстракции ионов из криогенной газовой ячейки охлаждения</t>
         </is>
       </c>
     </row>
     <row r="111" ht="188.45" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>S3-14</t>
+          <t>S3-15</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9810,21 +9810,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Новоселов</t>
+          <t>Зимин</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Алексей</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Сергеевич</t>
+          <t>Илья</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9834,19 +9829,19 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>noval@jinr.ru</t>
+          <t>zimin@jinr.ru</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>Измерение времени экстракции ионов из криогенной газовой ячейки охлаждения</t>
+          <t>Нейтронные сцинтилляторы на основе кристалла ZnS(Ag)</t>
         </is>
       </c>
     </row>
     <row r="112" ht="116.1" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>S3-15</t>
+          <t>S3-16</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9855,16 +9850,21 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Зимин</t>
+          <t>Сидорова</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Илья</t>
+          <t>Ольга</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Викторовна</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9874,19 +9874,19 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>zimin@jinr.ru</t>
+          <t>sidorova@jinr.ru</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>Нейтронные сцинтилляторы на основе кристалла ZnS(Ag)</t>
+          <t>Физическая структура кросс-толка гамма-квантов в сферических многодетекторных сцинтилляционных системах</t>
         </is>
       </c>
     </row>
     <row r="113" ht="246.6" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>S3-16</t>
+          <t>S3-17</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9895,43 +9895,38 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Сидорова</t>
+          <t>Strizhak</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ольга</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Викторовна</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ИЯИ</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>sidorova@jinr.ru</t>
+          <t>strizhak@inr.ru</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>Физическая структура кросс-толка гамма-квантов в сферических многодетекторных сцинтилляционных системах</t>
+          <t>Performance and light yield of CsI(pure) scintillation module prototypes at LN2 temperature</t>
         </is>
       </c>
     </row>
     <row r="114" ht="188.45" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>S3-17</t>
+          <t>S3-18</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9940,38 +9935,38 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Strizhak</t>
+          <t>Суслов</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Иван</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>ИЯИ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>strizhak@inr.ru</t>
+          <t>ivsuslov@jinr.ru</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>Performance and light yield of CsI(pure) scintillation module prototypes at LN2 temperature</t>
+          <t>Пласстмассовые сцинтилляторы с возможностью разделения частиц по форме импульса</t>
         </is>
       </c>
     </row>
     <row r="115" ht="333.6" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>S3-18</t>
+          <t>S3-19</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9980,16 +9975,21 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Суслов</t>
+          <t>Евсеев</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -9999,19 +9999,19 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ivsuslov@jinr.ru</t>
+          <t>evseevsa@jinr.ru</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>Пласстмассовые сцинтилляторы с возможностью разделения частиц по форме импульса</t>
+          <t>Исследование радиационной стойкости SiC- и Si-детекторов после облучения альфа-частицами</t>
         </is>
       </c>
     </row>
     <row r="116" ht="203.1" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>S3-19</t>
+          <t>S3-20</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10020,43 +10020,43 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Евсеев</t>
+          <t>Смирнов</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Игорь</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Борисович</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ПИЯФ</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>evseevsa@jinr.ru</t>
+          <t>smirnov_ib@pnpi.nrcki.ru</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
-          <t>Исследование радиационной стойкости SiC- и Si-детекторов после облучения альфа-частицами</t>
+          <t>Average Spatial Resolution of Detector Layers of Four-Layer Position-Sensitive Detectors</t>
         </is>
       </c>
     </row>
     <row r="117" ht="130.5" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>S3-20</t>
+          <t>S3-21</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10065,43 +10065,43 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Смирнов</t>
+          <t>Стрекаловский</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Олег</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Викторович</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>ПИЯФ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>smirnov_ib@pnpi.nrcki.ru</t>
+          <t>stroleg1@yandex.ru</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>Average Spatial Resolution of Detector Layers of Four-Layer Position-Sensitive Detectors</t>
+          <t>Применение диджитайзеров CAEN-ХХ42 для регистрации заряженных частиц</t>
         </is>
       </c>
     </row>
     <row r="118" ht="275.45" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>S3-21</t>
+          <t>S3-22</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10110,43 +10110,38 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Стрекаловский</t>
+          <t>Шимко</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Олег</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Викторович</t>
+          <t>Павел</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>stroleg1@yandex.ru</t>
+          <t>pashashimko0306@gmail.com</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>Применение диджитайзеров CAEN-ХХ42 для регистрации заряженных частиц</t>
+          <t>Исследование распределения поглощённой дозы в полимерных материалах при облучении ускоренными электронами</t>
         </is>
       </c>
     </row>
     <row r="119" ht="203.1" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>S3-22</t>
+          <t>S3-23</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10155,38 +10150,38 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Шимко</t>
+          <t>Цыганкова</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Павел</t>
+          <t>Валерия</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>СВКНИИ ДВО</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>pashashimko0306@gmail.com</t>
+          <t>tsigankova.valeriya@mail.ru</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>Исследование распределения поглощённой дозы в полимерных материалах при облучении ускоренными электронами</t>
+          <t>Влияние ²²²Rn на расчёт радиоуглеродного возраста древесных углей</t>
         </is>
       </c>
     </row>
     <row r="120" ht="203.1" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S3-23</t>
+          <t>S3-24</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10195,38 +10190,43 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Цыганкова</t>
+          <t>Пухаева</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Валерия</t>
+          <t>Нелли</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Ефимовна</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>СВКНИИ ДВО</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>tsigankova.valeriya@mail.ru</t>
+          <t>pukhaeva@jinr.ru</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>Влияние ²²²Rn на расчёт радиоуглеродного возраста древесных углей</t>
+          <t>Nd/ZnS-модифицированные квантовые точки CdZnSeS как нанокомпоненты сцинтилляционных сред для поиска безнейтринного двойного β-распада ¹⁵⁰Nd</t>
         </is>
       </c>
     </row>
     <row r="121" ht="217.5" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S3-24</t>
+          <t>S3-25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10264,14 +10264,14 @@
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>Nd/ZnS-модифицированные квантовые точки CdZnSeS как нанокомпоненты сцинтилляционных сред для поиска безнейтринного двойного β-распада ¹⁵⁰Nd</t>
+          <t>Results of ARFIM experiment setup for applied research of NOSU</t>
         </is>
       </c>
     </row>
     <row r="122" ht="188.45" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>S3-25</t>
+          <t>S3-26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10309,99 +10309,99 @@
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>Results of ARFIM experiment setup for applied research of NOSU</t>
+          <t>Neodymium-modified CdZnSeS/ZnS quantum dots: evolution of optical response and evidence limits for core/shell architecture</t>
         </is>
       </c>
     </row>
     <row r="123" ht="174" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>S3-26</t>
+          <t>S3-27</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Пухаева</t>
+          <t>Петровская</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Нелли</t>
+          <t>Анна</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ефимовна</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>ОИЯИ</t>
+          <t>Станиславовна</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>pukhaeva@jinr.ru</t>
+          <t>anita3425@yandex.ru</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>Neodymium-modified CdZnSeS/ZnS quantum dots: evolution of optical response and evidence limits for core/shell architecture</t>
+          <t>Перспективы применения сухой ионно-плазменной технологии дезактивации оборудования ЯЭУ из титановых сплавов</t>
         </is>
       </c>
     </row>
     <row r="124" ht="261" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S3-27</t>
+          <t>S4-01</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Петровская</t>
+          <t>Бикметов</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Никита</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Станиславовна</t>
+          <t>Рафальевич</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>anita3425@yandex.ru</t>
+          <t>bikmetov@jinr.ru</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>Перспективы применения сухой ионно-плазменной технологии дезактивации оборудования ЯЭУ из титановых сплавов</t>
+          <t>Investigation of nuclear deformation influence on anisotropic flows in heavy-ion collisions at NICA energies</t>
         </is>
       </c>
     </row>
     <row r="125" ht="174" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S4-01</t>
+          <t>S4-02</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10410,43 +10410,43 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Бикметов</t>
+          <t>Вечернин</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Владимир</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Рафальевич</t>
+          <t>Викторович</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>bikmetov@jinr.ru</t>
+          <t>v.vechernin@spbu.ru</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>Investigation of nuclear deformation influence on anisotropic flows in heavy-ion collisions at NICA energies</t>
+          <t>Кумулятивные явления в области больших поперечных импульсов и их наблюдение в столкновениях ядер на коллайдере NICA</t>
         </is>
       </c>
     </row>
     <row r="126" ht="362.45" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S4-02</t>
+          <t>S4-03</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10455,43 +10455,38 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Вечернин</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Владимир</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Викторович</t>
+          <t>Shubham</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>v.vechernin@spbu.ru</t>
+          <t>s.sharma.hep@gmail.com</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>Кумулятивные явления в области больших поперечных импульсов и их наблюдение в столкновениях ядер на коллайдере NICA</t>
+          <t>Inclusive J/ψ Production as a Probe of Gluon Dynamics at NICA</t>
         </is>
       </c>
     </row>
     <row r="127" ht="144.95" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>S4-03</t>
+          <t>S4-04</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10500,38 +10495,43 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Жаров</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Shubham</t>
+          <t>Михаил</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>s.sharma.hep@gmail.com</t>
+          <t>m.zharov@spbu.ru</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>Inclusive J/ψ Production as a Probe of Gluon Dynamics at NICA</t>
+          <t>Моделирование кумулятивных эффектов в столкновениях тяжелых ионов при энергиях коллайдера NICA</t>
         </is>
       </c>
     </row>
     <row r="128" ht="290.1" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S4-04</t>
+          <t>S4-05</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10540,43 +10540,43 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Жаров</t>
+          <t>Идрисов</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Дим</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Маратович</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>m.zharov@spbu.ru</t>
+          <t>idrisov.dim@mail.ru</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>Моделирование кумулятивных эффектов в столкновениях тяжелых ионов при энергиях коллайдера NICA</t>
+          <t>Методы определения центральности с использованием передних детекторов в эксперименте BM@N</t>
         </is>
       </c>
     </row>
     <row r="129" ht="261" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S4-05</t>
+          <t>S4-06</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10585,43 +10585,43 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Идрисов</t>
+          <t>Plotnikov</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Дим</t>
+          <t>Vasilii</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Маратович</t>
+          <t>Alexandrovich</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>idrisov.dim@mail.ru</t>
+          <t>vplotnikov@jinr.ru</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>Методы определения центральности с использованием передних детекторов в эксперименте BM@N</t>
+          <t>Λd сorrelation function in Xe+CsI collisions at 3.8 AGeV in the BM@N experiment</t>
         </is>
       </c>
     </row>
     <row r="130" ht="231.95" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>S4-06</t>
+          <t>S4-07</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10630,43 +10630,43 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Plotnikov</t>
+          <t>Зубанков</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vasilii</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Alexandrovich</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>vplotnikov@jinr.ru</t>
+          <t>zubankov@inr.ru</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>Λd сorrelation function in Xe+CsI collisions at 3.8 AGeV in the BM@N experiment</t>
+          <t>Measurement of double differential inclusive cross sections of forward neutron emission in the BM@N experiment</t>
         </is>
       </c>
     </row>
     <row r="131" ht="275.45" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>S4-07</t>
+          <t>S4-08</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10675,43 +10675,43 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Зубанков</t>
+          <t>Андронов</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Евгений</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>zubankov@inr.ru</t>
+          <t>e.v.andronov@spbu.ru</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>Measurement of double differential inclusive cross sections of forward neutron emission in the BM@N experiment</t>
+          <t>Influence of colour string configurations on rapidity multiplicity correlations</t>
         </is>
       </c>
     </row>
     <row r="132" ht="130.5" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>S4-08</t>
+          <t>S4-10</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10719,17 +10719,19 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C132" t="n">
-        <v>8</v>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Андронов</t>
+          <t>Герасименюк</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Евгений</t>
+          <t>Николай</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -10739,24 +10741,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ДВФУ</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>e.v.andronov@spbu.ru</t>
+          <t>gerasimenyuk.nv@dvfu.ru</t>
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>Influence of colour string configurations on rapidity multiplicity correlations</t>
+          <t>Экранирование заряда в многокомпонентной аблелевой модели Хиггса</t>
         </is>
       </c>
     </row>
     <row r="133" ht="246.6" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>S4-10</t>
+          <t>S4-11</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10766,44 +10768,44 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Герасименюк</t>
+          <t>Зайцев</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Николай</t>
+          <t>Андрей</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>ДВФУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>gerasimenyuk.nv@dvfu.ru</t>
+          <t>zaicev@jinr.ru</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>Экранирование заряда в многокомпонентной аблелевой модели Хиггса</t>
+          <t>Ядро ⁸Be и состояние Хойла в диссоциации релятивистских ядер</t>
         </is>
       </c>
     </row>
     <row r="134" ht="217.5" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>S4-11</t>
+          <t>S4-12</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10813,44 +10815,44 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Зайцев</t>
+          <t>Скородько</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Татьяна</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Юрьевна</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>zaicev@jinr.ru</t>
+          <t>tatiskor@mail.ru</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>Ядро ⁸Be и состояние Хойла в диссоциации релятивистских ядер</t>
+          <t>Dibaryon d*(2380) : prediction, detection, understanding</t>
         </is>
       </c>
     </row>
     <row r="135" ht="188.45" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>S4-12</t>
+          <t>S4-14</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10860,44 +10862,44 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Скородько</t>
+          <t>Friesen</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Татьяна</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Юрьевна</t>
+          <t>Vadimovna</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>tatiskor@mail.ru</t>
+          <t>avfriesen@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>Dibaryon d*(2380) : prediction, detection, understanding</t>
+          <t>Mass spectrum of noncharmed and charmed meson states at finite temperature in extended linear-sigma model</t>
         </is>
       </c>
     </row>
     <row r="136" ht="246.6" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>S4-14</t>
+          <t>S4-15</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10905,24 +10907,22 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="C136" t="n">
+        <v>15</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Friesen</t>
+          <t>Авдеев</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vadimovna</t>
+          <t>Петрович</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10932,19 +10932,19 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>avfriesen@theor.jinr.ru</t>
+          <t>avdeyev@jinr.ru</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>Mass spectrum of noncharmed and charmed meson states at finite temperature in extended linear-sigma model</t>
+          <t>Source velocity in collisions of 2.1 GeV and 3.6 GeV protons with gold target.</t>
         </is>
       </c>
     </row>
     <row r="137" ht="174" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>S4-15</t>
+          <t>S4-16</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10953,43 +10953,43 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Авдеев</t>
+          <t>Иванищев</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Дмитрий</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Петрович</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИЦ КИ-ПИЯФ, СПбПУ</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>avdeyev@jinr.ru</t>
+          <t>ivanishchev_da@pnpi.nrcki.ru</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>Source velocity in collisions of 2.1 GeV and 3.6 GeV protons with gold target.</t>
+          <t>Особенности измерения свойств резонансов в эксперименте MPD в Xe+W столкновениях при энергии 2,5 A*ГэВ</t>
         </is>
       </c>
     </row>
     <row r="138" ht="246.6" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>S4-16</t>
+          <t>S4-17</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10998,43 +10998,43 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Иванищев</t>
+          <t>Силагадзе</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Зураб</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Карлоевич</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>НИЦ КИ-ПИЯФ, СПбПУ</t>
+          <t>ИЯФ Новосиб</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ivanishchev_da@pnpi.nrcki.ru</t>
+          <t>silagadze@inp.nsk.su</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>Особенности измерения свойств резонансов в эксперименте MPD в Xe+W столкновениях при энергии 2,5 A*ГэВ</t>
+          <t>Pauli equation in spaces of constant curvature and extended Nikiforov-Uvarov method</t>
         </is>
       </c>
     </row>
     <row r="139" ht="174" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S4-17</t>
+          <t>S4-18</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11043,43 +11043,43 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Силагадзе</t>
+          <t>Феофилов</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Зураб</t>
+          <t>Григорий</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Карлоевич</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>ИЯФ Новосиб</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>silagadze@inp.nsk.su</t>
+          <t>g.feofilov@spbu.ru</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>Pauli equation in spaces of constant curvature and extended Nikiforov-Uvarov method</t>
+          <t>Минимизация объемных флуктуаций при поиске критической точки сильно взаимодействующей материи в релятивистских ядерных столкновениях</t>
         </is>
       </c>
     </row>
     <row r="140" ht="144.95" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>S4-18</t>
+          <t>S4-19</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11088,43 +11088,38 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Феофилов</t>
+          <t>Prokhorova</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Григорий</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Александрович</t>
+          <t>Daria</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>Tsinghua Univ., China</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>g.feofilov@spbu.ru</t>
+          <t>daria-prokhorova@mail.tsinghua.edu.cn</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>Минимизация объемных флуктуаций при поиске критической точки сильно взаимодействующей материи в релятивистских ядерных столкновениях</t>
+          <t>Heavy-flavor jet quenching in pre-equilibrium medium</t>
         </is>
       </c>
     </row>
     <row r="141" ht="144.95" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>S4-19</t>
+          <t>S4-20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11133,38 +11128,43 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Prokhorova</t>
+          <t>Недорезов</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Daria</t>
+          <t>Егор</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Вячеславович</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tsinghua Univ., China</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>daria-prokhorova@mail.tsinghua.edu.cn</t>
+          <t>nedorezov@jinr.ru</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>Heavy-flavor jet quenching in pre-equilibrium medium</t>
+          <t>Overview of the STAR hot QCD results</t>
         </is>
       </c>
     </row>
     <row r="142" ht="174" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>S4-20</t>
+          <t>S4-21</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11173,43 +11173,43 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Недорезов</t>
+          <t>Ануфриев</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Егор</t>
+          <t>Антон</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Вячеславович</t>
+          <t>Витальевич</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>nedorezov@jinr.ru</t>
+          <t>antonman200@yandex.ru</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>Overview of the STAR hot QCD results</t>
+          <t>Исследование выходов заряженных адронов в рамках гидродинамического моделирования с применением голографического уравнения состояния</t>
         </is>
       </c>
     </row>
     <row r="143" ht="231.95" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>S4-21</t>
+          <t>S4-22</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11218,21 +11218,21 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Ануфриев</t>
+          <t>Галактионов</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Антон</t>
+          <t>Кирилл</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Витальевич</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -11242,19 +11242,19 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>antonman200@yandex.ru</t>
+          <t>kirill.galaktionov@spbu.ru</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>Исследование выходов заряженных адронов в рамках гидродинамического моделирования с применением голографического уравнения состояния</t>
+          <t>Исследование нейросетевых подходов к оценке прицельного параметра в столкновениях тяжелых ионов на основе 4π информации о событии</t>
         </is>
       </c>
     </row>
     <row r="144" ht="159.6" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>S4-22</t>
+          <t>S4-23</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11263,43 +11263,43 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Галактионов</t>
+          <t>Дьяченко</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Кирилл</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Трофимович</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>НИЦ КИ-ПИЯФ</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>kirill.galaktionov@spbu.ru</t>
+          <t>dyachenko_a@mail.ru</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>Исследование нейросетевых подходов к оценке прицельного параметра в столкновениях тяжелых ионов на основе 4π информации о событии</t>
+          <t>Неравновесный квантовый гидродинамический подход и эмиссия фрагментов в столкновениях тяжелых ионов промежуточных энергий</t>
         </is>
       </c>
     </row>
     <row r="145" ht="246.6" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>S4-23</t>
+          <t>S4-24</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11308,43 +11308,43 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Дьяченко</t>
+          <t>Белокурова</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Светлана</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Трофимович</t>
+          <t>Николаевна</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>НИЦ КИ-ПИЯФ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>dyachenko_a@mail.ru</t>
+          <t>s.belokurova@spbu.ru</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>Неравновесный квантовый гидродинамический подход и эмиссия фрагментов в столкновениях тяжелых ионов промежуточных энергий</t>
+          <t>Применение классического глауберовского подхода к описанию дейтрон-дейтронного взаимодействия</t>
         </is>
       </c>
     </row>
     <row r="146" ht="203.1" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>S4-24</t>
+          <t>S4-25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11353,21 +11353,21 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Белокурова</t>
+          <t>Размыслов</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Светлана</t>
+          <t>Константин</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Владимирович</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -11377,19 +11377,19 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>s.belokurova@spbu.ru</t>
+          <t>yoitz@yandex.ru</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>Применение классического глауберовского подхода к описанию дейтрон-дейтронного взаимодействия</t>
+          <t>О применении генераторов EPOS4, UrQMD, PHQMD и PYTHIA для анализа событий в физике сверхвысоких энергий</t>
         </is>
       </c>
     </row>
     <row r="147" ht="318.95" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S4-25</t>
+          <t>S4-26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11398,43 +11398,43 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Размыслов</t>
+          <t>Мягков</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Константин</t>
+          <t>Данила</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>НИИЯФ МГУ</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>yoitz@yandex.ru</t>
+          <t>danila.myagkov.msu@mail.ru</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>О применении генераторов EPOS4, UrQMD, PHQMD и PYTHIA для анализа событий в физике сверхвысоких энергий</t>
+          <t>Моделирование влияния деформации ядер на азимутальную анизотропию частиц в генераторе событий HYDJET++</t>
         </is>
       </c>
     </row>
     <row r="148" ht="130.5" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S4-26</t>
+          <t>S4-27</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11443,43 +11443,38 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Мягков</t>
+          <t>Vasilieva</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Данила</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Александрович</t>
+          <t>Anastasiia</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>НИИЯФ МГУ</t>
+          <t>МИФИ</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>danila.myagkov.msu@mail.ru</t>
+          <t>anastasiyavasileva00@gmail.com</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>Моделирование влияния деформации ядер на азимутальную анизотропию частиц в генераторе событий HYDJET++</t>
+          <t>Analysis of charged and identified hadron spectra with Tsallis distributions in O+O, Kr+Kr, and Xe+Xe collisions at √sₙₙ = 6 GeV using the UrQMD model</t>
         </is>
       </c>
     </row>
     <row r="149" ht="72.59999999999999" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>S4-27</t>
+          <t>S4-28</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11488,83 +11483,88 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Vasilieva</t>
+          <t>Калугин</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Anastasiia</t>
+          <t>Никита</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Константинович</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>МИФИ</t>
+          <t>КИ ИФВЭ</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>anastasiyavasileva00@gmail.com</t>
+          <t>Nikita.Kalugin@ihep.ru</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>Analysis of charged and identified hadron spectra with Tsallis distributions in O+O, Kr+Kr, and Xe+Xe collisions at √sₙₙ = 6 GeV using the UrQMD model</t>
+          <t>Измерение выстроенности K*⁻(892)-мезонов, образованных в каон-ядерных и пион-ядерных взаимодействиях на ускорительном комплексе У-70</t>
         </is>
       </c>
     </row>
     <row r="150" ht="348" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>S4-28</t>
+          <t>S5-01</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Калугин</t>
+          <t>Чернышев</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Борис</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Константинович</t>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>КИ ИФВЭ</t>
+          <t>МИФИ</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Nikita.Kalugin@ihep.ru</t>
+          <t>chernyshev@mephi.ru</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>Измерение выстроенности K*⁻(892)-мезонов, образованных в каон-ядерных и пион-ядерных взаимодействиях на ускорительном комплексе У-70</t>
+          <t>Поиск тринейтрона в реакциях поглощения остановившихся пионов ядрами ⁹Be</t>
         </is>
       </c>
     </row>
     <row r="151" ht="318.95" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>S5-01</t>
+          <t>S5-02</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11573,43 +11573,43 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Чернышев</t>
+          <t>Борзаков</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Борис</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Борисович</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>МИФИ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>chernyshev@mephi.ru</t>
+          <t>sbor@nf.jinr.ru</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>Поиск тринейтрона в реакциях поглощения остановившихся пионов ядрами ⁹Be</t>
+          <t>Возможное существование синглетного дейтрона как дибарионного резонанса и проблема существования динейтрона</t>
         </is>
       </c>
     </row>
     <row r="152" ht="290.1" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>S5-02</t>
+          <t>S5-03</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11618,43 +11618,43 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Борзаков</t>
+          <t>Ефименко</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Мария</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Константиновна</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ТОГУ</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>sbor@nf.jinr.ru</t>
+          <t>ef.maria97@yandex.ru</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>Возможное существование синглетного дейтрона как дибарионного резонанса и проблема существования динейтрона</t>
+          <t>Excited states of ⁶He nucleus in the SS-HORSE–NCSM approach</t>
         </is>
       </c>
     </row>
     <row r="153" ht="246.6" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>S5-03</t>
+          <t>S5-04</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11663,21 +11663,21 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Ефименко</t>
+          <t>Зайцев</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Мария</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Константиновна</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11687,19 +11687,19 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>ef.maria97@yandex.ru</t>
+          <t>000282@togudv.ru</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>Excited states of ⁶He nucleus in the SS-HORSE–NCSM approach</t>
+          <t>Ионизация атомов протонным ударом в представлении параболических квазиштурмовских функций</t>
         </is>
       </c>
     </row>
     <row r="154" ht="261" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S5-04</t>
+          <t>S5-05</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11708,7 +11708,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11717,12 +11717,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Сергеевич</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11732,19 +11732,19 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>000282@togudv.ru</t>
+          <t>alzaytsev@togudv.ru</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>Ионизация атомов протонным ударом в представлении параболических квазиштурмовских функций</t>
+          <t>Атом водорода в поле лазерного импульса в представлении параболических волновых пакетов</t>
         </is>
       </c>
     </row>
     <row r="155" ht="261" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S5-05</t>
+          <t>S5-06</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11753,43 +11753,38 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Зайцев</t>
+          <t>Шалапинин</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Александр</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Сергеевич</t>
+          <t>Денис</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>ТОГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>alzaytsev@togudv.ru</t>
+          <t>shalapinin@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>Атом водорода в поле лазерного импульса в представлении параболических волновых пакетов</t>
+          <t>Van der Waals dimers of neon</t>
         </is>
       </c>
     </row>
     <row r="156" ht="348" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>S5-06</t>
+          <t>S5-07</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11798,38 +11793,43 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Шалапинин</t>
+          <t>Рубцова</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Денис</t>
+          <t>Ольга</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Андреевна</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>shalapinin@theor.jinr.ru</t>
+          <t>rubtsova-olga@yandex.ru</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>Van der Waals dimers of neon</t>
+          <t>Finding virtual states via wave-packet continuum discretization</t>
         </is>
       </c>
     </row>
     <row r="157" ht="304.5" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>S5-07</t>
+          <t>S5-08</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11838,43 +11838,43 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Рубцова</t>
+          <t>Мотовилов</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ольга</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Андреевна</t>
+          <t>Константинович</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>rubtsova-olga@yandex.ru</t>
+          <t>motovilv@gmail.com</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>Finding virtual states via wave-packet continuum discretization</t>
+          <t>Resonances of a two-particle system on a 1D lattice</t>
         </is>
       </c>
     </row>
     <row r="158" ht="188.45" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>S5-08</t>
+          <t>S5-09</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11883,88 +11883,88 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Мотовилов</t>
+          <t>Яковлев</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Константинович</t>
+          <t>Леонидович</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>motovilv@gmail.com</t>
+          <t>s.yakovlev@spbu.ru</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>Resonances of a two-particle system on a 1D lattice</t>
+          <t>3-3 рассеяние в системах трёх частиц с короткодействующими и кулоновскими взаимодействиями</t>
         </is>
       </c>
     </row>
     <row r="159" ht="261" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>S5-09</t>
+          <t>S6-02</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Яковлев</t>
+          <t>Кондратьев</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Владимир</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Леонидович</t>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>s.yakovlev@spbu.ru</t>
+          <t>vkondrat@theor.jinr.ru</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>3-3 рассеяние в системах трёх частиц с короткодействующими и кулоновскими взаимодействиями</t>
+          <t>Эффекты динамо и осцилляций в спектрах нейтрино сверхновых</t>
         </is>
       </c>
     </row>
     <row r="160" ht="130.5" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S6-02</t>
+          <t>S6-03</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11973,7 +11973,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12002,14 +12002,14 @@
       </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
-          <t>Эффекты динамо и осцилляций в спектрах нейтрино сверхновых</t>
+          <t>Эффекты намагниченности ядер во взрывном нуклеосинтезе</t>
         </is>
       </c>
     </row>
     <row r="161" ht="246.6" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S6-03</t>
+          <t>S6-04</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12018,21 +12018,16 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Кондратьев</t>
+          <t>Лубашевский</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Владимир</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Николаевич</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12042,19 +12037,19 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>vkondrat@theor.jinr.ru</t>
+          <t>lubashev@jinr.ru</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>Эффекты намагниченности ядер во взрывном нуклеосинтезе</t>
+          <t>Search for rare processes within the νGeN experiment at Kalinin nuclear power plant</t>
         </is>
       </c>
     </row>
     <row r="162" ht="231.95" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S6-04</t>
+          <t>S6-05</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12063,38 +12058,43 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Лубашевский</t>
+          <t>Громов</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Максим</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Борисович</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>НИИЯФ</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>lubashev@jinr.ru</t>
+          <t>gromov@physics.msu.ru</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>Search for rare processes within the νGeN experiment at Kalinin nuclear power plant</t>
+          <t>Precise reactor antineutrino spectrum measurement with TAO detector</t>
         </is>
       </c>
     </row>
     <row r="163" ht="57.95" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S6-05</t>
+          <t>S6-06</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12103,21 +12103,21 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Громов</t>
+          <t>Михеев</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Семён</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Алексеевич</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12127,19 +12127,19 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>gromov@physics.msu.ru</t>
+          <t>semenmihey@gmail.com</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>Precise reactor antineutrino spectrum measurement with TAO detector</t>
+          <t>Условия появления Λ-гиперонов в материи нейтронных звёзд в моделях среднего поля</t>
         </is>
       </c>
     </row>
     <row r="164" ht="130.5" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S6-06</t>
+          <t>S6-07</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12148,43 +12148,38 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Михеев</t>
+          <t>Kabir</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Семён</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Алексеевич</t>
+          <t>Abdul</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>Institute of Space Technology (Islamabad, Pakistan)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>semenmihey@gmail.com</t>
+          <t>kabirkhanak1@gmail.com</t>
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>Условия появления Λ-гиперонов в материи нейтронных звёзд в моделях среднего поля</t>
+          <t>Analysis of radiative capture of proton ¹¹B (p, γ) ¹²C at low energy</t>
         </is>
       </c>
     </row>
     <row r="165" ht="101.45" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S6-07</t>
+          <t>S6-08</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12193,78 +12188,78 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Le</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Abdul</t>
+          <t>Huy Viet</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Institute of Space Technology (Islamabad, Pakistan)</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>kabirkhanak1@gmail.com</t>
+          <t>leviethuy1@duytan.edu.vn</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>Analysis of radiative capture of proton ¹¹B (p, γ) ¹²C at low energy</t>
+          <t>Characterization of the cosmic muon background in the νGeN experiment</t>
         </is>
       </c>
     </row>
     <row r="166" ht="217.5" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S6-08</t>
+          <t>S7-01</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Le</t>
+          <t>Киселев</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Huy Viet</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>ОИЯИ</t>
+          <t>Василий</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Алексеевич</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>leviethuy1@duytan.edu.vn</t>
+          <t>kiselevva@fnkcrio.ru</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t>Characterization of the cosmic muon background in the νGeN experiment</t>
+          <t>Подход к оптимизации распределения поглощенной дозы в биологическом объекте в лучевой терапии пучком ускоренных протонов</t>
         </is>
       </c>
     </row>
     <row r="167" ht="144.95" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>S7-01</t>
+          <t>S7-02</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12273,38 +12268,43 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Киселев</t>
+          <t>Щербаков</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Василий</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Алексеевич</t>
+          <t>Александрович</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>kiselevva@fnkcrio.ru</t>
+          <t>sherbakov.aa15@physics.msu.ru</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>Подход к оптимизации распределения поглощенной дозы в биологическом объекте в лучевой терапии пучком ускоренных протонов</t>
+          <t>Оценка рисков развития радиационно-индуцированных заболеваний при проведении лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="168" ht="174" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>S7-02</t>
+          <t>S7-03</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12313,43 +12313,43 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Щербаков</t>
+          <t>Васильева</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Алина</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Геннадиевна</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>НИЦ КИ ИФВЭ</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>sherbakov.aa15@physics.msu.ru</t>
+          <t>vasilyeva-ag@ihep.ru</t>
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
-          <t>Оценка рисков развития радиационно-индуцированных заболеваний при проведении лучевой терапии</t>
+          <t>Измерение сечения реакции ¹²C(¹²C,X)¹¹C: особенности эксперимента и оценка неопределенностей</t>
         </is>
       </c>
     </row>
     <row r="169" ht="144.95" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>S7-03</t>
+          <t>S7-04</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -12358,21 +12358,21 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Васильева</t>
+          <t>Парменова</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Алина</t>
+          <t>Екатерина</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Геннадиевна</t>
+          <t>Владимировна</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12382,19 +12382,19 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>vasilyeva-ag@ihep.ru</t>
+          <t>Ekaterina.Parmenova@ihep.ru</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>Измерение сечения реакции ¹²C(¹²C,X)¹¹C: особенности эксперимента и оценка неопределенностей</t>
+          <t>Реализация работы с данными КТ в системе планирования ионной лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="170" ht="188.45" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>S7-04</t>
+          <t>S7-05</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -12403,43 +12403,43 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Парменова</t>
+          <t>Петров</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Екатерина</t>
+          <t>Виталий</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Владимировна</t>
+          <t>Валерьевич</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>НИЦ КИ ИФВЭ</t>
+          <t>СПбГУ</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Ekaterina.Parmenova@ihep.ru</t>
+          <t>vitalii17@bk.ru</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t>Реализация работы с данными КТ в системе планирования ионной лучевой терапии</t>
+          <t>Трекинг, измерение энергии и получение диагностических изображений с использованием кремниевых пиксельных сенсоров</t>
         </is>
       </c>
     </row>
     <row r="171" ht="159.6" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>S7-05</t>
+          <t>S7-06</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -12448,43 +12448,43 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Петров</t>
+          <t>Мерзликин</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Виталий</t>
+          <t>Григорий</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Валерьевич</t>
+          <t>Васильевич</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>vitalii17@bk.ru</t>
+          <t>grishamerzlikin@gmail.com</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>Трекинг, измерение энергии и получение диагностических изображений с использованием кремниевых пиксельных сенсоров</t>
+          <t>Реконструкция трёхмерного дозового рапсределения при облучении биологических объектов пучками протонов высокой интенсивности</t>
         </is>
       </c>
     </row>
     <row r="172" ht="203.1" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>S7-06</t>
+          <t>S7-07</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -12493,21 +12493,21 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Мерзликин</t>
+          <t>Яковлев</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Иван</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Андреевич</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12517,19 +12517,19 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>grishamerzlikin@gmail.com</t>
+          <t>iv.a.yakovlev@gmail.com</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>Реконструкция трёхмерного дозового рапсределения при облучении биологических объектов пучками протонов высокой интенсивности</t>
+          <t>Расчет характеристик черенковского детектора для контроля пучков протонов, используемых для флэш-терапии</t>
         </is>
       </c>
     </row>
     <row r="173" ht="159.6" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>S7-07</t>
+          <t>S7-08</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -12538,43 +12538,43 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Яковлев</t>
+          <t>Зябченков</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Владислав</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Олегович</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ОИЯИ</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>iv.a.yakovlev@gmail.com</t>
+          <t>vladislavzyabchenkov@mail.ru</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>Расчет характеристик черенковского детектора для контроля пучков протонов, используемых для флэш-терапии</t>
+          <t>Количественная оценка содержания тория и урана в свинце для радиационной защиты методом ИСП-МС</t>
         </is>
       </c>
     </row>
     <row r="174" ht="159.6" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>S7-08</t>
+          <t>S7-09</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -12583,43 +12583,43 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Зябченков</t>
+          <t>Копылова</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Владислав</t>
+          <t>Екатерина</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Олегович</t>
+          <t>Александровна</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>vladislavzyabchenkov@mail.ru</t>
+          <t>ekaterinakalip@gmail.com</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t>Количественная оценка содержания тория и урана в свинце для радиационной защиты методом ИСП-МС</t>
+          <t>Применение деформируемой регистрации изображений в лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="175" ht="290.1" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>S7-09</t>
+          <t>S7-10</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -12628,43 +12628,38 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Копылова</t>
+          <t>Мамаева</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Екатерина</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Александровна</t>
+          <t>Саргылана</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>СФВУ (Якутия)</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>ekaterinakalip@gmail.com</t>
+          <t>sargylana_mamaeva@mail.ru</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>Применение деформируемой регистрации изображений в лучевой терапии</t>
+          <t>Биофизическая модель электрических характеристик эритроцитов при лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="176" ht="231.95" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>S7-10</t>
+          <t>S7-11</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -12673,38 +12668,43 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Мамаева</t>
+          <t>Мерзликин</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Саргылана</t>
+          <t>Григорий</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Васильевич</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>СФВУ (Якутия)</t>
+          <t>ИЯИ РАН</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>sargylana_mamaeva@mail.ru</t>
+          <t>grishamerzlikin@gmail.com</t>
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t>Биофизическая модель электрических характеристик эритроцитов при лучевой терапии</t>
+          <t>Корректировка и валидация алгоритма оценки прбега протонов в различных матералах на основании КТ-исследований</t>
         </is>
       </c>
     </row>
     <row r="177" ht="217.5" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S7-11</t>
+          <t>S7-12</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -12713,43 +12713,43 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Мерзликин</t>
+          <t>Ашрапов</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Улугбек</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Товфикович</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>INR Uzbekistan</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>grishamerzlikin@gmail.com</t>
+          <t>ashrapov@inp.uz</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>Корректировка и валидация алгоритма оценки прбега протонов в различных матералах на основании КТ-исследований</t>
+          <t>Использование гамма-облученного оксида алюминия для изготовления генераторов технеция-99М</t>
         </is>
       </c>
     </row>
     <row r="178" ht="174" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S7-12</t>
+          <t>S7-13</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12758,43 +12758,38 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Ашрапов</t>
+          <t>Кузьменков</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Улугбек</t>
+          <t>Антон</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Товфикович</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>INR Uzbekistan</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>ashrapov@inp.uz</t>
+          <t>zhelton@yandex.ru</t>
         </is>
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t>Использование гамма-облученного оксида алюминия для изготовления генераторов технеция-99М</t>
+          <t>Фотоядерное получение медицинских изотопов рения на осмиевых и иридиевых мишенях</t>
         </is>
       </c>
     </row>
     <row r="179" ht="318.95" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S7-13</t>
+          <t>S7-14</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12803,38 +12798,38 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Кузьменков</t>
+          <t>Yusupov</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Антон</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Александрович</t>
+          <t>Mirjalol</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>zhelton@yandex.ru</t>
+          <t>ymirjalol@bk.ru</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>Фотоядерное получение медицинских изотопов рения на осмиевых и иридиевых мишенях</t>
+          <t>Ядерные реакции на кислороде, углероде, азоте и боре при облучении протонным пучком 160 МэВ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="318.95" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S7-14</t>
+          <t>S7-15</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12843,38 +12838,43 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Yusupov</t>
+          <t>Пятаев</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Mirjalol</t>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>МКНЦ, МГУ</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>ymirjalol@bk.ru</t>
+          <t>pataevdima2@gmail.com</t>
         </is>
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>Ядерные реакции на кислороде, углероде, азоте и боре при облучении протонным пучком 160 МэВ</t>
+          <t>Исследование влияния термопластических масок на поверхностную дозу и дозовое распределение в лучевой терапии</t>
         </is>
       </c>
     </row>
     <row r="181" ht="231.95" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>S7-15</t>
+          <t>S7-16</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12883,43 +12883,43 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Пятаев</t>
+          <t>Оганян</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Ваге</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Робертович</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>МКНЦ, МГУ</t>
+          <t>МИФИ, МКНЦ</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>pataevdima2@gmail.com</t>
+          <t>vahe.ohanyan2000@yandex.ru</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>Исследование влияния термопластических масок на поверхностную дозу и дозовое распределение в лучевой терапии</t>
+          <t>Биофизическое моделирование распределения температуры при гипертермии: обзор алгоритмов и проектирование расчётного модуля.</t>
         </is>
       </c>
     </row>
     <row r="182" ht="217.5" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>S7-16</t>
+          <t>S7-17</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12928,43 +12928,43 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Оганян</t>
+          <t>Онищук</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ваге</t>
+          <t>Елена</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Робертович</t>
+          <t>Александровна</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>МИФИ, МКНЦ</t>
+          <t>ИАЭ Обнинск</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>vahe.ohanyan2000@yandex.ru</t>
+          <t>elenaonischuk@yandex.ru</t>
         </is>
       </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>Биофизическое моделирование распределения температуры при гипертермии: обзор алгоритмов и проектирование расчётного модуля.</t>
+          <t>Optimization of photoneutron source parameters for boron neutron capture therapy</t>
         </is>
       </c>
     </row>
     <row r="183" ht="159.6" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>S7-17</t>
+          <t>S7-18</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12973,43 +12973,43 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Онищук</t>
+          <t>Балачков</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Максим</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Александровна</t>
+          <t>Михайлович</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>ИАЭ Обнинск</t>
+          <t>ТПУ (Томск)</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>elenaonischuk@yandex.ru</t>
+          <t>mmb2@tpu.ru</t>
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>Optimization of photoneutron source parameters for boron neutron capture therapy</t>
+          <t>Спектральные измерения пучка быстрых нейтронов циклотрона У-120</t>
         </is>
       </c>
     </row>
     <row r="184" ht="174" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>S7-18</t>
+          <t>S7-19</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -13018,43 +13018,43 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Балачков</t>
+          <t>Сабуров</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Вячеслав</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Михайлович</t>
+          <t>Олегович</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>ТПУ (Томск)</t>
+          <t>МРНЦ им. А.Ф. Цыба</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>mmb2@tpu.ru</t>
+          <t>vosaburov@gmail.com</t>
         </is>
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>Спектральные измерения пучка быстрых нейтронов циклотрона У-120</t>
+          <t>Статус проекта по созданию комплекса нейтронной терапии на базе компактного нейтронного генератора НГ-24МТ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="275.45" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>S7-19</t>
+          <t>S7-20</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -13063,21 +13063,21 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Сабуров</t>
+          <t>Соловьев</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Вячеслав</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Олегович</t>
+          <t>Николаевич</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13087,19 +13087,19 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>vosaburov@gmail.com</t>
+          <t>salonf@mrrc.obninsk.ru</t>
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>Статус проекта по созданию комплекса нейтронной терапии на базе компактного нейтронного генератора НГ-24МТ</t>
+          <t>Особенности вычислительного прогнозирования отклика ионизационных камер для радиотерапевтического применения</t>
         </is>
       </c>
     </row>
     <row r="186" ht="203.1" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>S7-20</t>
+          <t>S7-21</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -13108,43 +13108,43 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Соловьев</t>
+          <t>Хуцистова</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Алана</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Отариевна</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>МРНЦ им. А.Ф. Цыба</t>
+          <t>МГУ</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>salonf@mrrc.obninsk.ru</t>
+          <t>www.alanakhutS1@mail.ru</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>Особенности вычислительного прогнозирования отклика ионизационных камер для радиотерапевтического применения</t>
+          <t>Моделирование комбинированного воздействия ионизирующего излучения и озона для стерилизации биоматериалов</t>
         </is>
       </c>
     </row>
     <row r="187" ht="217.5" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>S7-21</t>
+          <t>S7-22</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -13153,21 +13153,21 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Хуцистова</t>
+          <t>Запорожская</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Алана</t>
+          <t>Ксения</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Отариевна</t>
+          <t>Васильевна</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -13177,19 +13177,19 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>www.alanakhutS1@mail.ru</t>
+          <t>zaporozhskayakv@my.msu.ru</t>
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>Моделирование комбинированного воздействия ионизирующего излучения и озона для стерилизации биоматериалов</t>
+          <t>Применение шумоподавляющих фильтров при плёночной дозиметрии радиохирургических планов лечения</t>
         </is>
       </c>
     </row>
     <row r="188" ht="231.95" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>S7-22</t>
+          <t>S7-23</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -13198,21 +13198,21 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Запорожская</t>
+          <t>Новикова</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ксения</t>
+          <t>Евгения</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Васильевна</t>
+          <t>Антоновна</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -13222,19 +13222,19 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>zaporozhskayakv@my.msu.ru</t>
+          <t>evgeniyanovikovazar@gmail.com</t>
         </is>
       </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t>Применение шумоподавляющих фильтров при плёночной дозиметрии радиохирургических планов лечения</t>
+          <t>Методика дозиметрии источника для электронной поверхностной брахитерапии</t>
         </is>
       </c>
     </row>
     <row r="189" ht="246.6" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>S7-23</t>
+          <t>S7-24</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -13243,84 +13243,40 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Новикова</t>
+          <t>Петрова</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Евгения</t>
+          <t>Кристина</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Антоновна</t>
+          <t>Алексеевна</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>СФВУ (Якутия)</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>evgeniyanovikovazar@gmail.com</t>
+          <t>kristinan_1604@mail.ru</t>
         </is>
       </c>
       <c r="I189" s="4" t="inlineStr">
         <is>
-          <t>Методика дозиметрии источника для электронной поверхностной брахитерапии</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="304.5" customHeight="1">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>S7-24</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>24</v>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Петрова</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Кристина</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Алексеевна</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>СФВУ (Якутия)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>kristinan_1604@mail.ru</t>
-        </is>
-      </c>
-      <c r="I190" s="4" t="inlineStr">
-        <is>
           <t>Накопление золошлаковых отходов и выбросов котельного комплекса и рост онкологической заболеваемости</t>
         </is>
       </c>
     </row>
+    <row r="190" ht="304.5" customHeight="1"/>
     <row r="191" ht="159.6" customHeight="1"/>
     <row r="192" ht="174" customHeight="1"/>
     <row r="193" ht="261" customHeight="1"/>
@@ -15132,7 +15088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15321,6 +15277,21 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>46289.45625</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Доклад П. В. Кострюкова (секция 1, пятница) снят. Остальные доклады этого заседания сдвинуты вперёд, начало по-прежнему в 14:00.</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>P. V. Kostryukov’s talk (section 1, Friday) is removed. The other talks in that sitting move up; it still starts at 14:00.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/programme.xlsx
+++ b/data/programme.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Секции" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Блоки" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Доклады" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Постеры" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Изменения" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Настройки" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Секции" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Блоки" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Доклады" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Постеры" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Изменения" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Купряшкин И. В.</t>
+          <t>Кепагорин М. Г.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>I. V. Kupryashkin</t>
+          <t>M. G. Kepagorbain</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Купряшкин И. В.</t>
+          <t>Кепагорин М. Г.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>I. V. Kupryashkin</t>
+          <t>M. G. Kepagorbain</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Купряшкин И. В.</t>
+          <t>Кепагорин М. Г.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>I. V. Kupryashkin</t>
+          <t>M. G. Kepagorbain</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Чувильский Ю. М.</t>
+          <t>Кавибуский К. П.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Yu. M. Tchuvil'sky</t>
+          <t>K. P. Kavibubskiy</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Чувильский Ю. М.</t>
+          <t>Кавибуский К. П.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Yu. M. Tchuvil'sky</t>
+          <t>K. P. Kavibubskiy</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Чувильский Ю. М.</t>
+          <t>Кавибуский К. П.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Yu. M. Tchuvil'sky</t>
+          <t>K. P. Kavibubskiy</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Сидорчук С. И.</t>
+          <t>Десувикл Л. Б.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>S. I. Sidorchuk</t>
+          <t>L. B. Desuviklb</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Сидорчук С. И.</t>
+          <t>Десувикл Л. Б.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>S. I. Sidorchuk</t>
+          <t>L. B. Desuviklb</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Сидорчук С. И.</t>
+          <t>Десувикл Л. Б.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>S. I. Sidorchuk</t>
+          <t>L. B. Desuviklb</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Сидорчук С. И.</t>
+          <t>Десувикл Л. Б.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>S. I. Sidorchuk</t>
+          <t>L. B. Desuviklb</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Сидорчук С. И.</t>
+          <t>Десувикл Л. Б.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>S. I. Sidorchuk</t>
+          <t>L. B. Desuviklb</t>
         </is>
       </c>
     </row>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>И. Н. Изосимов</t>
+          <t>Д. Д. Тенамсов</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>I. N. Izosimov</t>
+          <t>D. D. Tenamsov</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>И. А. Митропольский</t>
+          <t>Р. Л. Монапопоаский</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>I. A. Mitropolsky</t>
+          <t>R. L. Monappaskiy</t>
         </is>
       </c>
     </row>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>А. А. Дзюба</t>
+          <t>П. Н. Рориб</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>A. A. Dzyuba</t>
+          <t>P. N. Roribb</t>
         </is>
       </c>
     </row>
@@ -1931,12 +1931,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>В. О. Сабуров</t>
+          <t>М. М. Супалов</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>V. O. Saburov</t>
+          <t>M. M. Supalov</t>
         </is>
       </c>
     </row>
@@ -2008,12 +2008,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Титова Л. В.</t>
+          <t>Бусова Д. Г.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L. V. Titova</t>
+          <t>D. G. Busova</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Титова Л. В.</t>
+          <t>Бусова Д. Г.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L. V. Titova</t>
+          <t>D. G. Busova</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Титова Л. В.</t>
+          <t>Бусова Д. Г.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>L. V. Titova</t>
+          <t>D. G. Busova</t>
         </is>
       </c>
     </row>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Чувильский Ю. М.</t>
+          <t>Кавибуский К. П.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Yu. M. Tchuvil'sky</t>
+          <t>K. P. Kavibubskiy</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Чувильский Ю. М.</t>
+          <t>Кавибуский К. П.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Yu. M. Tchuvil'sky</t>
+          <t>K. P. Kavibubskiy</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Чувильский Ю. М.</t>
+          <t>Кавибуский К. П.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Yu. M. Tchuvil'sky</t>
+          <t>K. P. Kavibubskiy</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2361,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>И. А. Мазур</t>
+          <t>К. С. Неров</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>I. A. Mazur</t>
+          <t>K. S. Nerov</t>
         </is>
       </c>
     </row>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>А. С. Демьянова</t>
+          <t>П. В. Гопавнова</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A. S. Demyanova</t>
+          <t>P. V. Gopavnova</t>
         </is>
       </c>
     </row>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Г. А. Феофилов</t>
+          <t>М. Л. Лагогпов</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>G. A. Feofilov</t>
+          <t>M. L. Lagogpov</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>О. В. Белов</t>
+          <t>М. Н. Балов</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O. V. Belov</t>
+          <t>M. N. Balov</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>А. С. Демьянова</t>
+          <t>П. В. Гопавнова</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>A. S. Demyanova</t>
+          <t>P. V. Gopavnova</t>
         </is>
       </c>
     </row>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>В. И. Жеребчевский</t>
+          <t>С. К. Тамирадеский</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>V. I. Zherebchevsky</t>
+          <t>S. K. Tamiradebskiy</t>
         </is>
       </c>
     </row>
@@ -2638,12 +2638,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Д. Прохорова</t>
+          <t>К. Сакакдова</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>D. Prokhorova</t>
+          <t>K. Sakakdbova</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>А. П. Черняев</t>
+          <t>Л. Д. Вефасев</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A. P. Chernyaev</t>
+          <t>L. D. Vefasbaev</t>
         </is>
       </c>
     </row>
@@ -2761,12 +2761,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Жеребчевский В. И.</t>
+          <t>Тамирадеский С. К.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>V. I. Zherebchevsky</t>
+          <t>S. K. Tamiradebskiy</t>
         </is>
       </c>
     </row>
@@ -2812,12 +2812,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Жеребчевский В. И.</t>
+          <t>Тамирадеский С. К.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>V. I. Zherebchevsky</t>
+          <t>S. K. Tamiradebskiy</t>
         </is>
       </c>
     </row>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Жеребчевский В. И.</t>
+          <t>Тамирадеский С. К.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>V. I. Zherebchevsky</t>
+          <t>S. K. Tamiradebskiy</t>
         </is>
       </c>
     </row>
@@ -2945,12 +2945,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Черняев А. П.</t>
+          <t>Вефасев Л. Д.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>A. P. Chernyaev</t>
+          <t>L. D. Vefasbaev</t>
         </is>
       </c>
     </row>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Черняев А. П.</t>
+          <t>Вефасев Л. Д.</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>A. P. Chernyaev</t>
+          <t>L. D. Vefasbaev</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Черняев А. П.</t>
+          <t>Вефасев Л. Д.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>A. P. Chernyaev</t>
+          <t>L. D. Vefasbaev</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Д. М. Родкин</t>
+          <t>Б. Н. Гувлин</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>D. M. Rodkin</t>
+          <t>B. N. Guvlin</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3155,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Д. Е. Любашевский</t>
+          <t>П. Т. Сутадаиский</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>D. E. Lyubashevsky</t>
+          <t>P. T. Sutadaibskiy</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>А. И. Мазур</t>
+          <t>Л. Р. Бунип</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>A. I. Mazur</t>
+          <t>L. R. Bunip</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>А. С. Чепурнов</t>
+          <t>Ф. Л. Латандов</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A. S. Chepurnov</t>
+          <t>F. L. Latandbov</t>
         </is>
       </c>
     </row>
@@ -3350,12 +3350,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Нестеренко В.</t>
+          <t>Ракефренко Д.</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>V. Nesterenko</t>
+          <t>D. Rakefrenko</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Нестеренко В.</t>
+          <t>Ракефренко Д.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>V. Nesterenko</t>
+          <t>D. Rakefrenko</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Нестеренко В.</t>
+          <t>Ракефренко Д.</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>V. Nesterenko</t>
+          <t>D. Rakefrenko</t>
         </is>
       </c>
     </row>
@@ -3534,12 +3534,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Яковлев С. Л.</t>
+          <t>Фафовев Т. Р.</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>S. L. Yakovlev</t>
+          <t>T. R. Fafovbev</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Яковлев С. Л.</t>
+          <t>Фафовев Т. Р.</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>S. L. Yakovlev</t>
+          <t>T. R. Fafovbev</t>
         </is>
       </c>
     </row>
@@ -3636,12 +3636,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Яковлев С. Л.</t>
+          <t>Фафовев Т. Р.</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>S. L. Yakovlev</t>
+          <t>T. R. Fafovbev</t>
         </is>
       </c>
     </row>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Пшеничнов И. А.</t>
+          <t>Мувилонов М. М.</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>I. A. Pshenichnov</t>
+          <t>M. M. Muvilonbaov</t>
         </is>
       </c>
     </row>
@@ -3826,12 +3826,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Пшеничнов И. А.</t>
+          <t>Мувилонов М. М.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>I. A. Pshenichnov</t>
+          <t>M. M. Muvilonbaov</t>
         </is>
       </c>
     </row>
@@ -3877,12 +3877,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Пшеничнов И. А.</t>
+          <t>Мувилонов М. М.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>I. A. Pshenichnov</t>
+          <t>M. M. Muvilonbaov</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Мочалов В. В.</t>
+          <t>Дакафов Д. Л.</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>V. V. Mochalov</t>
+          <t>D. L. Dakafbov</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Мочалов В. В.</t>
+          <t>Дакафов Д. Л.</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>V. V. Mochalov</t>
+          <t>D. L. Dakafbov</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Мочалов В. В.</t>
+          <t>Дакафов Д. Л.</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>V. V. Mochalov</t>
+          <t>D. L. Dakafbov</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>О. А. Рубцова</t>
+          <t>Н. С. Ланрова</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O. A. Rubtsova</t>
+          <t>N. S. Lanrbova</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>М. А. Науменко</t>
+          <t>В. Ф. Докзенко</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>M. A. Naumenko</t>
+          <t>V. F. Dokzenko</t>
         </is>
       </c>
     </row>
@@ -4210,12 +4210,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>А. В. Канцырев</t>
+          <t>Р. Б. Санебпев</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>A. V. Kantsyrev</t>
+          <t>R. B. Sanebpbev</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4251,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>А. А. Зайцев</t>
+          <t>Б. Р. Тавпев</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>A. A. Zaitsev</t>
+          <t>B. R. Tavpbev</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>А. В. Канцырев</t>
+          <t>Р. Б. Санебпев</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>A. V. Kantsyrev</t>
+          <t>R. B. Sanebpbev</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>А. А. Зайцев</t>
+          <t>Б. Р. Тавпев</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>A. A. Zaitsev</t>
+          <t>B. R. Tavpbev</t>
         </is>
       </c>
     </row>
@@ -4405,12 +4405,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>С. Мамаева</t>
+          <t>П. Надпева</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>S. Mamaeva</t>
+          <t>P. Nadpeva</t>
         </is>
       </c>
     </row>
@@ -4456,12 +4456,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Мазур А. И.</t>
+          <t>Бунип Л. Р.</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>A. I. Mazur</t>
+          <t>L. R. Bunip</t>
         </is>
       </c>
     </row>
@@ -4507,12 +4507,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Мазур А. И.</t>
+          <t>Бунип Л. Р.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>A. I. Mazur</t>
+          <t>L. R. Bunip</t>
         </is>
       </c>
     </row>
@@ -4558,12 +4558,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Мазур А. И.</t>
+          <t>Бунип Л. Р.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>A. I. Mazur</t>
+          <t>L. R. Bunip</t>
         </is>
       </c>
     </row>
@@ -4661,12 +4661,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>С. Мамаева</t>
+          <t>П. Надпева</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>S. Mamaeva</t>
+          <t>P. Nadpeva</t>
         </is>
       </c>
     </row>
@@ -4821,22 +4821,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Боос</t>
+          <t>Бафт</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Эдуард</t>
+          <t>Мудобн</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Эрнстович</t>
+          <t>Ведадович</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>boos@theory.sinp.msu.ru</t>
+          <t>baftlepeset@example.org</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -4866,22 +4866,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Колганова</t>
+          <t>Кодоксова</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Довба</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Александровна</t>
+          <t>Рагокалаковна</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>kea@theor.jinr.ru</t>
+          <t>kodok@example.org</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -4911,22 +4911,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Джолос</t>
+          <t>Кезимр</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ростислав</t>
+          <t>Логугобур</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Тапепенкович</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>jolos@theor.jinr.ru</t>
+          <t>kezimrs@example.org</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lednicky</t>
+          <t>Nokoucky</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Devenan</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>lednicky@jinr.ru</t>
+          <t>noko@example.org</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -5006,22 +5006,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Жеребчевский</t>
+          <t>Тамирадеский</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Сасемигб</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Иосифович</t>
+          <t>Кесугович</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>v.zherebchevsky@spbu.ru</t>
+          <t>tamiradebsk@example.org</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Чувильский</t>
+          <t>Кавибуский</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Юрий</t>
+          <t>Кеий</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Михайлович</t>
+          <t>Полевлович</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>tchuvlyuri@gmail.com</t>
+          <t>kavibubs@example.org</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -5106,22 +5106,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Лубсандоржиев</t>
+          <t>Ронобубаколев</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Баярто</t>
+          <t>Садоба</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Константинович</t>
+          <t>Немофарогкович</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>lubsand@rambler.ru</t>
+          <t>ronobu@example.org</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -5156,22 +5156,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Бредихин</t>
+          <t>Ладевмин</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Подк</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Сергеевич</t>
+          <t>Нафогевич</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ivan@gammatech.pro</t>
+          <t>ladevm@example.org</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -5221,22 +5221,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Пашков</t>
+          <t>Порвов</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Кедегимус</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Рапополмович</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>av.pashkov@edigitizer.ru</t>
+          <t>porvovladozi@example.org</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -5286,17 +5286,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ходаков</t>
+          <t>Тасаров</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Фагикд</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>rodionova@spegroup.ru</t>
+          <t>tasarovte@example.org</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -5346,22 +5346,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Сидорчук</t>
+          <t>Десувикл</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Лароей</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Иванович</t>
+          <t>Бундович</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>sidorchuk@jinr.ru</t>
+          <t>desuv@example.org</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -5396,22 +5396,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ларионова</t>
+          <t>Гилосмова</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Дарья</t>
+          <t>Навтя</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Максимовна</t>
+          <t>Буфонтовна</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>dashalario@gmail.com</t>
+          <t>gilosmov@example.org</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -5446,22 +5446,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ким</t>
+          <t>Саф</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Виктор</t>
+          <t>Фаледл</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Тимофеевич</t>
+          <t>Напенлевич</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>victor.t.kim@gmail.com</t>
+          <t>safgukavel@example.org</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Коваленко</t>
+          <t>Канесенко</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Фонанирв</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Фонетмевич</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>v.kovalenko@spbu.ru</t>
+          <t>kanesen@example.org</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -5546,22 +5546,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Мочалов</t>
+          <t>Дакафов</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Василий</t>
+          <t>Дотегуй</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Вадимович</t>
+          <t>Лофолович</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>mochalov@ihep.ru</t>
+          <t>daka@example.org</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -5596,22 +5596,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Белов</t>
+          <t>Балов</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Олег</t>
+          <t>Мукф</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Валерьевич</t>
+          <t>Наридревич</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>oleg.belov@jinr.int</t>
+          <t>balovka@example.org</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -5646,22 +5646,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Колупаева</t>
+          <t>Катарсева</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Людмила</t>
+          <t>Панекра</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Дмитриевна</t>
+          <t>Пегопсевна</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>kolupaeva@jinr.ru</t>
+          <t>katar@example.org</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -5696,22 +5696,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Черняев</t>
+          <t>Вефасев</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Лолосурин</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Петрович</t>
+          <t>Донлович</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>a.p.chernyaev@yandex.ru</t>
+          <t>vefasbaevde@example.org</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -5744,22 +5744,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Шитов</t>
+          <t>Тебов</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Дегунл</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Игоревич</t>
+          <t>Лагфевич</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>schitov.mih@mail.ru</t>
+          <t>tebbovv@example.org</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -5794,22 +5794,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Апарин</t>
+          <t>Навлин</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Велебуй</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Мисегувенович</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>aparin@jinr.ru</t>
+          <t>na@example.org</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -5844,22 +5844,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Свирихин</t>
+          <t>Зипонкин</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Колонолоп</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Игоревич</t>
+          <t>Бузфевич</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>asvirikhin@jinr.ru</t>
+          <t>ziponk@example.org</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -5894,22 +5894,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Балдин</t>
+          <t>Госрин</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Антон</t>
+          <t>Вонол</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Рападедебович</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>an.baldin@mail.ru</t>
+          <t>gosri@example.org</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -5944,22 +5944,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Боос</t>
+          <t>Бафт</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Эдуард</t>
+          <t>Мудобн</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Эрнстович</t>
+          <t>Ведадович</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>boos@theory.sinp.msu.ru</t>
+          <t>baftlepeset@example.org</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -5994,22 +5994,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Пшеничнов</t>
+          <t>Мувилонов</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Муриь</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Анатольевич</t>
+          <t>Мупалафевич</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>pshenich@inr.ru</t>
+          <t>muv@example.org</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -6044,22 +6044,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Картавцев</t>
+          <t>Бугиталев</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Олег</t>
+          <t>Вобф</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Иванович</t>
+          <t>Вевкович</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>oik@jinr.ru</t>
+          <t>b@example.org</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -6094,22 +6094,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Воронин</t>
+          <t>Некекин</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Лапамурб</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Пеникодвович</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>voronin_vv@pnpi.nrcki.ru</t>
+          <t>nekekinlopeg@example.org</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -6144,22 +6144,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Гаганов</t>
+          <t>Фородов</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Валерий</t>
+          <t>Сугизий</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Валерьевич</t>
+          <t>Миногсевич</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>gavaler@rambler.ru</t>
+          <t>forodo@example.org</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -6194,22 +6194,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Варламов</t>
+          <t>Зисаптов</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Лоризилм</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Низиргевич</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>vvvarlamov@gmail.com</t>
+          <t>zisaptov@example.org</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -6244,17 +6244,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Нестеренко</t>
+          <t>Ракефренко</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Валентин</t>
+          <t>Допакевл</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>nester@theor.jinr.ru</t>
+          <t>rakefren@example.org</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -6289,22 +6289,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Титова</t>
+          <t>Бусова</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Лариса</t>
+          <t>Детева</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Витальевна</t>
+          <t>Гогидкевна</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>titova_lv@phys.vsu.ru</t>
+          <t>busovakov@example.org</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -6339,22 +6339,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Любашевский</t>
+          <t>Сутадаиский</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Пезирой</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Евгеньевич</t>
+          <t>Табагсевич</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>dima_physicist@mail.ru</t>
+          <t>sutadaibsk@example.org</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -6389,22 +6389,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Сороковиков</t>
+          <t>Гопозиниров</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Расулд</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Локопгевич</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>sorokovikov@jinr.ru</t>
+          <t>gopozin@example.org</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Чепурнов</t>
+          <t>Латандов</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Фозитабув</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Сергеевич</t>
+          <t>Леригевич</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>aschepurnov@yandex.ru</t>
+          <t>latandbov@example.org</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -6489,22 +6489,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Прусаченко</t>
+          <t>Кедоргенко</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Павел</t>
+          <t>Тевед</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Сергеевич</t>
+          <t>Моносевич</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>prusachenko@jinr.ru</t>
+          <t>kedorge@example.org</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -6537,17 +6537,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ефимов</t>
+          <t>Лепнов</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Набулопос</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>efimov98@mail.ru</t>
+          <t>lepn@example.org</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -6582,22 +6582,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Дзюба</t>
+          <t>Рориб</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Подепой</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Налелагифович</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>dzyuba_aa@pnpi.nrcki.ru</t>
+          <t>roribblesav@example.org</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -6632,22 +6632,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Родкин</t>
+          <t>Гувлин</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Бупотай</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Михайлович</t>
+          <t>Неповзович</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>rodkindm92@gmail.com</t>
+          <t>guvlinvi@example.org</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -6680,27 +6680,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Рубцова</t>
+          <t>Ланрова</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ольга</t>
+          <t>Нибга</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Андреевна</t>
+          <t>Салемевна</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ЛАРЕН</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>rubtsova-olga@yandex.ru</t>
+          <t>lanrbovaguk@example.org</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -6725,27 +6725,27 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Третьякова</t>
+          <t>Рононанова</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Татьяна</t>
+          <t>Зифодра</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Юрьевна</t>
+          <t>Подевна</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ЛАРЕН</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>tretyakova@sinp.msu.ru</t>
+          <t>rononanova@example.org</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -6770,22 +6770,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Плеханов</t>
+          <t>Телелсов</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Владимир Г.</t>
+          <t>Фанивобд К.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Garon Sci. Lab., Fonoriton LtD (Tallinn, Estonia)</t>
+          <t>Miral Sci. Lab., Polverton LtD (Ostwick, Valeria)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>vgplekhanov@gmail.com</t>
+          <t>telelsovs@example.org</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -6810,27 +6810,27 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Мазур</t>
+          <t>Неров</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Косуь</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Сарадогурович</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ИЯИ</t>
+          <t>ВИР</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>mazur@inr.ru</t>
+          <t>n@example.org</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -6855,22 +6855,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Пермяков</t>
+          <t>Лотексов</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Евгений</t>
+          <t>Нелелой</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ИЯИ</t>
+          <t>ВИР</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>zhenya-10000@yandex.ru</t>
+          <t>loteksovvo@example.org</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -6895,22 +6895,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Мосунов</t>
+          <t>Зиропов</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Данотм</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ЛАРЕН</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>mosunov.mm19@physics.msu.ru</t>
+          <t>ziropovsulomomo@example.org</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -6935,27 +6935,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Шарыпов</t>
+          <t>Фосазов</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Роман</t>
+          <t>Намуг</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Эдуардович</t>
+          <t>Ловогмович</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ТОГУ</t>
+          <t>РИВН</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2017104939@pnu.edu.ru</t>
+          <t>fosazovfo@example.org</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -6980,27 +6980,27 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Изосимов</t>
+          <t>Тенамсов</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Далоь</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Давортевич</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>izosimov@jinr.ru</t>
+          <t>tena@example.org</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -7025,27 +7025,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Арутюнова</t>
+          <t>Небулпова</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Анастасия</t>
+          <t>Нифоровмя</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Юрьевна</t>
+          <t>Падевна</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>КИ-ПИЯФ</t>
+          <t>ОТ-СЕЛМ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>arutiunova_ai@pnpi.nrcki.ru</t>
+          <t>nebulpovakadovo@example.org</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -7070,27 +7070,27 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Быстряков</t>
+          <t>Фотегилов</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Артём</t>
+          <t>Кагун</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Дмитриевич</t>
+          <t>Супалпевич</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>bystryakov-a@jinr.ru</t>
+          <t>fotegilo@example.org</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -7115,27 +7115,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Митропольский</t>
+          <t>Монапопоаский</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Рапб</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Лесавевич</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ПИЯФ</t>
+          <t>СЕЛМ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Mitropolsky_IA@pnpi.nrcki.ru</t>
+          <t>monappaskiysukam@example.org</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -7160,27 +7160,27 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Стовпец</t>
+          <t>Петагор</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Даниил</t>
+          <t>Будефв</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Евгеньевич</t>
+          <t>Гидесбевич</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stovpets@theor.jinr.ru</t>
+          <t>petagordal@example.org</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -7205,22 +7205,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Фомина</t>
+          <t>Нотина</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Мария</t>
+          <t>Нервя</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>masjnj.89@gmail.com</t>
+          <t>notinab@example.org</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -7245,27 +7245,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Гусев</t>
+          <t>Мизев</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Илья</t>
+          <t>Додя</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Сергеевич</t>
+          <t>Фонедевич</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>МИФИ</t>
+          <t>ТЕЗО</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ilya_ilua_gusev@mail.ru</t>
+          <t>mizevvekemu@example.org</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -7290,27 +7290,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Северюхин</t>
+          <t>Вемопогин</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Момофай</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Павлович</t>
+          <t>Мозрович</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>sever@theor.jinr.ru</t>
+          <t>vemopog@example.org</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -7335,22 +7335,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Арсеньев</t>
+          <t>Таналрев</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Николай</t>
+          <t>Ветазий</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>arsenev@theor.jinr.ru</t>
+          <t>tanalrevk@example.org</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -7375,27 +7375,27 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Чуйкина</t>
+          <t>Бусмина</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Анастасия</t>
+          <t>Кавовомпя</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Владимировна</t>
+          <t>Нивекодповна</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ВНИИЭФ</t>
+          <t>БАРХАН</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>chuikina.av@mail.ru</t>
+          <t>busmina@example.org</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -7420,27 +7420,27 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Расулова</t>
+          <t>Допесова</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Фазилат</t>
+          <t>Вовикон</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Абдувалиевна</t>
+          <t>Самодолревна</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>rasulova@jinr.ru</t>
+          <t>dope@example.org</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -7465,22 +7465,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Усманов</t>
+          <t>Тенолов</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Пазлитдин</t>
+          <t>Гимирапам</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Наманганский государственный технический университет (Наманган, Узбекистан)</t>
+          <t>Северный политехнический университет прибрежного края (Северград, Валмерия)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>usmanov1956.56@mail.ru</t>
+          <t>tenolovvis@example.org</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -7505,22 +7505,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Rosn</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Yanzhao</t>
+          <t>Zisateo</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>ТПУ (Томск</t>
+          <t>КРН (Берег</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>yanchzhao1@tpu.ru</t>
+          <t>rosnd@example.org</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -7545,27 +7545,27 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Косарев</t>
+          <t>Рогуфев</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Лебугл</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Сергеевич</t>
+          <t>Веконевич</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>mkosarev2000@mail.ru</t>
+          <t>rogufevp@example.org</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -7590,27 +7590,27 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Смольянников</t>
+          <t>Радегидатлов</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Нафарой</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Юрьевич</t>
+          <t>Гупевич</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>dsmoliannikov@theor.jinr.ru</t>
+          <t>radegidatlovpob@example.org</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -7635,27 +7635,27 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Воинов</t>
+          <t>Могпов</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Лефакай</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Анатольевич</t>
+          <t>Зироведевич</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>voinov@jinr.ru</t>
+          <t>mo@example.org</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -7680,22 +7680,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Стегайлов</t>
+          <t>Пафадовов</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Гусувекс</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stega@jinr.ru</t>
+          <t>p@example.org</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -7720,22 +7720,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Моисеев</t>
+          <t>Гифофев</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Пенота</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>moiseev@theor.jinr.ru</t>
+          <t>gifofevda@example.org</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -7760,27 +7760,27 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Молодцова</t>
+          <t>Догобпова</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ирина</t>
+          <t>Ритна</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Владимировна</t>
+          <t>Тесапамвовна</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>molod@theor.jinr.ru</t>
+          <t>dogobpo@example.org</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -7807,27 +7807,27 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Демьянова</t>
+          <t>Гопавнова</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Алла</t>
+          <t>Пока</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Сергеевна</t>
+          <t>Вигувевна</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>БАР ОТ</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>a.s.demyanova@bk.ru</t>
+          <t>gopavno@example.org</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -7854,27 +7854,27 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Соловьев</t>
+          <t>Веласгев</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Ленидесап</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Сергеевич</t>
+          <t>Ковезевич</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>ВНИИА</t>
+          <t>ПЛИОН</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>alexander.solovyev@mail.ru</t>
+          <t>velasgevgonavi@example.org</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -7901,27 +7901,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Куликов</t>
+          <t>Левинов</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Василий</t>
+          <t>Кесугий</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Даводевич</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ЛАРЕН</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>kulikov@nucl-th.sinp.msu.ru</t>
+          <t>levinovpaparopa@example.org</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -7948,22 +7948,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Shakhov</t>
+          <t>Baribov</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aleksei</t>
+          <t>Sebakoo</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>shahov@jinr.ru</t>
+          <t>ba@example.org</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -7990,27 +7990,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Егоров</t>
+          <t>Кагтов</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Деканз</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Викторович</t>
+          <t>Зитездович</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ТГУ(Томск)</t>
+          <t>ЯРЬ(Берег)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>egorovphys@mail.ru</t>
+          <t>kagtov@example.org</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -8037,27 +8037,27 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Яников</t>
+          <t>Сенвов</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Устин</t>
+          <t>Кегус</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Михайлович</t>
+          <t>Кевелмович</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ЛАРЕН</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>yanikov-u@yandex.ru</t>
+          <t>senvovm@example.org</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -8082,27 +8082,27 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Изосимов</t>
+          <t>Тенамсов</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Далоь</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Давортевич</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>izosimov@jinr.ru</t>
+          <t>tena@example.org</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -8129,22 +8129,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tran</t>
+          <t>Voks</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ngoc TOan</t>
+          <t>Gunl DEmv</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>chan@jinr.ru</t>
+          <t>v@example.org</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -8171,27 +8171,27 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Уланова</t>
+          <t>Гопвова</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ирина</t>
+          <t>Рабра</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ивановна</t>
+          <t>Ловдовна</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>ulanova@jinr.ru</t>
+          <t>gop@example.org</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -8216,27 +8216,27 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Шевчик</t>
+          <t>Микелп</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Егор</t>
+          <t>Зирд</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Мивифевич</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>shevchik@jinr.ru</t>
+          <t>mike@example.org</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -8263,22 +8263,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Shehada</t>
+          <t>Peguvek</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Abdullah</t>
+          <t>Lanebudm</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>shikhada@jinr.ru</t>
+          <t>pegu@example.org</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -8305,27 +8305,27 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fedorov</t>
+          <t>Votebov</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nikita</t>
+          <t>Bagina</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Alexandrovich</t>
+          <t>Gikamovgovich</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>na.fedorov@physics.msu.ru</t>
+          <t>votebovmovemu@example.org</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -8350,22 +8350,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Грозданов</t>
+          <t>Рапегутов</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Димитър</t>
+          <t>Ледабуб</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>dimitar@nf.jinr.ru</t>
+          <t>rapegu@example.org</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -8390,27 +8390,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Демичев</t>
+          <t>Бусекев</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Лепент</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Керадевич</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>mdemichev@jinr.ru</t>
+          <t>busek@example.org</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -8435,27 +8435,27 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ким</t>
+          <t>Нит</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Говеой</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Фасемодонович</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>КВУ</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>kim@srd.sinp.msu.ru</t>
+          <t>nitnala@example.org</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -8480,27 +8480,27 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Давыдов</t>
+          <t>Новипов</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Зитеданаг</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Иванович</t>
+          <t>Рисмович</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ЛАРЕН</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>aleksander.davydov@physmsu.ru</t>
+          <t>novipovpodanorapo@example.org</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -8525,27 +8525,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Титова</t>
+          <t>Бусова</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Лариса</t>
+          <t>Детева</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Витальевна</t>
+          <t>Гогидкевна</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ВГУ</t>
+          <t>ЛУГ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>titova_lv@phys.vsu.ru</t>
+          <t>busovakov@example.org</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -8570,27 +8570,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Любашевский</t>
+          <t>Сутадаиский</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Пезирой</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Евгеньевич</t>
+          <t>Табагсевич</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ВГУ</t>
+          <t>ЛУГ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>dima_physicist@mail.ru</t>
+          <t>sutadaibsk@example.org</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -8615,22 +8615,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Abdullah</t>
+          <t>Teninofl</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Md. Nure Alam</t>
+          <t>Bp. Kasa Fagl</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Department of Physics, Jagannath University (Dhaka, Bangladesh)</t>
+          <t>Department of Physics, Lirenthal University (Ostia, Valemarcha)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>abdullah@phy.jnu.ac.bd</t>
+          <t>teninoflna@example.org</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -8657,22 +8657,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Галюзов</t>
+          <t>Догифов</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Булаай</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ВНИИА</t>
+          <t>ПЛИОН</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>agar10@yandex.ru</t>
+          <t>dogi@example.org</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -8699,22 +8699,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Музалевский</t>
+          <t>Миковеоский</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Римв</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>muzalevsky@jinr.ru</t>
+          <t>mikove@example.org</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -8741,27 +8741,27 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Naumenko</t>
+          <t>Dokzenko</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mikhail</t>
+          <t>Velobav</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Alekseyevich</t>
+          <t>Fasepetevich</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>anaumenko@jinr.ru</t>
+          <t>dokze@example.org</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -8788,27 +8788,27 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Поташев</t>
+          <t>Кевовев</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Станислав</t>
+          <t>Банопадар</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ильич</t>
+          <t>Фарич</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ИЯИ</t>
+          <t>ВИР</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>s.potashev@mail.ru</t>
+          <t>kevove@example.org</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -8835,22 +8835,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Макаров</t>
+          <t>Гутебов</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Данила</t>
+          <t>Лоназа</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>makarov-danila-2001@mail.ru</t>
+          <t>gutebovnomuzibu@example.org</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -8877,22 +8877,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Безбах</t>
+          <t>Догутм</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Пазией</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>bezbakh@jinr.ru</t>
+          <t>dog@example.org</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
@@ -8919,22 +8919,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Ryzhkov</t>
+          <t>Gusurov</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nikita</t>
+          <t>Susaka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ryzhkov@theor.jinr.ru</t>
+          <t>gusurovdo@example.org</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -8959,22 +8959,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Адоньев</t>
+          <t>Неробев</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Степан</t>
+          <t>Вефозн</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>КВУ</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stepan1018@mail.ru</t>
+          <t>nerobe@example.org</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -8999,22 +8999,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Karanfil</t>
+          <t>Morikopm</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ege</t>
+          <t>Raa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>karanfil@jinr.ru</t>
+          <t>mori@example.org</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -9039,22 +9039,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Mikhailova</t>
+          <t>Gumirabova</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tatiana</t>
+          <t>Peniska</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>tmikh@jinr.ru</t>
+          <t>g@example.org</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -9079,22 +9079,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Молоторенко</t>
+          <t>Денипоненко</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ксения</t>
+          <t>Ракеря</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ВГУ, ОИЯИ</t>
+          <t>ЛУГ, ЛАРН</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>molotorenkoksenia@gmail.com</t>
+          <t>deniponenkoburi@example.org</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -9119,22 +9119,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Унжакова</t>
+          <t>Вебутова</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Лана</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>РифГУ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>a.unzhakova@spbu.ru</t>
+          <t>vebutov@example.org</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -9159,27 +9159,27 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Goncharenko</t>
+          <t>Sudadomenko</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Kalk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Alexandrovich</t>
+          <t>Nosububkovich</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ЛАРЕН</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>iv.gonch.0907@gmail.com</t>
+          <t>sudadomenko@example.org</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -9204,27 +9204,27 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Андреев</t>
+          <t>Гукасев</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Дасуравид</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Деладеслович</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>andreev.av20@physics.msu.ru</t>
+          <t>gukasevvezipolo@example.org</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -9249,27 +9249,27 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Ковалев</t>
+          <t>Фафопев</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Наривз</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Говекович</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>КВУ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>physics1818@yandex.ru</t>
+          <t>fafopevvo@example.org</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
@@ -9294,27 +9294,27 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Скобляков</t>
+          <t>Доневобов</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Мигодой</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Викторович</t>
+          <t>Нопепзович</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>БАР ОТ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>dinAlt220@yandex.ru</t>
+          <t>donevob@example.org</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -9339,27 +9339,27 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Канцырев</t>
+          <t>Санебпев</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Ридомуй</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Викторович</t>
+          <t>Букомнович</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>БАР ОТ</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>kantsyrev@itep.ru</t>
+          <t>saneb@example.org</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
@@ -9384,22 +9384,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Лашин</t>
+          <t>Форин</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Константин</t>
+          <t>Вонапепосб</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ВНИИЭФ</t>
+          <t>БАРХАН</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>kosty2112@gmail.com</t>
+          <t>forinfa@example.org</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
@@ -9424,27 +9424,27 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Олейников</t>
+          <t>Ропегуров</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Владислав</t>
+          <t>Давокенав</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Петрович</t>
+          <t>Нокгович</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ИЯФ Новосиб</t>
+          <t>НОЛ Приволж</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>V.P.Oleynikov@inp.nsk.su</t>
+          <t>ropegurovnak@example.org</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
@@ -9469,22 +9469,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Петров</t>
+          <t>Павбов</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Нигусуой</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>МИФИ</t>
+          <t>ТЕЗО</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>grigoriy.6.petrov@gmail.com</t>
+          <t>pavbovlorimumup@example.org</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
@@ -9509,27 +9509,27 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Семенов</t>
+          <t>Корилов</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Мукаой</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Госагонсович</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>НИЦ КИ</t>
+          <t>БАР ОТ</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>kindr_cool@mail.ru</t>
+          <t>korilo@example.org</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
@@ -9554,22 +9554,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Бурякова</t>
+          <t>Тагомова</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Посза</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>ВНИИЭф</t>
+          <t>БАРХАф</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>suyazova.elena@mail.ru</t>
+          <t>tagomovamo@example.org</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
@@ -9594,27 +9594,27 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Розов</t>
+          <t>Посов</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Мибаой</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Данониндович</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>rozovs@jinr.ru</t>
+          <t>po@example.org</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
@@ -9639,27 +9639,27 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Каретников</t>
+          <t>Ларорамбов</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Лерисз</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Донатович</t>
+          <t>Ропатович</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ВНИИА</t>
+          <t>ПЛИОН</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>mcsym01@gmail.com</t>
+          <t>laror@example.org</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -9684,22 +9684,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Данилкин</t>
+          <t>Гулелкин</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Владислав</t>
+          <t>Тарабанат</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>donyvlad@gmail.com</t>
+          <t>gulelk@example.org</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
@@ -9724,27 +9724,27 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Веденеев</t>
+          <t>Расардев</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Вячеслав</t>
+          <t>Мулонелб</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Юрьевич</t>
+          <t>Лелевич</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>vvedeneyev@gmail.com</t>
+          <t>rasardev@example.org</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
@@ -9769,27 +9769,27 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Новоселов</t>
+          <t>Кефофатов</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Нимокой</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Сергеевич</t>
+          <t>Пафафевич</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>noval@jinr.ru</t>
+          <t>k@example.org</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
@@ -9814,22 +9814,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Зимин</t>
+          <t>Фодин</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Илья</t>
+          <t>Кавя</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>zimin@jinr.ru</t>
+          <t>f@example.org</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
@@ -9854,27 +9854,27 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Сидорова</t>
+          <t>Дефосова</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ольга</t>
+          <t>Неска</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Викторовна</t>
+          <t>Досасровна</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>sidorova@jinr.ru</t>
+          <t>defo@example.org</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -9899,22 +9899,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Strizhak</t>
+          <t>Rapafatc</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Semufodor</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>ИЯИ</t>
+          <t>ВИР</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>strizhak@inr.ru</t>
+          <t>rap@example.org</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -9939,22 +9939,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Суслов</t>
+          <t>Бадфов</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Мозр</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ivsuslov@jinr.ru</t>
+          <t>badf@example.org</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
@@ -9979,27 +9979,27 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Евсеев</t>
+          <t>Пегдев</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Зигиий</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Рисегокопович</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>evseevsa@jinr.ru</t>
+          <t>pegd@example.org</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
@@ -10024,27 +10024,27 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Смирнов</t>
+          <t>Ледалов</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Тафоь</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Самумович</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>ПИЯФ</t>
+          <t>СЕЛМ</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>smirnov_ib@pnpi.nrcki.ru</t>
+          <t>ledalovgonan@example.org</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
@@ -10069,27 +10069,27 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Стрекаловский</t>
+          <t>Пабусувииский</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Олег</t>
+          <t>Сасв</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Викторович</t>
+          <t>Мопонмович</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>stroleg1@yandex.ru</t>
+          <t>pabusu@example.org</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
@@ -10114,22 +10114,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Шимко</t>
+          <t>Морат</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Павел</t>
+          <t>Локол</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>КВУ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>pashashimko0306@gmail.com</t>
+          <t>moratranotale@example.org</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Цыганкова</t>
+          <t>Роседмова</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Валерия</t>
+          <t>Севогмя</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>СВКНИИ ДВО</t>
+          <t>МЕЛНИИ СЕВ</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>tsigankova.valeriya@mail.ru</t>
+          <t>rosedmovagupezi@example.org</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
@@ -10194,27 +10194,27 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Пухаева</t>
+          <t>Гомфева</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Нелли</t>
+          <t>Гунаи</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ефимовна</t>
+          <t>Кавловна</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pukhaeva@jinr.ru</t>
+          <t>gomf@example.org</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
@@ -10239,27 +10239,27 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Пухаева</t>
+          <t>Гомфева</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Нелли</t>
+          <t>Гунаи</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ефимовна</t>
+          <t>Кавловна</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>pukhaeva@jinr.ru</t>
+          <t>gomf@example.org</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
@@ -10284,27 +10284,27 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Пухаева</t>
+          <t>Гомфева</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Нелли</t>
+          <t>Гунаи</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ефимовна</t>
+          <t>Кавловна</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>pukhaeva@jinr.ru</t>
+          <t>gomf@example.org</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
@@ -10329,22 +10329,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Петровская</t>
+          <t>Дакофоская</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Пева</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Станиславовна</t>
+          <t>Легунигировна</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>anita3425@yandex.ru</t>
+          <t>dakofos@example.org</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
@@ -10369,27 +10369,27 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Бикметов</t>
+          <t>Кениртов</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Тевора</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Рафальевич</t>
+          <t>Гокезвевич</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>bikmetov@jinr.ru</t>
+          <t>keni@example.org</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
@@ -10414,27 +10414,27 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Вечернин</t>
+          <t>Посулпин</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Ловогирд</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Викторович</t>
+          <t>Гонемдович</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>РифГУ</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>v.vechernin@spbu.ru</t>
+          <t>posulpi@example.org</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
@@ -10459,22 +10459,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Tadebr</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shubham</t>
+          <t>Zidenig</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>КВУ</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>s.sharma.hep@gmail.com</t>
+          <t>tadebrvelo@example.org</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
@@ -10499,27 +10499,27 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Жаров</t>
+          <t>Вебов</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Талогп</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Нитепевич</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>РифГУ</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>m.zharov@spbu.ru</t>
+          <t>vebo@example.org</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
@@ -10544,27 +10544,27 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Идрисов</t>
+          <t>Сумизов</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Дим</t>
+          <t>Фоз</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Маратович</t>
+          <t>Лапетович</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ВИР БУК</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>idrisov.dim@mail.ru</t>
+          <t>sumizov@example.org</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr">
@@ -10589,27 +10589,27 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Plotnikov</t>
+          <t>Nigikezov</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Vasilii</t>
+          <t>Nafaguu</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Alexandrovich</t>
+          <t>Gidoledgovich</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>vplotnikov@jinr.ru</t>
+          <t>nigike@example.org</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
@@ -10634,27 +10634,27 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Зубанков</t>
+          <t>Молонлов</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Госадобаф</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Сугофозигович</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ВИР БУК</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>zubankov@inr.ru</t>
+          <t>mol@example.org</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
@@ -10679,27 +10679,27 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Андронов</t>
+          <t>Назилвов</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Евгений</t>
+          <t>Сапепай</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Мосавесдович</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>РифГУ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>e.v.andronov@spbu.ru</t>
+          <t>nazilvov@example.org</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
@@ -10726,27 +10726,27 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Герасименюк</t>
+          <t>Ракобувесас</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Николай</t>
+          <t>Ропогий</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Морономпович</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>ДВФУ</t>
+          <t>ШАЛМ</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>gerasimenyuk.nv@dvfu.ru</t>
+          <t>rakobuvesas@example.org</t>
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr">
@@ -10773,27 +10773,27 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Зайцев</t>
+          <t>Тавпев</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Буниий</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Рипемипефович</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>zaicev@jinr.ru</t>
+          <t>ta@example.org</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
@@ -10820,27 +10820,27 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Скородько</t>
+          <t>Винадорал</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Татьяна</t>
+          <t>Назинка</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Юрьевна</t>
+          <t>Фаневна</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ВИР БУК</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>tatiskor@mail.ru</t>
+          <t>vina@example.org</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
@@ -10867,27 +10867,27 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Friesen</t>
+          <t>Fabafav</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Rasupegma</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vadimovna</t>
+          <t>Ketevovna</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>avfriesen@theor.jinr.ru</t>
+          <t>fabafavdena@example.org</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
@@ -10912,27 +10912,27 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Авдеев</t>
+          <t>Детсев</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Лодеей</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Петрович</t>
+          <t>Зискович</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>avdeyev@jinr.ru</t>
+          <t>det@example.org</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
@@ -10957,27 +10957,27 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Иванищев</t>
+          <t>Тедекдев</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Коталей</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Кафолотанович</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>НИЦ КИ-ПИЯФ, СПбПУ</t>
+          <t>БАР ОТ-СЕЛМ, МорПУ</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>ivanishchev_da@pnpi.nrcki.ru</t>
+          <t>tedekdbalevbunef@example.org</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
@@ -11002,27 +11002,27 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Силагадзе</t>
+          <t>Сагоморик</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Зураб</t>
+          <t>Тевос</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Карлоевич</t>
+          <t>Певифевич</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>ИЯФ Новосиб</t>
+          <t>НОЛ Приволж</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>silagadze@inp.nsk.su</t>
+          <t>sagomori@example.org</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr">
@@ -11047,27 +11047,27 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Феофилов</t>
+          <t>Лагогпов</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Мибавиуй</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Лебаволанович</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>РифГУ</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>g.feofilov@spbu.ru</t>
+          <t>lagogp@example.org</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
@@ -11092,22 +11092,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Prokhorova</t>
+          <t>Sakakdbova</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Daria</t>
+          <t>Kogra</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tsinghua Univ., China</t>
+          <t>Mireldan Univ., Ostia</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>daria-prokhorova@mail.tsinghua.edu.cn</t>
+          <t>sakakdbovapavebuneziralap@example.org</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
@@ -11132,27 +11132,27 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Недорезов</t>
+          <t>Мумигунов</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Егор</t>
+          <t>Гост</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Вячеславович</t>
+          <t>Фомоленбович</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>nedorezov@jinr.ru</t>
+          <t>mumig@example.org</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
@@ -11177,27 +11177,27 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Ануфриев</t>
+          <t>Фадазгев</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Антон</t>
+          <t>Рипоб</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Витальевич</t>
+          <t>Горокбевич</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>РифГУ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>antonman200@yandex.ru</t>
+          <t>fadazgevs@example.org</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
@@ -11222,27 +11222,27 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Галактионов</t>
+          <t>Нефомотатов</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Кирилл</t>
+          <t>Довебн</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Фозитакафович</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>РифГУ</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>kirill.galaktionov@spbu.ru</t>
+          <t>nefomotatovvip@example.org</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -11267,27 +11267,27 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Дьяченко</t>
+          <t>Гиктенко</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Канипедег</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Трофимович</t>
+          <t>Неникпович</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>НИЦ КИ-ПИЯФ</t>
+          <t>БАР ОТ-СЕЛМ</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>dyachenko_a@mail.ru</t>
+          <t>giktenk@example.org</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
@@ -11312,27 +11312,27 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Белокурова</t>
+          <t>Фофапалова</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Светлана</t>
+          <t>Виновита</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Гиринревна</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>РифГУ</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>s.belokurova@spbu.ru</t>
+          <t>fofapalo@example.org</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
@@ -11357,27 +11357,27 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Размыслов</t>
+          <t>Ромусепов</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Константин</t>
+          <t>Покенамипг</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Нефонимвович</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>РифГУ</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>yoitz@yandex.ru</t>
+          <t>rom@example.org</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr">
@@ -11402,27 +11402,27 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Мягков</t>
+          <t>Гумпов</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Данила</t>
+          <t>Гопона</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Корифоселович</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>НИИЯФ МГУ</t>
+          <t>ЛАРЕН КВУ</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>danila.myagkov.msu@mail.ru</t>
+          <t>gumpovtafatasa@example.org</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
@@ -11447,22 +11447,22 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Vasilieva</t>
+          <t>Levevpeva</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Anastasiia</t>
+          <t>Fademifoma</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>МИФИ</t>
+          <t>ТЕЗО</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>anastasiyavasileva00@gmail.com</t>
+          <t>levevpevafonikamut@example.org</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -11487,27 +11487,27 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Калугин</t>
+          <t>Семумин</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Никита</t>
+          <t>Зикоба</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Константинович</t>
+          <t>Гикеногудсович</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>КИ ИФВЭ</t>
+          <t>ОТ ЗЕОН</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Nikita.Kalugin@ihep.ru</t>
+          <t>semuminvev@example.org</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
@@ -11532,27 +11532,27 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Чернышев</t>
+          <t>Ривербев</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Борис</t>
+          <t>Кесен</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Депатевич</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>МИФИ</t>
+          <t>ТЕЗО</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>chernyshev@mephi.ru</t>
+          <t>riverbe@example.org</t>
         </is>
       </c>
       <c r="I150" s="4" t="inlineStr">
@@ -11577,27 +11577,27 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Борзаков</t>
+          <t>Позинвов</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Фогиай</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Раридович</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>sbor@nf.jinr.ru</t>
+          <t>poz@example.org</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
@@ -11622,27 +11622,27 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Ефименко</t>
+          <t>Гумненко</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Мария</t>
+          <t>Факгя</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Константиновна</t>
+          <t>Нидеридатдовна</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>ТОГУ</t>
+          <t>РИВН</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>ef.maria97@yandex.ru</t>
+          <t>gumnenko@example.org</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
@@ -11667,27 +11667,27 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Зайцев</t>
+          <t>Бадфев</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Мибуай</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Мигусатебович</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>ТОГУ</t>
+          <t>РИВН</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>000282@togudv.ru</t>
+          <t>bpdf@example.org</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
@@ -11712,27 +11712,27 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Зайцев</t>
+          <t>Телкев</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Посапосув</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Сергеевич</t>
+          <t>Тебукевич</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>ТОГУ</t>
+          <t>РИВН</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>alzaytsev@togudv.ru</t>
+          <t>telkevl@example.org</t>
         </is>
       </c>
       <c r="I154" s="4" t="inlineStr">
@@ -11757,22 +11757,22 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Шалапинин</t>
+          <t>Несумотин</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Денис</t>
+          <t>Гомип</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>shalapinin@theor.jinr.ru</t>
+          <t>nesumotinfaf@example.org</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
@@ -11797,27 +11797,27 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Рубцова</t>
+          <t>Ланрова</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ольга</t>
+          <t>Нибга</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Андреевна</t>
+          <t>Салемевна</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ЛАРЕН</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>rubtsova-olga@yandex.ru</t>
+          <t>lanrbovaguk@example.org</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
@@ -11842,27 +11842,27 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Мотовилов</t>
+          <t>Нобаралов</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Рипонофав</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Константинович</t>
+          <t>Ламупогузфович</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>motovilv@gmail.com</t>
+          <t>nobara@example.org</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
@@ -11887,27 +11887,27 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Яковлев</t>
+          <t>Фафовев</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Текаай</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Леонидович</t>
+          <t>Риделпович</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>РифГУ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>s.yakovlev@spbu.ru</t>
+          <t>fafovb@example.org</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
@@ -11932,27 +11932,27 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Кондратьев</t>
+          <t>Гуготалфев</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Гутевесв</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Гувобфевич</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>vkondrat@theor.jinr.ru</t>
+          <t>gugotalfev@example.org</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
@@ -11977,27 +11977,27 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Кондратьев</t>
+          <t>Гуготалфев</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Гутевесв</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Гувобфевич</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>vkondrat@theor.jinr.ru</t>
+          <t>gugotalfev@example.org</t>
         </is>
       </c>
       <c r="I160" s="4" t="inlineStr">
@@ -12022,22 +12022,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Лубашевский</t>
+          <t>Фаготаоский</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Бумодай</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>lubashev@jinr.ru</t>
+          <t>fago@example.org</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
@@ -12062,27 +12062,27 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Громов</t>
+          <t>Суфзов</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Тагонм</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Борисович</t>
+          <t>Ралозович</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ЛАРЕН</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>gromov@physics.msu.ru</t>
+          <t>sufzovgif@example.org</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
@@ -12107,27 +12107,27 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Михеев</t>
+          <t>Лерсев</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Семён</t>
+          <t>Зипеб</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Алексеевич</t>
+          <t>Лодедпевич</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>НИИЯФ</t>
+          <t>ЛАРЕН</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>semenmihey@gmail.com</t>
+          <t>lersevvi@example.org</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
@@ -12152,22 +12152,22 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Bados</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Abdul</t>
+          <t>Vovek</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Institute of Space Technology (Islamabad, Pakistan)</t>
+          <t>Institute of Coastal Mechanics (Calderon, Montavia)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>kabirkhanak1@gmail.com</t>
+          <t>badospopak@example.org</t>
         </is>
       </c>
       <c r="I164" s="4" t="inlineStr">
@@ -12192,22 +12192,22 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Le</t>
+          <t>Mv</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Huy Viet</t>
+          <t>Naa Nolc</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>leviethuy1@duytan.edu.vn</t>
+          <t>mvvovogigote@example.org</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
@@ -12232,22 +12232,22 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Киселев</t>
+          <t>Леникев</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Василий</t>
+          <t>Муленей</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Алексеевич</t>
+          <t>Темудсевич</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>kiselevva@fnkcrio.ru</t>
+          <t>lenikevg@example.org</t>
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr">
@@ -12272,27 +12272,27 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Щербаков</t>
+          <t>Фадогмов</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Корилей</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Кодокенебович</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>КВУ</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>sherbakov.aa15@physics.msu.ru</t>
+          <t>fadogmovkalovosab@example.org</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
@@ -12317,27 +12317,27 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Васильева</t>
+          <t>Тевегсева</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Алина</t>
+          <t>Зиспа</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Геннадиевна</t>
+          <t>Раладосевна</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>НИЦ КИ ИФВЭ</t>
+          <t>БАР ОТ ЗЕОН</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>vasilyeva-ag@ihep.ru</t>
+          <t>tevegsev@example.org</t>
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr">
@@ -12362,27 +12362,27 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Парменова</t>
+          <t>Погунлова</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Екатерина</t>
+          <t>Такефонва</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Владимировна</t>
+          <t>Сенивигровна</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>НИЦ КИ ИФВЭ</t>
+          <t>БАР ОТ ЗЕОН</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Ekaterina.Parmenova@ihep.ru</t>
+          <t>pogunlovafovigu@example.org</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
@@ -12407,27 +12407,27 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Петров</t>
+          <t>Нефбов</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Виталий</t>
+          <t>Фодопой</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Валерьевич</t>
+          <t>Факотфевич</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>РифГУ</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>vitalii17@bk.ru</t>
+          <t>nef@example.org</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
@@ -12452,27 +12452,27 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Мерзликин</t>
+          <t>Даротелин</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Мопероей</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Лобугмевич</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ВИР БУК</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>grishamerzlikin@gmail.com</t>
+          <t>darotelinfodo@example.org</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
@@ -12497,27 +12497,27 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Яковлев</t>
+          <t>Вокенев</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Иван</t>
+          <t>Нинф</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Андреевич</t>
+          <t>Фавозевич</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ВИР БУК</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>iv.a.yakovlev@gmail.com</t>
+          <t>vokenevpego@example.org</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
@@ -12542,27 +12542,27 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Зябченков</t>
+          <t>Нагубадов</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Владислав</t>
+          <t>Дегонилог</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Олегович</t>
+          <t>Нобфович</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>ОИЯИ</t>
+          <t>ЛАРН</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>vladislavzyabchenkov@mail.ru</t>
+          <t>nagubadovdegigol@example.org</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
@@ -12587,27 +12587,27 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Копылова</t>
+          <t>Норофова</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Екатерина</t>
+          <t>Рифовосма</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Александровна</t>
+          <t>Сепатегусовна</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>КВУ</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>ekaterinakalip@gmail.com</t>
+          <t>norofovasena@example.org</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
@@ -12632,22 +12632,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Мамаева</t>
+          <t>Надпева</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Саргылана</t>
+          <t>Песапегна</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>СФВУ (Якутия)</t>
+          <t>ОРВУ (Севера)</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>sargylana_mamaeva@mail.ru</t>
+          <t>nadpevapanape@example.org</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
@@ -12672,27 +12672,27 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Мерзликин</t>
+          <t>Даротелин</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Григорий</t>
+          <t>Мопероей</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Лобугмевич</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>ИЯИ РАН</t>
+          <t>ВИР БУК</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>grishamerzlikin@gmail.com</t>
+          <t>darotelinfodo@example.org</t>
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr">
@@ -12717,27 +12717,27 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Ашрапов</t>
+          <t>Зидепов</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Улугбек</t>
+          <t>Косапок</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Товфикович</t>
+          <t>Ногогмович</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>INR Uzbekistan</t>
+          <t>KNR Valemarchi</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>ashrapov@inp.uz</t>
+          <t>zid@example.org</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
@@ -12762,22 +12762,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Кузьменков</t>
+          <t>Гипанагмов</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Антон</t>
+          <t>Видон</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Семоробупович</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>zhelton@yandex.ru</t>
+          <t>gipan@example.org</t>
         </is>
       </c>
       <c r="I178" s="4" t="inlineStr">
@@ -12802,22 +12802,22 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Yusupov</t>
+          <t>Ninogov</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Mirjalol</t>
+          <t>Ribaponf</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>КВУ</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>ymirjalol@bk.ru</t>
+          <t>nin@example.org</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
@@ -12842,27 +12842,27 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Пятаев</t>
+          <t>Сасзев</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Сутелой</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Фопомбевич</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>МКНЦ, МГУ</t>
+          <t>ЛИСТ, КВУ</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>pataevdima2@gmail.com</t>
+          <t>saszbevbu@example.org</t>
         </is>
       </c>
       <c r="I180" s="4" t="inlineStr">
@@ -12887,27 +12887,27 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Оганян</t>
+          <t>Гинилр</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Ваге</t>
+          <t>Лосе</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Робертович</t>
+          <t>Фадефрович</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>МИФИ, МКНЦ</t>
+          <t>ТЕЗО, ЛИСТ</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>vahe.ohanyan2000@yandex.ru</t>
+          <t>ginilrbnamukol@example.org</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
@@ -12932,27 +12932,27 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Онищук</t>
+          <t>Кегимг</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Барла</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Александровна</t>
+          <t>Ногосекебовна</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>ИАЭ Обнинск</t>
+          <t>БЮР Прибреж</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>elenaonischuk@yandex.ru</t>
+          <t>kegimgbalmo@example.org</t>
         </is>
       </c>
       <c r="I182" s="4" t="inlineStr">
@@ -12977,27 +12977,27 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Балачков</t>
+          <t>Текефгов</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Максим</t>
+          <t>Тепосг</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Михайлович</t>
+          <t>Комобмович</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>ТПУ (Томск)</t>
+          <t>КРН (Берег)</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>mmb2@tpu.ru</t>
+          <t>t@example.org</t>
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr">
@@ -13022,27 +13022,27 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Сабуров</t>
+          <t>Супалов</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Вячеслав</t>
+          <t>Мивебусл</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Олегович</t>
+          <t>Монлович</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>МРНЦ им. А.Ф. Цыба</t>
+          <t>ЛКДЦ им. К.М. Орша</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>vosaburov@gmail.com</t>
+          <t>supalov@example.org</t>
         </is>
       </c>
       <c r="I184" s="4" t="inlineStr">
@@ -13067,27 +13067,27 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Соловьев</t>
+          <t>Лопертев</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Гудодой</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Догобсевич</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>МРНЦ им. А.Ф. Цыба</t>
+          <t>ЛКДЦ им. К.М. Орша</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>salonf@mrrc.obninsk.ru</t>
+          <t>lopertevra@example.org</t>
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr">
@@ -13112,27 +13112,27 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Хуцистова</t>
+          <t>Навекмова</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Алана</t>
+          <t>Котса</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Отариевна</t>
+          <t>Седеревна</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>КВУ</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>www.alanakhutS1@mail.ru</t>
+          <t>navekmbaova@example.org</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
@@ -13157,27 +13157,27 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Запорожская</t>
+          <t>Робутееская</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ксения</t>
+          <t>Фовофя</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Васильевна</t>
+          <t>Зипабфевна</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>КВУ</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>zaporozhskayakv@my.msu.ru</t>
+          <t>robuteeskayad@example.org</t>
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr">
@@ -13202,27 +13202,27 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Новикова</t>
+          <t>Кекогова</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Евгения</t>
+          <t>Кеникдя</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Антоновна</t>
+          <t>Нипоновна</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>МГУ</t>
+          <t>КВУ</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>evgeniyanovikovazar@gmail.com</t>
+          <t>kekogovamosubuken@example.org</t>
         </is>
       </c>
       <c r="I188" s="4" t="inlineStr">
@@ -13247,27 +13247,27 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Петрова</t>
+          <t>Теднова</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Кристина</t>
+          <t>Мидолеба</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Алексеевна</t>
+          <t>Зимункевна</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>СФВУ (Якутия)</t>
+          <t>ОРВУ (Севера)</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>kristinan_1604@mail.ru</t>
+          <t>tednovanip@example.org</t>
         </is>
       </c>
       <c r="I189" s="4" t="inlineStr">
@@ -13384,17 +13384,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Драчнев</t>
+          <t>Монанев</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Илья</t>
+          <t>Буся</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>drachnev_is@pnpi.nrcki.ru</t>
+          <t>monanevvinole@example.org</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -13416,17 +13416,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Efimov</t>
+          <t>Lepnov</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Nabulopos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>efimov98@mail.ru</t>
+          <t>lepn@example.org</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -13448,17 +13448,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Efimov</t>
+          <t>Lepnov</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Nabulopos</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>efimov98@mail.ru</t>
+          <t>lepn@example.org</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -13480,17 +13480,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Efimov</t>
+          <t>Lepnov</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Nabulopos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>efimov98@mail.ru</t>
+          <t>lepn@example.org</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -13512,22 +13512,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Жусупов</t>
+          <t>Нисемов</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Марат</t>
+          <t>Сакас</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Абжанович</t>
+          <t>Лесепович</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>raushan.kabatayeva@gmail.com</t>
+          <t>nisemovmokanisur@example.org</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -13549,22 +13549,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Жусупов</t>
+          <t>Нисемов</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Марат</t>
+          <t>Сакас</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Абжанович</t>
+          <t>Лесепович</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>raushan.kabatayeva@gmail.com</t>
+          <t>nisemovmokanisur@example.org</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -13586,22 +13586,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Отводенко</t>
+          <t>Будепенко</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Яна</t>
+          <t>Нба</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Олеговна</t>
+          <t>Гинсовна</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>otvodenko.yana@mail.ru</t>
+          <t>budepenkol@example.org</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -13623,22 +13623,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Панкратов</t>
+          <t>Водолавов</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Матвей</t>
+          <t>Булоай</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Вимипамисович</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>pankratovmatthew@yandex.ru</t>
+          <t>vodolavovlotan@example.org</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ulyanova</t>
+          <t>Mifakova</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Mukodedee</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ulyanovavs@my.msu.ru</t>
+          <t>mifakova@example.org</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -13692,22 +13692,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Хайруллин</t>
+          <t>Гилогипин</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Артур</t>
+          <t>Зинас</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ришатович</t>
+          <t>Банинович</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>a9072v@gmail.com</t>
+          <t>gilo@example.org</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -13729,22 +13729,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Богданов</t>
+          <t>Фонилвов</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Олег</t>
+          <t>Микн</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Викторович</t>
+          <t>Банортович</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>bov@tpu.ru</t>
+          <t>d@example.org</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -13766,22 +13766,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Гаганов</t>
+          <t>Фородов</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Валерий</t>
+          <t>Сугизий</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Валерьевич</t>
+          <t>Миногсевич</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>gavaler@rambler.ru</t>
+          <t>forodo@example.org</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -13803,22 +13803,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Долгополов</t>
+          <t>Мивинеплов</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Рикебутан</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Викторович</t>
+          <t>Нилормович</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>dolgopolov211@mail.ru</t>
+          <t>mivineplo@example.org</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -13840,17 +13840,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Дружинин</t>
+          <t>Досурнин</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Егор</t>
+          <t>Сенс</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>druzh2003@mail.ru</t>
+          <t>dosur@example.org</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -13872,22 +13872,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Зуев</t>
+          <t>Нзев</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Говизигиф</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Павлович</t>
+          <t>Робзович</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>alexanderzyev1@gmail.com</t>
+          <t>nzevkonakoke@example.org</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -13909,22 +13909,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Каспаров</t>
+          <t>Вофосров</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Нобурарил</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Кемугулемович</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>kasparov200191@gmail.com</t>
+          <t>vofosrovdaba@example.org</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -13946,22 +13946,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Кондратьев</t>
+          <t>Гуготалфев</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Гутевесв</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Гувобфевич</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>vkondrat@theor.jinr.ru</t>
+          <t>gugotalfev@example.org</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -13983,22 +13983,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Мицук</t>
+          <t>Парил</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Вячеслав</t>
+          <t>Рарисанп</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Несамовтович</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>vyacheslavmitsuk@yandex.ru</t>
+          <t>parilminekomin@example.org</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -14020,17 +14020,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Торилов</t>
+          <t>Фадасов</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Бутауй</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>s.torilov@spbu.ru</t>
+          <t>fadas@example.org</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -14052,17 +14052,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Аламури</t>
+          <t>Буфасас</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Абдулмажид Хусейн</t>
+          <t>Зиполафогт Ленилф</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>st123089@student.spbu.ru</t>
+          <t>bufasasvetav@example.org</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -14084,22 +14084,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Дормидонов</t>
+          <t>Садабупсов</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Депефагур</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Евгеньевич</t>
+          <t>Талотлевич</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>dormidonov@gmail.com</t>
+          <t>sadabups@example.org</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -14121,17 +14121,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dyachkov</t>
+          <t>Novidrov</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vyacheslav</t>
+          <t>Rolokotedk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>lnirp206@gmail.com</t>
+          <t>novidr@example.org</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -14153,17 +14153,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zeynalov</t>
+          <t>Vizivdov</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shakir</t>
+          <t>Vemusb</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>zeinal@nf.jinr.ru</t>
+          <t>viziv@example.org</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -14185,17 +14185,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Землин</t>
+          <t>Ламкин</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Егор</t>
+          <t>Ривб</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>zemlin.egor2011@yandex.ru</t>
+          <t>lamkinsekeveb@example.org</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -14217,22 +14217,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Комарова</t>
+          <t>Гипасова</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Дарья</t>
+          <t>Зимня</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Андреевна</t>
+          <t>Селофевна</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>komarova@spbu.ru</t>
+          <t>gipa@example.org</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -14254,22 +14254,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Кострыгина</t>
+          <t>Раселотина</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Анастасия</t>
+          <t>Нибадефтя</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Михайловна</t>
+          <t>Пололковна</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>naskostrigina2002@gmail.com</t>
+          <t>raselotinasadot@example.org</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -14291,17 +14291,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Лю</t>
+          <t>Лп</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Дэжуй</t>
+          <t>Фазий</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1034056141@qq.com</t>
+          <t>lpgus@example.org</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -14323,22 +14323,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Мордовской</t>
+          <t>Теноморатр</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Михаил</t>
+          <t>Гидефн</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Вадимович</t>
+          <t>Данолович</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>mvmordovsk@mail.ru</t>
+          <t>tenomo@example.org</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -14360,22 +14360,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Парменова</t>
+          <t>Погунлова</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Екатерина</t>
+          <t>Такефонва</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Владимировна</t>
+          <t>Сенивигровна</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ekaterina.Parmenova@ihep.ru</t>
+          <t>pogunlovafovigu@example.org</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -14397,22 +14397,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Петровская</t>
+          <t>Дакофоская</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Пева</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Станиславовна</t>
+          <t>Легунигировна</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>anita3425@yandex.ru</t>
+          <t>dakofos@example.org</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -14434,22 +14434,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Писклюков</t>
+          <t>Нефолодов</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Пепаой</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Далогиланович</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>uvalov.dima@mail.ru</t>
+          <t>nefolod@example.org</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -14471,22 +14471,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Писклюков</t>
+          <t>Нефолодов</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Пепаой</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Далогиланович</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>uvalov.dima@mail.ru</t>
+          <t>nefolod@example.org</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -14508,22 +14508,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Писклюков</t>
+          <t>Нефолодов</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Пепаой</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Далогиланович</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>uvalov.dima@mail.ru</t>
+          <t>nefolod@example.org</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -14545,17 +14545,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sidorova</t>
+          <t>Defosova</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Olga</t>
+          <t>Nska</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>sidorova@jinr.ru</t>
+          <t>defo@example.org</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -14577,22 +14577,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Симонова</t>
+          <t>Сугинова</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Варвара</t>
+          <t>Сурогпа</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Аркадьевна</t>
+          <t>Лефонтевна</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>varvara.simonova@gmail.com</t>
+          <t>suginovatepapa@example.org</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -14614,22 +14614,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Толстых</t>
+          <t>Поламог</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Юлия</t>
+          <t>Лося</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Викторовна</t>
+          <t>Педегвовна</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>tolstyhiulya@yandex.ru</t>
+          <t>polamogkef@example.org</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -14651,22 +14651,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Шабанов</t>
+          <t>Пабумов</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Арсений</t>
+          <t>Кодозий</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Игоревич</t>
+          <t>Готфевич</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>arseniy.shabanov@phystech.edu</t>
+          <t>pabumovlasedopopo@example.org</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -14688,22 +14688,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Коваленко</t>
+          <t>Канесенко</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Фонанирв</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Фонетмевич</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>v.kovalenko@spbu.ru</t>
+          <t>kanesen@example.org</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -14725,22 +14725,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Коваленко</t>
+          <t>Канесенко</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Фонанирв</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Николаевич</t>
+          <t>Фонетмевич</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>v.kovalenko@spbu.ru</t>
+          <t>kanesen@example.org</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Дьяченко</t>
+          <t>Гиктенко</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Канипедег</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Трофимович</t>
+          <t>Неникпович</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>dyachenko_a@mail.ru</t>
+          <t>giktenk@example.org</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -14799,22 +14799,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Муратова</t>
+          <t>Голомова</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Валентина</t>
+          <t>Кабападса</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Сумулвевна</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>muratova_vn@pnpi.nrcki.ru</t>
+          <t>golomovafoven@example.org</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -14836,22 +14836,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Вуколова</t>
+          <t>Кегунова</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ангелина-Наталия</t>
+          <t>Лазинела-Лакамня</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Валерьевна</t>
+          <t>Зипетмевна</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>anvukolova@gmail.com</t>
+          <t>kegunova@example.org</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -14873,17 +14873,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Magomedov</t>
+          <t>Tanimipov</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gazimagomed</t>
+          <t>Podoginekat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>magomedov@jinr.ru</t>
+          <t>tanim@example.org</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -14905,22 +14905,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Николаева</t>
+          <t>Милортева</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Надежда</t>
+          <t>Муригфа</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Анатольевна</t>
+          <t>Ловебусевна</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>larsoon696@mail.ru</t>
+          <t>milort@example.org</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -14942,17 +14942,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Пекшев</t>
+          <t>Нолдев</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Андрей</t>
+          <t>Повеай</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pekshev_AN@nrcki.ru</t>
+          <t>noldevv@example.org</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -14974,17 +14974,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Сорокина</t>
+          <t>Додепина</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Аида</t>
+          <t>Рала</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>sorokina.ajda@ya.ru</t>
+          <t>dodepin@example.org</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -15006,17 +15006,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ibraimova</t>
+          <t>Monensova</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sayara</t>
+          <t>Falena</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>sayara_ibraimova@mail.ru</t>
+          <t>monensovalel@example.org</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -15038,27 +15038,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Мальцев</t>
+          <t>Кефонев</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Николай</t>
+          <t>Бадопей</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Фогубумусович</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>СПбГУ</t>
+          <t>РифГУ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>n.maltsev@spbu.ru</t>
+          <t>kefon@example.org</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -15148,12 +15148,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Указаны аудитории. Не приедут (доклады отменены): Варламов, Мардыбан, Безбах А. Н., Данилов, Каманин, Бытьев; постеры Долгополов, Торилов, Дормидонов, Землин, Комарова, Кострыгина, Ibraimova.</t>
+          <t>Указаны аудитории. Не приедут (доклады отменены): Зисаптов, Танирапм, Догутм П. Б., Патепов, Монедин, Ненсев; постеры Мивинеплов, Фадасов, Садабупсов, Ламкин, Гипасова, Раселотина, Monensova.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rooms added. Cancelled (will not attend): Varlamov, Mardyban, Bezbakh A. N., Danilov, Kamanin, Bytiev; posters Dolgopolov, Torilov, Dormidonov, Zemlin, Komarova, Kostrygina, Ibraimova.</t>
+          <t>Rooms added. Cancelled (will not attend): Zisaptov, Tanirapm, Dogutmb P. B., Patepov, Monedin, Nensev; posters Mivineplov, Fadasov, Sadabupsov, Lamkin, Gipasova, Raselotina, Monensova.</t>
         </is>
       </c>
     </row>
@@ -15178,12 +15178,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Председатели секционных заседаний. Доклад Н. А. Мальцева перенесён в постерную сессию. Время постеров 23.09, 16:45–18:00.</t>
+          <t>Председатели секционных заседаний. Доклад Б. Ф. Кефонева перенесён в постерную сессию. Время постеров 23.09, 16:45–18:00.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Section session chairs published. N. A. Maltsev’s talk moved to the poster session. Poster session time 23 Sep, 16:45–18:00.</t>
+          <t>Section session chairs published. B. F. Kefonev’s talk moved to the poster session. Poster session time 23 Sep, 16:45–18:00.</t>
         </is>
       </c>
     </row>
@@ -15193,12 +15193,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Перестановки докладов: И. Н. Изосимов (секция 2) и Е. А. Шевчик поменялись местами во вторник; пленарные М. И. Шитова и А. Ефимова — среда и суббота. Организация Д. А. Иванищева: НИЦ КИ-ПИЯФ, СПбПУ.</t>
+          <t>Перестановки докладов: Д. Д. Тенамсов (секция 2) и З. М. Микелп поменялись местами во вторник; пленарные Д. Л. Тебова и Н. Лепнова — среда и суббота. Организация К. К. Тедекдева: БАР ОТ-СЕЛМ, МорПУ.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Talks swapped: I. N. Izosimov (section 2) and E. A. Shevchik on Tuesday; plenaries of M. I. Shitov and A. Efimov — Wednesday and Saturday. Affiliation of D. A. Ivanishchev: NRC KI–PNPI, SPbPU.</t>
+          <t>Talks swapped: D. D. Tenamsov (section 2) and Z. M. Mikelpba on Tuesday; plenaries of D. L. Tebbov and N. Lepnov — Wednesday and Saturday. Affiliation of K. K. Tedekdbalev: BAR OT–SELM, MorPU.</t>
         </is>
       </c>
     </row>
@@ -15208,12 +15208,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>А. В. Дербин не приедет: его доклад снят, секция 6 в среду начинается в 14:00 без него. В пятницу секция 3 — в 315л, секция 7 — в 117л.</t>
+          <t>Р. М. Гиприн не приедет: его доклад снят, секция 6 в среду начинается в 14:00 без него. В пятницу секция 3 — в 315л, секция 7 — в 117л.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>A. V. Derbin will not attend: his talk is removed, and section 6 on Wednesday starts at 14:00 without it. On Friday, section 3 is in 315л and section 7 is in 117л.</t>
+          <t>R. M. Giprin will not attend: his talk is removed, and section 6 on Wednesday starts at 14:00 without it. On Friday, section 3 is in 315л and section 7 is in 117л.</t>
         </is>
       </c>
     </row>
@@ -15223,12 +15223,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Секция 7: Е. А. Копылова, M. Yusupov, Д. Н. Пятаев и В. Р. Оганян перенесены на пятницу, 14:45–15:45, после уже стоящих докладов. Остальные доклады секции 7 во вторник сдвинуты вперёд.</t>
+          <t>Секция 7: Р. С. Норофова, R. Ninogov, С. Ф. Сасзев и Л. Ф. Гинилр перенесены на пятницу, 14:45–15:45, после уже стоящих докладов. Остальные доклады секции 7 во вторник сдвинуты вперёд.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Section 7: E. A. Kopylova, M. Yusupov, D. N. Pyataev and V. R. Ohanyan are moved to Friday 14:45–15:45, after the existing section 7 talks. The other Tuesday section 7 talks move up.</t>
+          <t>Section 7: R. S. Norofova, R. Ninogov, S. F. Saszbev and L. F. Ginilrb are moved to Friday 14:45–15:45, after the existing section 7 talks. The other Tuesday section 7 talks move up.</t>
         </is>
       </c>
     </row>
@@ -15238,12 +15238,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Секция 7 в пятницу после кофе, 16:15–17:15, 117л: А. С. Петровская, затем Е. А. Онищук, А. Н. Соловьев и А. О. Хуцистова. Вечерняя секция 7 во вторник сокращена.</t>
+          <t>Секция 7 в пятницу после кофе, 16:15–17:15, 117л: П. Л. Дакофоская, затем Б. Н. Кегимг, Г. Д. Лопертев и К. С. Навекмова. Вечерняя секция 7 во вторник сокращена.</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Section 7 on Friday after coffee, 16:15–17:15, room 117л: A. S. Petrovskaya, then E. A. Onishchuk, A. N. Solovyev and A. O. Khutsistova. Tuesday evening section 7 is shortened.</t>
+          <t>Section 7 on Friday after coffee, 16:15–17:15, room 117л: P. L. Dakofoskaya, then B. N. Kegimgbal, G. D. Lopertev and K. S. Navekmbaova. Tuesday evening section 7 is shortened.</t>
         </is>
       </c>
     </row>
@@ -15283,12 +15283,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Доклад П. В. Кострюкова (секция 1, пятница) снят. Остальные доклады этого заседания сдвинуты вперёд, начало по-прежнему в 14:00.</t>
+          <t>Доклад Е. З. Кокепасова (секция 1, пятница) снят. Остальные доклады этого заседания сдвинуты вперёд, начало по-прежнему в 14:00.</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>P. V. Kostryukov’s talk (section 1, Friday) is removed. The other talks in that sitting move up; it still starts at 14:00.</t>
+          <t>E. Z. Kokepasbov’s talk (section 1, Friday) is removed. The other talks in that sitting move up; it still starts at 14:00.</t>
         </is>
       </c>
     </row>
